--- a/Datas/FormulaData.xlsx
+++ b/Datas/FormulaData.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t>formulaName</t>
   </si>
@@ -95,6 +95,10 @@
   </si>
   <si>
     <t>1001,1002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>produceTime</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -436,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:F4"/>
+  <dimension ref="A2:G4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -445,7 +449,7 @@
     <col min="5" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -464,8 +468,11 @@
       <c r="F2" t="s">
         <v>7</v>
       </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -484,8 +491,11 @@
       <c r="F3" t="s">
         <v>5</v>
       </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -503,6 +513,9 @@
       </c>
       <c r="F4">
         <v>2</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/FormulaData.xlsx
+++ b/Datas/FormulaData.xlsx
@@ -35,12 +35,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">  装备 = 0,
-    衣物=1,
-    药剂 = 2,
-    酒水 = 3,
-    冷食 = 4,
-    热食 = 5</t>
+          <t>铸造 = 0,纺织 = 1,书写=2, 粉磨 = 10, 徒手 = 11,蒸煮 = 12,烘烤 = 13,酿造 = 14,搅拌=15</t>
         </r>
         <r>
           <rPr>
@@ -60,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="176">
   <si>
     <t>formulaName</t>
   </si>
@@ -100,6 +95,498 @@
   <si>
     <t>produceTime</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>面粉</t>
+  </si>
+  <si>
+    <t>咖啡粉</t>
+  </si>
+  <si>
+    <t>黄油</t>
+  </si>
+  <si>
+    <t>腌芜菁</t>
+  </si>
+  <si>
+    <t>蔬菜沙拉</t>
+  </si>
+  <si>
+    <t>三明治</t>
+  </si>
+  <si>
+    <t>腌萝卜</t>
+  </si>
+  <si>
+    <t>拉面</t>
+  </si>
+  <si>
+    <t>蜂蜜蛋糕</t>
+  </si>
+  <si>
+    <t>披萨</t>
+  </si>
+  <si>
+    <t>腌黄瓜</t>
+  </si>
+  <si>
+    <t>烤西兰花</t>
+  </si>
+  <si>
+    <t>水煮蛋</t>
+  </si>
+  <si>
+    <t>烤肉串</t>
+  </si>
+  <si>
+    <t>饭团</t>
+  </si>
+  <si>
+    <t>烤面包</t>
+  </si>
+  <si>
+    <t>烤海苔</t>
+  </si>
+  <si>
+    <t>烤肉饼</t>
+  </si>
+  <si>
+    <t>汉堡</t>
+  </si>
+  <si>
+    <t>辣蟹堡</t>
+  </si>
+  <si>
+    <t>土豆泥</t>
+  </si>
+  <si>
+    <t>海鲜饭</t>
+  </si>
+  <si>
+    <t>烤玉米</t>
+  </si>
+  <si>
+    <t>蔬菜汁</t>
+  </si>
+  <si>
+    <t>西瓜果汁</t>
+  </si>
+  <si>
+    <t>奇异果汁</t>
+  </si>
+  <si>
+    <t>葡萄汁</t>
+  </si>
+  <si>
+    <t>菠萝汁</t>
+  </si>
+  <si>
+    <t>草莓汁</t>
+  </si>
+  <si>
+    <t>蓝莓汁</t>
+  </si>
+  <si>
+    <t>玉米汁</t>
+  </si>
+  <si>
+    <t>烤蜜薯</t>
+  </si>
+  <si>
+    <t>甜菜汁</t>
+  </si>
+  <si>
+    <t>奶酪</t>
+  </si>
+  <si>
+    <t>烤茄子</t>
+  </si>
+  <si>
+    <t>饺子</t>
+  </si>
+  <si>
+    <t>炖菜</t>
+  </si>
+  <si>
+    <t>烤芦笋</t>
+  </si>
+  <si>
+    <t>红菜汤</t>
+  </si>
+  <si>
+    <t>豌豆汤</t>
+  </si>
+  <si>
+    <t>草莓牛奶</t>
+  </si>
+  <si>
+    <t>莓莓果汁</t>
+  </si>
+  <si>
+    <t>鲑鱼饭团</t>
+  </si>
+  <si>
+    <t>拿铁</t>
+  </si>
+  <si>
+    <t>黑咖啡</t>
+  </si>
+  <si>
+    <t>葡萄酒</t>
+  </si>
+  <si>
+    <t>伏特加</t>
+  </si>
+  <si>
+    <t>啤酒</t>
+  </si>
+  <si>
+    <t>朗姆</t>
+  </si>
+  <si>
+    <t>野蜂拉格</t>
+  </si>
+  <si>
+    <t>双莓白兰地</t>
+  </si>
+  <si>
+    <t>绯红之吻</t>
+  </si>
+  <si>
+    <t>阳光男孩</t>
+  </si>
+  <si>
+    <t>盐烤鲮鱼</t>
+  </si>
+  <si>
+    <t>盐烤丁鱼</t>
+  </si>
+  <si>
+    <t>盐烤虹鳟鱼</t>
+  </si>
+  <si>
+    <t>烤鲷鱼</t>
+  </si>
+  <si>
+    <t>盐烤金鳟鱼</t>
+  </si>
+  <si>
+    <t>盐烤鲑鱼</t>
+  </si>
+  <si>
+    <t>烤沙丁鱼串</t>
+  </si>
+  <si>
+    <t>烤竹荚鱼</t>
+  </si>
+  <si>
+    <t>烤海鳗</t>
+  </si>
+  <si>
+    <t>烤比目鱼</t>
+  </si>
+  <si>
+    <t>烤河豚鱼</t>
+  </si>
+  <si>
+    <t>烤条石鲷</t>
+  </si>
+  <si>
+    <t>烤红鲷鱼</t>
+  </si>
+  <si>
+    <t>烤蓝蟹</t>
+  </si>
+  <si>
+    <t>烤龙虾</t>
+  </si>
+  <si>
+    <t>烤金枪鱼</t>
+  </si>
+  <si>
+    <t>煮蟹肉</t>
+  </si>
+  <si>
+    <t>海鲜浓汤</t>
+  </si>
+  <si>
+    <t>鳗鱼饭</t>
+  </si>
+  <si>
+    <t>鲫鱼蔬菜汤</t>
+  </si>
+  <si>
+    <t>鲮鱼丸</t>
+  </si>
+  <si>
+    <t>鲑鱼刺身</t>
+  </si>
+  <si>
+    <t>章鱼小丸子</t>
+  </si>
+  <si>
+    <t>炖煮条石鲷</t>
+  </si>
+  <si>
+    <t>红鲷刺身</t>
+  </si>
+  <si>
+    <t>河豚刺身</t>
+  </si>
+  <si>
+    <t>螃蟹煲</t>
+  </si>
+  <si>
+    <t>金枪鱼刺身</t>
+  </si>
+  <si>
+    <t>龙虾鱼子酱</t>
+  </si>
+  <si>
+    <t>1020</t>
+  </si>
+  <si>
+    <t>1024</t>
+  </si>
+  <si>
+    <t>1001,3002</t>
+  </si>
+  <si>
+    <t>1002,1005,1009,1006</t>
+  </si>
+  <si>
+    <t>3112,1002,1006,1008</t>
+  </si>
+  <si>
+    <t>1004,3002</t>
+  </si>
+  <si>
+    <t>3009,3008,1003,3109</t>
+  </si>
+  <si>
+    <t>3009,3007,3005</t>
+  </si>
+  <si>
+    <t>3009,3130,1013,3008</t>
+  </si>
+  <si>
+    <t>1006,3002</t>
+  </si>
+  <si>
+    <t>1007</t>
+  </si>
+  <si>
+    <t>3007</t>
+  </si>
+  <si>
+    <t>1003,3008,1011</t>
+  </si>
+  <si>
+    <t>3113,3000</t>
+  </si>
+  <si>
+    <t>3009,3004</t>
+  </si>
+  <si>
+    <t>3011</t>
+  </si>
+  <si>
+    <t>1016,3008,3002</t>
+  </si>
+  <si>
+    <t>3112,1008,3114,3130</t>
+  </si>
+  <si>
+    <t>3112,3166,1011,3130</t>
+  </si>
+  <si>
+    <t>1015,3011</t>
+  </si>
+  <si>
+    <t>3000,4105,4115,3006</t>
+  </si>
+  <si>
+    <t>1019,3011</t>
+  </si>
+  <si>
+    <t>1001,1006,1004,1005</t>
+  </si>
+  <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>1012</t>
+  </si>
+  <si>
+    <t>1022</t>
+  </si>
+  <si>
+    <t>1023</t>
+  </si>
+  <si>
+    <t>1025</t>
+  </si>
+  <si>
+    <t>1026</t>
+  </si>
+  <si>
+    <t>1019</t>
+  </si>
+  <si>
+    <t>1027,3005</t>
+  </si>
+  <si>
+    <t>1028</t>
+  </si>
+  <si>
+    <t>3006</t>
+  </si>
+  <si>
+    <t>3006,3001</t>
+  </si>
+  <si>
+    <t>1013,1016,1003,3002</t>
+  </si>
+  <si>
+    <t>3009,3008,1002,1003</t>
+  </si>
+  <si>
+    <t>1005,1018,1028,3011</t>
+  </si>
+  <si>
+    <t>1017</t>
+  </si>
+  <si>
+    <t>1028,1005,1008,3004</t>
+  </si>
+  <si>
+    <t>1014,3008,1009,3004</t>
+  </si>
+  <si>
+    <t>3006,3125</t>
+  </si>
+  <si>
+    <t>1026,1025,3005</t>
+  </si>
+  <si>
+    <t>3000,4021,3113</t>
+  </si>
+  <si>
+    <t>3010,3006,3004</t>
+  </si>
+  <si>
+    <t>3010,3004</t>
+  </si>
+  <si>
+    <t>3123,3001</t>
+  </si>
+  <si>
+    <t>1015,3001</t>
+  </si>
+  <si>
+    <t>1020,1021,3001</t>
+  </si>
+  <si>
+    <t>3129,3001</t>
+  </si>
+  <si>
+    <t>3005,1021,3001</t>
+  </si>
+  <si>
+    <t>3126,3125,3001</t>
+  </si>
+  <si>
+    <t>3125,3123,3121,3001</t>
+  </si>
+  <si>
+    <t>3122,3124,3127,3001</t>
+  </si>
+  <si>
+    <t>4006,3002</t>
+  </si>
+  <si>
+    <t>4009,3002</t>
+  </si>
+  <si>
+    <t>4015,3002</t>
+  </si>
+  <si>
+    <t>4016,3003</t>
+  </si>
+  <si>
+    <t>4017,3002</t>
+  </si>
+  <si>
+    <t>4021,3002</t>
+  </si>
+  <si>
+    <t>4100,3003</t>
+  </si>
+  <si>
+    <t>4101,3003</t>
+  </si>
+  <si>
+    <t>4103,3003</t>
+  </si>
+  <si>
+    <t>4106,3003</t>
+  </si>
+  <si>
+    <t>4109,3003</t>
+  </si>
+  <si>
+    <t>4111,3003</t>
+  </si>
+  <si>
+    <t>4112,3003</t>
+  </si>
+  <si>
+    <t>4113,3003</t>
+  </si>
+  <si>
+    <t>4115,3003</t>
+  </si>
+  <si>
+    <t>4116,3003</t>
+  </si>
+  <si>
+    <t>4007,3004</t>
+  </si>
+  <si>
+    <t>1018,3004,4100,4113</t>
+  </si>
+  <si>
+    <t>3153,3000</t>
+  </si>
+  <si>
+    <t>4000,1014,3004,1017</t>
+  </si>
+  <si>
+    <t>4006,1027</t>
+  </si>
+  <si>
+    <t>4021</t>
+  </si>
+  <si>
+    <t>4105,3007,3011</t>
+  </si>
+  <si>
+    <t>4111,1004</t>
+  </si>
+  <si>
+    <t>4112</t>
+  </si>
+  <si>
+    <t>4109</t>
+  </si>
+  <si>
+    <t>4113,1011,1009,1007</t>
+  </si>
+  <si>
+    <t>4116</t>
+  </si>
+  <si>
+    <t>3164,3134,1006,4021</t>
   </si>
 </sst>
 </file>
@@ -440,7 +927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G4"/>
+  <dimension ref="A2:G86"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -518,9 +1005,1896 @@
         <v>10</v>
       </c>
     </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>3009</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5">
+        <v>3009</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <v>3010</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6">
+        <v>3010</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>3011</v>
+      </c>
+      <c r="C7">
+        <v>11</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7">
+        <v>3011</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8">
+        <v>3100</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8">
+        <v>3100</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>3101</v>
+      </c>
+      <c r="C9">
+        <v>11</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9">
+        <v>3101</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10">
+        <v>3102</v>
+      </c>
+      <c r="C10">
+        <v>11</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10">
+        <v>3102</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11">
+        <v>3103</v>
+      </c>
+      <c r="C11">
+        <v>12</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11">
+        <v>3103</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12">
+        <v>3104</v>
+      </c>
+      <c r="C12">
+        <v>13</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <v>3104</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13">
+        <v>3105</v>
+      </c>
+      <c r="C13">
+        <v>13</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13">
+        <v>3105</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14">
+        <v>3106</v>
+      </c>
+      <c r="C14">
+        <v>11</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14">
+        <v>3106</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15">
+        <v>3107</v>
+      </c>
+      <c r="C15">
+        <v>13</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15">
+        <v>3107</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16">
+        <v>3108</v>
+      </c>
+      <c r="C16">
+        <v>12</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16">
+        <v>3108</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17">
+        <v>3109</v>
+      </c>
+      <c r="C17">
+        <v>13</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17">
+        <v>3109</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18">
+        <v>3110</v>
+      </c>
+      <c r="C18">
+        <v>11</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18">
+        <v>3110</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19">
+        <v>3111</v>
+      </c>
+      <c r="C19">
+        <v>13</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19">
+        <v>3111</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20">
+        <v>3112</v>
+      </c>
+      <c r="C20">
+        <v>13</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20">
+        <v>3112</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21">
+        <v>3113</v>
+      </c>
+      <c r="C21">
+        <v>13</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21">
+        <v>3113</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22">
+        <v>3114</v>
+      </c>
+      <c r="C22">
+        <v>11</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22">
+        <v>3114</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23">
+        <v>3115</v>
+      </c>
+      <c r="C23">
+        <v>11</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23">
+        <v>3115</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24">
+        <v>3116</v>
+      </c>
+      <c r="C24">
+        <v>12</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24">
+        <v>3116</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25">
+        <v>3117</v>
+      </c>
+      <c r="C25">
+        <v>12</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25">
+        <v>3117</v>
+      </c>
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26">
+        <v>3118</v>
+      </c>
+      <c r="C26">
+        <v>13</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26">
+        <v>3118</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27">
+        <v>3119</v>
+      </c>
+      <c r="C27">
+        <v>15</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E27">
+        <v>3119</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28">
+        <v>3120</v>
+      </c>
+      <c r="C28">
+        <v>15</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E28">
+        <v>3120</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29">
+        <v>3121</v>
+      </c>
+      <c r="C29">
+        <v>15</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29">
+        <v>3121</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30">
+        <v>3122</v>
+      </c>
+      <c r="C30">
+        <v>15</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30">
+        <v>3122</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31">
+        <v>3123</v>
+      </c>
+      <c r="C31">
+        <v>15</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E31">
+        <v>3123</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32">
+        <v>3124</v>
+      </c>
+      <c r="C32">
+        <v>15</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E32">
+        <v>3124</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+      <c r="G32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33">
+        <v>3125</v>
+      </c>
+      <c r="C33">
+        <v>15</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E33">
+        <v>3125</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34">
+        <v>3126</v>
+      </c>
+      <c r="C34">
+        <v>15</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E34">
+        <v>3126</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35">
+        <v>3127</v>
+      </c>
+      <c r="C35">
+        <v>13</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35">
+        <v>3127</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+      <c r="G35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36">
+        <v>3128</v>
+      </c>
+      <c r="C36">
+        <v>15</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E36">
+        <v>3128</v>
+      </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
+      <c r="G36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37">
+        <v>3129</v>
+      </c>
+      <c r="C37">
+        <v>15</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E37">
+        <v>3129</v>
+      </c>
+      <c r="F37">
+        <v>2</v>
+      </c>
+      <c r="G37">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38">
+        <v>3130</v>
+      </c>
+      <c r="C38">
+        <v>14</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E38">
+        <v>3130</v>
+      </c>
+      <c r="F38">
+        <v>2</v>
+      </c>
+      <c r="G38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39">
+        <v>3131</v>
+      </c>
+      <c r="C39">
+        <v>13</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E39">
+        <v>3131</v>
+      </c>
+      <c r="F39">
+        <v>2</v>
+      </c>
+      <c r="G39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40">
+        <v>3132</v>
+      </c>
+      <c r="C40">
+        <v>12</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E40">
+        <v>3132</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+      <c r="G40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41">
+        <v>3133</v>
+      </c>
+      <c r="C41">
+        <v>12</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E41">
+        <v>3133</v>
+      </c>
+      <c r="F41">
+        <v>2</v>
+      </c>
+      <c r="G41">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42">
+        <v>3134</v>
+      </c>
+      <c r="C42">
+        <v>13</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E42">
+        <v>3134</v>
+      </c>
+      <c r="F42">
+        <v>2</v>
+      </c>
+      <c r="G42">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43">
+        <v>3135</v>
+      </c>
+      <c r="C43">
+        <v>12</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E43">
+        <v>3135</v>
+      </c>
+      <c r="F43">
+        <v>2</v>
+      </c>
+      <c r="G43">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44">
+        <v>3136</v>
+      </c>
+      <c r="C44">
+        <v>12</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E44">
+        <v>3136</v>
+      </c>
+      <c r="F44">
+        <v>2</v>
+      </c>
+      <c r="G44">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45">
+        <v>3137</v>
+      </c>
+      <c r="C45">
+        <v>15</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E45">
+        <v>3137</v>
+      </c>
+      <c r="F45">
+        <v>2</v>
+      </c>
+      <c r="G45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46">
+        <v>3138</v>
+      </c>
+      <c r="C46">
+        <v>15</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E46">
+        <v>3138</v>
+      </c>
+      <c r="F46">
+        <v>2</v>
+      </c>
+      <c r="G46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47">
+        <v>3139</v>
+      </c>
+      <c r="C47">
+        <v>11</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E47">
+        <v>3139</v>
+      </c>
+      <c r="F47">
+        <v>2</v>
+      </c>
+      <c r="G47">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48">
+        <v>3140</v>
+      </c>
+      <c r="C48">
+        <v>15</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E48">
+        <v>3140</v>
+      </c>
+      <c r="F48">
+        <v>2</v>
+      </c>
+      <c r="G48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49">
+        <v>3141</v>
+      </c>
+      <c r="C49">
+        <v>15</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E49">
+        <v>3141</v>
+      </c>
+      <c r="F49">
+        <v>2</v>
+      </c>
+      <c r="G49">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50">
+        <v>3142</v>
+      </c>
+      <c r="C50">
+        <v>14</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E50">
+        <v>3142</v>
+      </c>
+      <c r="F50">
+        <v>2</v>
+      </c>
+      <c r="G50">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51">
+        <v>3143</v>
+      </c>
+      <c r="C51">
+        <v>14</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E51">
+        <v>3143</v>
+      </c>
+      <c r="F51">
+        <v>2</v>
+      </c>
+      <c r="G51">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52">
+        <v>3144</v>
+      </c>
+      <c r="C52">
+        <v>14</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E52">
+        <v>3144</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="G52">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53">
+        <v>3145</v>
+      </c>
+      <c r="C53">
+        <v>14</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E53">
+        <v>3145</v>
+      </c>
+      <c r="F53">
+        <v>2</v>
+      </c>
+      <c r="G53">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54">
+        <v>3146</v>
+      </c>
+      <c r="C54">
+        <v>14</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E54">
+        <v>3146</v>
+      </c>
+      <c r="F54">
+        <v>2</v>
+      </c>
+      <c r="G54">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55">
+        <v>3147</v>
+      </c>
+      <c r="C55">
+        <v>14</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E55">
+        <v>3147</v>
+      </c>
+      <c r="F55">
+        <v>2</v>
+      </c>
+      <c r="G55">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56">
+        <v>3148</v>
+      </c>
+      <c r="C56">
+        <v>14</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E56">
+        <v>3148</v>
+      </c>
+      <c r="F56">
+        <v>2</v>
+      </c>
+      <c r="G56">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57">
+        <v>3149</v>
+      </c>
+      <c r="C57">
+        <v>13</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E57">
+        <v>3149</v>
+      </c>
+      <c r="F57">
+        <v>2</v>
+      </c>
+      <c r="G57">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58">
+        <v>3150</v>
+      </c>
+      <c r="C58">
+        <v>13</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E58">
+        <v>3150</v>
+      </c>
+      <c r="F58">
+        <v>2</v>
+      </c>
+      <c r="G58">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59">
+        <v>3151</v>
+      </c>
+      <c r="C59">
+        <v>13</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E59">
+        <v>3151</v>
+      </c>
+      <c r="F59">
+        <v>2</v>
+      </c>
+      <c r="G59">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60">
+        <v>3152</v>
+      </c>
+      <c r="C60">
+        <v>13</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E60">
+        <v>3152</v>
+      </c>
+      <c r="F60">
+        <v>2</v>
+      </c>
+      <c r="G60">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61">
+        <v>3153</v>
+      </c>
+      <c r="C61">
+        <v>13</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E61">
+        <v>3153</v>
+      </c>
+      <c r="F61">
+        <v>2</v>
+      </c>
+      <c r="G61">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62">
+        <v>3154</v>
+      </c>
+      <c r="C62">
+        <v>13</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E62">
+        <v>3154</v>
+      </c>
+      <c r="F62">
+        <v>2</v>
+      </c>
+      <c r="G62">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63">
+        <v>3155</v>
+      </c>
+      <c r="C63">
+        <v>13</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E63">
+        <v>3155</v>
+      </c>
+      <c r="F63">
+        <v>2</v>
+      </c>
+      <c r="G63">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64">
+        <v>3156</v>
+      </c>
+      <c r="C64">
+        <v>13</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E64">
+        <v>3156</v>
+      </c>
+      <c r="F64">
+        <v>2</v>
+      </c>
+      <c r="G64">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65">
+        <v>3157</v>
+      </c>
+      <c r="C65">
+        <v>13</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E65">
+        <v>3157</v>
+      </c>
+      <c r="F65">
+        <v>2</v>
+      </c>
+      <c r="G65">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66">
+        <v>3158</v>
+      </c>
+      <c r="C66">
+        <v>13</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E66">
+        <v>3158</v>
+      </c>
+      <c r="F66">
+        <v>2</v>
+      </c>
+      <c r="G66">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67">
+        <v>3159</v>
+      </c>
+      <c r="C67">
+        <v>13</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E67">
+        <v>3159</v>
+      </c>
+      <c r="F67">
+        <v>2</v>
+      </c>
+      <c r="G67">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>75</v>
+      </c>
+      <c r="B68">
+        <v>3160</v>
+      </c>
+      <c r="C68">
+        <v>13</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E68">
+        <v>3160</v>
+      </c>
+      <c r="F68">
+        <v>2</v>
+      </c>
+      <c r="G68">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69">
+        <v>3161</v>
+      </c>
+      <c r="C69">
+        <v>13</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E69">
+        <v>3161</v>
+      </c>
+      <c r="F69">
+        <v>2</v>
+      </c>
+      <c r="G69">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70">
+        <v>3162</v>
+      </c>
+      <c r="C70">
+        <v>13</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E70">
+        <v>3162</v>
+      </c>
+      <c r="F70">
+        <v>2</v>
+      </c>
+      <c r="G70">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71">
+        <v>3163</v>
+      </c>
+      <c r="C71">
+        <v>13</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E71">
+        <v>3163</v>
+      </c>
+      <c r="F71">
+        <v>2</v>
+      </c>
+      <c r="G71">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72">
+        <v>3164</v>
+      </c>
+      <c r="C72">
+        <v>13</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E72">
+        <v>3164</v>
+      </c>
+      <c r="F72">
+        <v>2</v>
+      </c>
+      <c r="G72">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73">
+        <v>3165</v>
+      </c>
+      <c r="C73">
+        <v>12</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E73">
+        <v>3165</v>
+      </c>
+      <c r="F73">
+        <v>2</v>
+      </c>
+      <c r="G73">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74">
+        <v>3166</v>
+      </c>
+      <c r="C74">
+        <v>12</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E74">
+        <v>3166</v>
+      </c>
+      <c r="F74">
+        <v>2</v>
+      </c>
+      <c r="G74">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>82</v>
+      </c>
+      <c r="B75">
+        <v>3167</v>
+      </c>
+      <c r="C75">
+        <v>12</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E75">
+        <v>3167</v>
+      </c>
+      <c r="F75">
+        <v>2</v>
+      </c>
+      <c r="G75">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>83</v>
+      </c>
+      <c r="B76">
+        <v>3168</v>
+      </c>
+      <c r="C76">
+        <v>11</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E76">
+        <v>3168</v>
+      </c>
+      <c r="F76">
+        <v>2</v>
+      </c>
+      <c r="G76">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77">
+        <v>3169</v>
+      </c>
+      <c r="C77">
+        <v>12</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E77">
+        <v>3169</v>
+      </c>
+      <c r="F77">
+        <v>2</v>
+      </c>
+      <c r="G77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>85</v>
+      </c>
+      <c r="B78">
+        <v>3170</v>
+      </c>
+      <c r="C78">
+        <v>12</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E78">
+        <v>3170</v>
+      </c>
+      <c r="F78">
+        <v>2</v>
+      </c>
+      <c r="G78">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>86</v>
+      </c>
+      <c r="B79">
+        <v>3171</v>
+      </c>
+      <c r="C79">
+        <v>11</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E79">
+        <v>3171</v>
+      </c>
+      <c r="F79">
+        <v>2</v>
+      </c>
+      <c r="G79">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80">
+        <v>3172</v>
+      </c>
+      <c r="C80">
+        <v>12</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E80">
+        <v>3172</v>
+      </c>
+      <c r="F80">
+        <v>2</v>
+      </c>
+      <c r="G80">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81">
+        <v>3173</v>
+      </c>
+      <c r="C81">
+        <v>12</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E81">
+        <v>3173</v>
+      </c>
+      <c r="F81">
+        <v>2</v>
+      </c>
+      <c r="G81">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>89</v>
+      </c>
+      <c r="B82">
+        <v>3174</v>
+      </c>
+      <c r="C82">
+        <v>11</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E82">
+        <v>3174</v>
+      </c>
+      <c r="F82">
+        <v>2</v>
+      </c>
+      <c r="G82">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>90</v>
+      </c>
+      <c r="B83">
+        <v>3175</v>
+      </c>
+      <c r="C83">
+        <v>11</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E83">
+        <v>3175</v>
+      </c>
+      <c r="F83">
+        <v>2</v>
+      </c>
+      <c r="G83">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>91</v>
+      </c>
+      <c r="B84">
+        <v>3176</v>
+      </c>
+      <c r="C84">
+        <v>12</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E84">
+        <v>3176</v>
+      </c>
+      <c r="F84">
+        <v>2</v>
+      </c>
+      <c r="G84">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>92</v>
+      </c>
+      <c r="B85">
+        <v>3177</v>
+      </c>
+      <c r="C85">
+        <v>11</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E85">
+        <v>3177</v>
+      </c>
+      <c r="F85">
+        <v>2</v>
+      </c>
+      <c r="G85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>93</v>
+      </c>
+      <c r="B86">
+        <v>3178</v>
+      </c>
+      <c r="C86">
+        <v>11</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E86">
+        <v>3178</v>
+      </c>
+      <c r="F86">
+        <v>2</v>
+      </c>
+      <c r="G86">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Datas/FormulaData.xlsx
+++ b/Datas/FormulaData.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="FormulaData" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FormulaData!$A$3:$G$86</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1151,7 +1154,7 @@
         <v>3103</v>
       </c>
       <c r="C11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>99</v>
@@ -1174,7 +1177,7 @@
         <v>3104</v>
       </c>
       <c r="C12">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>100</v>
@@ -1220,7 +1223,7 @@
         <v>3106</v>
       </c>
       <c r="C14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>102</v>
@@ -1243,7 +1246,7 @@
         <v>3107</v>
       </c>
       <c r="C15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>103</v>
@@ -1266,7 +1269,7 @@
         <v>3108</v>
       </c>
       <c r="C16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>104</v>
@@ -1289,7 +1292,7 @@
         <v>3109</v>
       </c>
       <c r="C17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>105</v>
@@ -1312,7 +1315,7 @@
         <v>3110</v>
       </c>
       <c r="C18">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>106</v>
@@ -1335,7 +1338,7 @@
         <v>3111</v>
       </c>
       <c r="C19">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>107</v>
@@ -1404,7 +1407,7 @@
         <v>3114</v>
       </c>
       <c r="C22">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>110</v>
@@ -1450,7 +1453,7 @@
         <v>3116</v>
       </c>
       <c r="C24">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>112</v>
@@ -1496,7 +1499,7 @@
         <v>3118</v>
       </c>
       <c r="C26">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>114</v>
@@ -1519,7 +1522,7 @@
         <v>3119</v>
       </c>
       <c r="C27">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>115</v>
@@ -1703,7 +1706,7 @@
         <v>3127</v>
       </c>
       <c r="C35">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>123</v>
@@ -1726,7 +1729,7 @@
         <v>3128</v>
       </c>
       <c r="C36">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>124</v>
@@ -2209,7 +2212,7 @@
         <v>3149</v>
       </c>
       <c r="C57">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>146</v>
@@ -2577,7 +2580,7 @@
         <v>3165</v>
       </c>
       <c r="C73">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>162</v>
@@ -2892,9 +2895,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:G86"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="D13:D73" numberStoredAsText="1"/>
+  </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Datas/FormulaData.xlsx
+++ b/Datas/FormulaData.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="181">
   <si>
     <t>formulaName</t>
   </si>
@@ -590,6 +590,26 @@
   </si>
   <si>
     <t>3164,3134,1006,4021</t>
+  </si>
+  <si>
+    <t>木材</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>木柴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -930,7 +950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G86"/>
+  <dimension ref="A2:G90"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -2894,6 +2914,98 @@
         <v>10</v>
       </c>
     </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>176</v>
+      </c>
+      <c r="B87">
+        <v>2000</v>
+      </c>
+      <c r="C87">
+        <v>3</v>
+      </c>
+      <c r="D87">
+        <v>102</v>
+      </c>
+      <c r="E87">
+        <v>101</v>
+      </c>
+      <c r="F87">
+        <v>2</v>
+      </c>
+      <c r="G87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>177</v>
+      </c>
+      <c r="B88">
+        <v>2001</v>
+      </c>
+      <c r="C88">
+        <v>3</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E88">
+        <v>103</v>
+      </c>
+      <c r="F88">
+        <v>2</v>
+      </c>
+      <c r="G88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>177</v>
+      </c>
+      <c r="B89">
+        <v>2002</v>
+      </c>
+      <c r="C89">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E89">
+        <v>103</v>
+      </c>
+      <c r="F89">
+        <v>2</v>
+      </c>
+      <c r="G89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>177</v>
+      </c>
+      <c r="B90">
+        <v>2003</v>
+      </c>
+      <c r="C90">
+        <v>3</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E90">
+        <v>103</v>
+      </c>
+      <c r="F90">
+        <v>2</v>
+      </c>
+      <c r="G90">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:G86"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Datas/FormulaData.xlsx
+++ b/Datas/FormulaData.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="180">
   <si>
     <t>formulaName</t>
   </si>
@@ -601,10 +601,6 @@
   </si>
   <si>
     <t>104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>102</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -950,7 +946,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G90"/>
+  <dimension ref="A2:G89"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -2965,7 +2961,7 @@
         <v>177</v>
       </c>
       <c r="B89">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="C89">
         <v>3</v>
@@ -2980,29 +2976,6 @@
         <v>2</v>
       </c>
       <c r="G89">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
-        <v>177</v>
-      </c>
-      <c r="B90">
-        <v>2003</v>
-      </c>
-      <c r="C90">
-        <v>3</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E90">
-        <v>103</v>
-      </c>
-      <c r="F90">
-        <v>2</v>
-      </c>
-      <c r="G90">
         <v>2</v>
       </c>
     </row>

--- a/Datas/FormulaData.xlsx
+++ b/Datas/FormulaData.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="FormulaData" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FormulaData!$A$3:$G$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FormulaData!$A$3:$G$153</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -38,7 +39,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>铸造 = 0,纺织 = 1,书写=2, 粉磨 = 10, 徒手 = 11,蒸煮 = 12,烘烤 = 13,酿造 = 14,搅拌=15</t>
+          <t>铸造 = 0,缝纫 = 1,书写=2, 劈砍=3,加工=4，粉磨 = 10, 徒手 = 11,蒸煮 = 12,烘烤 = 13,酿造 = 14,搅拌=15</t>
         </r>
         <r>
           <rPr>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="305">
   <si>
     <t>formulaName</t>
   </si>
@@ -88,14 +89,6 @@
     <t>List&lt;int&gt;</t>
   </si>
   <si>
-    <t>测试西瓜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001,1002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>produceTime</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -606,13 +599,457 @@
   <si>
     <t>101</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>216</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毛线</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>布片</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>皮革</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>回春卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>振奋卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>昏睡卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>感电卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰氛卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>火氛卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>沉默卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>减速卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪避卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>力量卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>魅惑卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>290,292,244</t>
+  </si>
+  <si>
+    <t>294,265,207</t>
+  </si>
+  <si>
+    <t>251,287,257</t>
+  </si>
+  <si>
+    <t>290,225,286</t>
+  </si>
+  <si>
+    <t>267,261,286</t>
+  </si>
+  <si>
+    <t>284,291,286</t>
+  </si>
+  <si>
+    <t>263,255,210</t>
+  </si>
+  <si>
+    <t>236,259,250</t>
+  </si>
+  <si>
+    <t>285,278,281</t>
+  </si>
+  <si>
+    <t>288,256,240</t>
+  </si>
+  <si>
+    <t>293,289,254</t>
+  </si>
+  <si>
+    <t>长剑</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>诅咒之剑</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>烈焰之刃</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>大地之剑</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰之刃</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁枪</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>血腥之枪</t>
+  </si>
+  <si>
+    <t>骑士长枪</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>三叉戟</t>
+  </si>
+  <si>
+    <t>秘银长剑</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>幻影长枪</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斧</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒蜥之牙</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>恶魔之斧</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴雪斧</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>蛇皮鞭</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>藤鞭</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>女王鞭</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>蛇牙鞭</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷神之鞭</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡之鞭</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>布衣</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>皮铠</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>锁子甲</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>毛皮斗篷</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁铠甲</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>红莲之铠</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁龟铠</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>华丽背心</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>鳞铠</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>暗之袍</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>疾风背心</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法铠甲</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>钢刃锁甲</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>丝织长袍</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>水之羽衣</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>贵族长裙</t>
+  </si>
+  <si>
+    <t>幸运之衣</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>布鞋</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>皮鞋</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>士兵长靴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>登山者之靴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>运动鞋</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>贵族长靴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>武道鞋</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>骑士护胫</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>贤者之履</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>风神之履</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>踏浪长靴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1600,229,205,284</t>
+  </si>
+  <si>
+    <t>1600,218,299,212</t>
+  </si>
+  <si>
+    <t>1600,260,261,253</t>
+  </si>
+  <si>
+    <t>1605,259,237,239</t>
+  </si>
+  <si>
+    <t>1605,227,240,232</t>
+  </si>
+  <si>
+    <t>237,274,256,285</t>
+  </si>
+  <si>
+    <t>269,1605,264,208</t>
+  </si>
+  <si>
+    <t>1609,259,258,263</t>
+  </si>
+  <si>
+    <t>1609,253,260,267</t>
+  </si>
+  <si>
+    <t>270,225,239,1614</t>
+  </si>
+  <si>
+    <t>245,255,268,1615</t>
+  </si>
+  <si>
+    <t>1654,250,229,286</t>
+  </si>
+  <si>
+    <t>264,277,255,246</t>
+  </si>
+  <si>
+    <t>1651,242,247,241</t>
+  </si>
+  <si>
+    <t>1654,274,299,218</t>
+  </si>
+  <si>
+    <t>1656,279,234,247</t>
+  </si>
+  <si>
+    <t>248,1650,245,285</t>
+  </si>
+  <si>
+    <t>1701,234,223,279</t>
+  </si>
+  <si>
+    <t>1700,280,232,272</t>
+  </si>
+  <si>
+    <t>1702,275,240,299</t>
+  </si>
+  <si>
+    <t>1700,281,251,282</t>
+  </si>
+  <si>
+    <t>224,1704,264,258</t>
+  </si>
+  <si>
+    <t>1703,282,232,267</t>
+  </si>
+  <si>
+    <t>298,274</t>
+  </si>
+  <si>
+    <t>1600,220,257</t>
+  </si>
+  <si>
+    <t>104,298,274</t>
+  </si>
+  <si>
+    <t>1605,275,299</t>
+  </si>
+  <si>
+    <t>299,274,241</t>
+  </si>
+  <si>
+    <t>1609,254,211</t>
+  </si>
+  <si>
+    <t>238,276,214</t>
+  </si>
+  <si>
+    <t>221,276,214</t>
+  </si>
+  <si>
+    <t>1613,213,246</t>
+  </si>
+  <si>
+    <t>1612,211,1612</t>
+  </si>
+  <si>
+    <t>204,277</t>
+  </si>
+  <si>
+    <t>271,278,214</t>
+  </si>
+  <si>
+    <t>1651,227,299</t>
+  </si>
+  <si>
+    <t>1651,223,283</t>
+  </si>
+  <si>
+    <t>298,205</t>
+  </si>
+  <si>
+    <t>202,1654,210</t>
+  </si>
+  <si>
+    <t>272,228,277</t>
+  </si>
+  <si>
+    <t>273,278,271</t>
+  </si>
+  <si>
+    <t>1650,208,224</t>
+  </si>
+  <si>
+    <t>204,214,228</t>
+  </si>
+  <si>
+    <t>1650,232,282</t>
+  </si>
+  <si>
+    <t>204,222,278</t>
+  </si>
+  <si>
+    <t>271,222,278</t>
+  </si>
+  <si>
+    <t>298,210,202</t>
+  </si>
+  <si>
+    <t>1701,273,238</t>
+  </si>
+  <si>
+    <t>1700,208,214</t>
+  </si>
+  <si>
+    <t>传送卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>224,269,291</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -642,13 +1079,38 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -663,9 +1125,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -946,7 +1432,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G89"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A2:G153"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -998,90 +1485,90 @@
         <v>5</v>
       </c>
       <c r="G3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>3009</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4">
+        <v>3009</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>4001</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4">
-        <v>1010</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="B5">
+        <v>3010</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5">
+        <v>3010</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6">
+        <v>3011</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3002</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B5">
-        <v>3009</v>
-      </c>
-      <c r="C5">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5">
-        <v>3009</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6">
-        <v>3010</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6">
-        <v>3010</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
       <c r="B7">
-        <v>3011</v>
+        <v>3012</v>
       </c>
       <c r="C7">
         <v>11</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E7">
         <v>3011</v>
@@ -1093,18 +1580,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B8">
-        <v>3100</v>
+        <v>3013</v>
       </c>
       <c r="C8">
         <v>11</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E8">
         <v>3100</v>
@@ -1116,18 +1603,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9">
-        <v>3101</v>
+        <v>3014</v>
       </c>
       <c r="C9">
         <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E9">
         <v>3101</v>
@@ -1139,18 +1626,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B10">
-        <v>3102</v>
+        <v>3015</v>
       </c>
       <c r="C10">
         <v>11</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E10">
         <v>3102</v>
@@ -1162,18 +1649,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B11">
-        <v>3103</v>
+        <v>3016</v>
       </c>
       <c r="C11">
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E11">
         <v>3103</v>
@@ -1185,18 +1672,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B12">
-        <v>3104</v>
+        <v>3017</v>
       </c>
       <c r="C12">
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E12">
         <v>3104</v>
@@ -1208,18 +1695,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B13">
-        <v>3105</v>
+        <v>3018</v>
       </c>
       <c r="C13">
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E13">
         <v>3105</v>
@@ -1231,18 +1718,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B14">
-        <v>3106</v>
+        <v>3019</v>
       </c>
       <c r="C14">
         <v>13</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>3106</v>
@@ -1254,18 +1741,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B15">
-        <v>3107</v>
+        <v>3020</v>
       </c>
       <c r="C15">
         <v>11</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E15">
         <v>3107</v>
@@ -1277,18 +1764,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B16">
-        <v>3108</v>
+        <v>3021</v>
       </c>
       <c r="C16">
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E16">
         <v>3108</v>
@@ -1300,18 +1787,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B17">
-        <v>3109</v>
+        <v>3022</v>
       </c>
       <c r="C17">
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E17">
         <v>3109</v>
@@ -1323,18 +1810,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B18">
-        <v>3110</v>
+        <v>3023</v>
       </c>
       <c r="C18">
         <v>13</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E18">
         <v>3110</v>
@@ -1346,18 +1833,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B19">
-        <v>3111</v>
+        <v>3024</v>
       </c>
       <c r="C19">
         <v>11</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E19">
         <v>3111</v>
@@ -1369,18 +1856,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B20">
-        <v>3112</v>
+        <v>3025</v>
       </c>
       <c r="C20">
         <v>13</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E20">
         <v>3112</v>
@@ -1392,18 +1879,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B21">
-        <v>3113</v>
+        <v>3026</v>
       </c>
       <c r="C21">
         <v>13</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E21">
         <v>3113</v>
@@ -1415,18 +1902,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B22">
-        <v>3114</v>
+        <v>3027</v>
       </c>
       <c r="C22">
         <v>13</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E22">
         <v>3114</v>
@@ -1438,18 +1925,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B23">
-        <v>3115</v>
+        <v>3028</v>
       </c>
       <c r="C23">
         <v>11</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E23">
         <v>3115</v>
@@ -1461,18 +1948,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B24">
-        <v>3116</v>
+        <v>3029</v>
       </c>
       <c r="C24">
         <v>11</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E24">
         <v>3116</v>
@@ -1484,18 +1971,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B25">
-        <v>3117</v>
+        <v>3030</v>
       </c>
       <c r="C25">
         <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E25">
         <v>3117</v>
@@ -1507,18 +1994,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B26">
-        <v>3118</v>
+        <v>3031</v>
       </c>
       <c r="C26">
         <v>12</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E26">
         <v>3118</v>
@@ -1530,18 +2017,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B27">
-        <v>3119</v>
+        <v>3032</v>
       </c>
       <c r="C27">
         <v>13</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E27">
         <v>3119</v>
@@ -1553,18 +2040,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B28">
-        <v>3120</v>
+        <v>3033</v>
       </c>
       <c r="C28">
         <v>15</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E28">
         <v>3120</v>
@@ -1576,18 +2063,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B29">
-        <v>3121</v>
+        <v>3034</v>
       </c>
       <c r="C29">
         <v>15</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E29">
         <v>3121</v>
@@ -1599,18 +2086,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B30">
-        <v>3122</v>
+        <v>3035</v>
       </c>
       <c r="C30">
         <v>15</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E30">
         <v>3122</v>
@@ -1622,18 +2109,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B31">
-        <v>3123</v>
+        <v>3036</v>
       </c>
       <c r="C31">
         <v>15</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E31">
         <v>3123</v>
@@ -1645,18 +2132,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B32">
-        <v>3124</v>
+        <v>3037</v>
       </c>
       <c r="C32">
         <v>15</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E32">
         <v>3124</v>
@@ -1668,18 +2155,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B33">
-        <v>3125</v>
+        <v>3038</v>
       </c>
       <c r="C33">
         <v>15</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E33">
         <v>3125</v>
@@ -1691,18 +2178,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B34">
-        <v>3126</v>
+        <v>3039</v>
       </c>
       <c r="C34">
         <v>15</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E34">
         <v>3126</v>
@@ -1714,18 +2201,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B35">
-        <v>3127</v>
+        <v>3040</v>
       </c>
       <c r="C35">
         <v>15</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E35">
         <v>3127</v>
@@ -1737,18 +2224,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B36">
-        <v>3128</v>
+        <v>3041</v>
       </c>
       <c r="C36">
         <v>13</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E36">
         <v>3128</v>
@@ -1760,18 +2247,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B37">
-        <v>3129</v>
+        <v>3042</v>
       </c>
       <c r="C37">
         <v>15</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E37">
         <v>3129</v>
@@ -1783,18 +2270,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B38">
-        <v>3130</v>
+        <v>3043</v>
       </c>
       <c r="C38">
         <v>14</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E38">
         <v>3130</v>
@@ -1806,18 +2293,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B39">
-        <v>3131</v>
+        <v>3044</v>
       </c>
       <c r="C39">
         <v>13</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E39">
         <v>3131</v>
@@ -1829,18 +2316,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B40">
-        <v>3132</v>
+        <v>3045</v>
       </c>
       <c r="C40">
         <v>12</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E40">
         <v>3132</v>
@@ -1852,18 +2339,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B41">
-        <v>3133</v>
+        <v>3046</v>
       </c>
       <c r="C41">
         <v>12</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E41">
         <v>3133</v>
@@ -1875,18 +2362,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B42">
-        <v>3134</v>
+        <v>3047</v>
       </c>
       <c r="C42">
         <v>13</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E42">
         <v>3134</v>
@@ -1898,18 +2385,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B43">
-        <v>3135</v>
+        <v>3048</v>
       </c>
       <c r="C43">
         <v>12</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E43">
         <v>3135</v>
@@ -1921,18 +2408,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B44">
-        <v>3136</v>
+        <v>3049</v>
       </c>
       <c r="C44">
         <v>12</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E44">
         <v>3136</v>
@@ -1944,18 +2431,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B45">
-        <v>3137</v>
+        <v>3050</v>
       </c>
       <c r="C45">
         <v>15</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E45">
         <v>3137</v>
@@ -1967,18 +2454,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B46">
-        <v>3138</v>
+        <v>3051</v>
       </c>
       <c r="C46">
         <v>15</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E46">
         <v>3138</v>
@@ -1990,18 +2477,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B47">
-        <v>3139</v>
+        <v>3052</v>
       </c>
       <c r="C47">
         <v>11</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E47">
         <v>3139</v>
@@ -2013,18 +2500,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B48">
-        <v>3140</v>
+        <v>3053</v>
       </c>
       <c r="C48">
         <v>15</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E48">
         <v>3140</v>
@@ -2036,18 +2523,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B49">
-        <v>3141</v>
+        <v>3054</v>
       </c>
       <c r="C49">
         <v>15</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E49">
         <v>3141</v>
@@ -2059,18 +2546,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B50">
-        <v>3142</v>
+        <v>3055</v>
       </c>
       <c r="C50">
         <v>14</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E50">
         <v>3142</v>
@@ -2082,18 +2569,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B51">
-        <v>3143</v>
+        <v>3056</v>
       </c>
       <c r="C51">
         <v>14</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E51">
         <v>3143</v>
@@ -2105,18 +2592,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B52">
-        <v>3144</v>
+        <v>3057</v>
       </c>
       <c r="C52">
         <v>14</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E52">
         <v>3144</v>
@@ -2128,18 +2615,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B53">
-        <v>3145</v>
+        <v>3058</v>
       </c>
       <c r="C53">
         <v>14</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E53">
         <v>3145</v>
@@ -2151,18 +2638,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B54">
-        <v>3146</v>
+        <v>3059</v>
       </c>
       <c r="C54">
         <v>14</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E54">
         <v>3146</v>
@@ -2174,18 +2661,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B55">
-        <v>3147</v>
+        <v>3060</v>
       </c>
       <c r="C55">
         <v>14</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E55">
         <v>3147</v>
@@ -2197,18 +2684,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B56">
-        <v>3148</v>
+        <v>3061</v>
       </c>
       <c r="C56">
         <v>14</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E56">
         <v>3148</v>
@@ -2220,18 +2707,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B57">
-        <v>3149</v>
+        <v>3062</v>
       </c>
       <c r="C57">
         <v>14</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E57">
         <v>3149</v>
@@ -2243,18 +2730,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B58">
-        <v>3150</v>
+        <v>3063</v>
       </c>
       <c r="C58">
         <v>13</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E58">
         <v>3150</v>
@@ -2266,18 +2753,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B59">
-        <v>3151</v>
+        <v>3064</v>
       </c>
       <c r="C59">
         <v>13</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E59">
         <v>3151</v>
@@ -2289,18 +2776,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B60">
-        <v>3152</v>
+        <v>3065</v>
       </c>
       <c r="C60">
         <v>13</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E60">
         <v>3152</v>
@@ -2312,18 +2799,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B61">
-        <v>3153</v>
+        <v>3066</v>
       </c>
       <c r="C61">
         <v>13</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E61">
         <v>3153</v>
@@ -2335,18 +2822,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B62">
-        <v>3154</v>
+        <v>3067</v>
       </c>
       <c r="C62">
         <v>13</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E62">
         <v>3154</v>
@@ -2358,18 +2845,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B63">
-        <v>3155</v>
+        <v>3068</v>
       </c>
       <c r="C63">
         <v>13</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E63">
         <v>3155</v>
@@ -2381,18 +2868,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B64">
-        <v>3156</v>
+        <v>3069</v>
       </c>
       <c r="C64">
         <v>13</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E64">
         <v>3156</v>
@@ -2404,18 +2891,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B65">
-        <v>3157</v>
+        <v>3070</v>
       </c>
       <c r="C65">
         <v>13</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E65">
         <v>3157</v>
@@ -2427,18 +2914,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B66">
-        <v>3158</v>
+        <v>3071</v>
       </c>
       <c r="C66">
         <v>13</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E66">
         <v>3158</v>
@@ -2450,18 +2937,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B67">
-        <v>3159</v>
+        <v>3072</v>
       </c>
       <c r="C67">
         <v>13</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E67">
         <v>3159</v>
@@ -2473,18 +2960,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B68">
-        <v>3160</v>
+        <v>3073</v>
       </c>
       <c r="C68">
         <v>13</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E68">
         <v>3160</v>
@@ -2496,18 +2983,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B69">
-        <v>3161</v>
+        <v>3074</v>
       </c>
       <c r="C69">
         <v>13</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E69">
         <v>3161</v>
@@ -2519,18 +3006,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B70">
-        <v>3162</v>
+        <v>3075</v>
       </c>
       <c r="C70">
         <v>13</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E70">
         <v>3162</v>
@@ -2542,18 +3029,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B71">
-        <v>3163</v>
+        <v>3076</v>
       </c>
       <c r="C71">
         <v>13</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E71">
         <v>3163</v>
@@ -2565,18 +3052,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B72">
-        <v>3164</v>
+        <v>3077</v>
       </c>
       <c r="C72">
         <v>13</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E72">
         <v>3164</v>
@@ -2588,18 +3075,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B73">
-        <v>3165</v>
+        <v>3078</v>
       </c>
       <c r="C73">
         <v>13</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E73">
         <v>3165</v>
@@ -2611,18 +3098,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B74">
-        <v>3166</v>
+        <v>3079</v>
       </c>
       <c r="C74">
         <v>12</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E74">
         <v>3166</v>
@@ -2634,18 +3121,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B75">
-        <v>3167</v>
+        <v>3080</v>
       </c>
       <c r="C75">
         <v>12</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E75">
         <v>3167</v>
@@ -2657,18 +3144,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B76">
-        <v>3168</v>
+        <v>3081</v>
       </c>
       <c r="C76">
         <v>11</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E76">
         <v>3168</v>
@@ -2680,18 +3167,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B77">
-        <v>3169</v>
+        <v>3082</v>
       </c>
       <c r="C77">
         <v>12</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E77">
         <v>3169</v>
@@ -2703,18 +3190,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B78">
-        <v>3170</v>
+        <v>3083</v>
       </c>
       <c r="C78">
         <v>12</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E78">
         <v>3170</v>
@@ -2726,18 +3213,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B79">
-        <v>3171</v>
+        <v>3084</v>
       </c>
       <c r="C79">
         <v>11</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E79">
         <v>3171</v>
@@ -2749,18 +3236,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B80">
-        <v>3172</v>
+        <v>3085</v>
       </c>
       <c r="C80">
         <v>12</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E80">
         <v>3172</v>
@@ -2772,18 +3259,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B81">
-        <v>3173</v>
+        <v>3086</v>
       </c>
       <c r="C81">
         <v>12</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E81">
         <v>3173</v>
@@ -2795,18 +3282,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B82">
-        <v>3174</v>
+        <v>3087</v>
       </c>
       <c r="C82">
         <v>11</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E82">
         <v>3174</v>
@@ -2818,18 +3305,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B83">
-        <v>3175</v>
+        <v>3088</v>
       </c>
       <c r="C83">
         <v>11</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E83">
         <v>3175</v>
@@ -2841,18 +3328,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B84">
-        <v>3176</v>
+        <v>3089</v>
       </c>
       <c r="C84">
         <v>12</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E84">
         <v>3176</v>
@@ -2864,18 +3351,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B85">
-        <v>3177</v>
+        <v>3090</v>
       </c>
       <c r="C85">
         <v>11</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E85">
         <v>3177</v>
@@ -2887,18 +3374,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B86">
-        <v>3178</v>
+        <v>3091</v>
       </c>
       <c r="C86">
         <v>11</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E86">
         <v>3178</v>
@@ -2910,9 +3397,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B87">
         <v>2000</v>
@@ -2933,9 +3420,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B88">
         <v>2001</v>
@@ -2944,7 +3431,7 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E88">
         <v>103</v>
@@ -2956,9 +3443,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B89">
         <v>2003</v>
@@ -2967,7 +3454,7 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E89">
         <v>103</v>
@@ -2979,8 +3466,1486 @@
         <v>2</v>
       </c>
     </row>
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B90">
+        <v>2010</v>
+      </c>
+      <c r="C90">
+        <v>4</v>
+      </c>
+      <c r="D90" s="2">
+        <v>283</v>
+      </c>
+      <c r="E90" s="2">
+        <v>277</v>
+      </c>
+      <c r="F90">
+        <v>2</v>
+      </c>
+      <c r="G90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B91">
+        <v>2011</v>
+      </c>
+      <c r="C91">
+        <v>4</v>
+      </c>
+      <c r="D91" s="2">
+        <v>277</v>
+      </c>
+      <c r="E91" s="2">
+        <v>204</v>
+      </c>
+      <c r="F91">
+        <v>2</v>
+      </c>
+      <c r="G91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B92">
+        <v>2012</v>
+      </c>
+      <c r="C92">
+        <v>4</v>
+      </c>
+      <c r="D92" s="2">
+        <v>203</v>
+      </c>
+      <c r="E92" s="2">
+        <v>271</v>
+      </c>
+      <c r="F92">
+        <v>2</v>
+      </c>
+      <c r="G92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B93">
+        <v>2100</v>
+      </c>
+      <c r="C93">
+        <v>2</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E93" s="2">
+        <v>4000</v>
+      </c>
+      <c r="F93">
+        <v>2</v>
+      </c>
+      <c r="G93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B94">
+        <v>2101</v>
+      </c>
+      <c r="C94">
+        <v>2</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E94" s="2">
+        <v>4001</v>
+      </c>
+      <c r="F94">
+        <v>2</v>
+      </c>
+      <c r="G94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B95">
+        <v>2102</v>
+      </c>
+      <c r="C95">
+        <v>2</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E95" s="2">
+        <v>4002</v>
+      </c>
+      <c r="F95">
+        <v>2</v>
+      </c>
+      <c r="G95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B96">
+        <v>2103</v>
+      </c>
+      <c r="C96">
+        <v>2</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E96" s="2">
+        <v>4003</v>
+      </c>
+      <c r="F96">
+        <v>2</v>
+      </c>
+      <c r="G96">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B97">
+        <v>2104</v>
+      </c>
+      <c r="C97">
+        <v>2</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E97" s="2">
+        <v>4004</v>
+      </c>
+      <c r="F97">
+        <v>2</v>
+      </c>
+      <c r="G97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B98">
+        <v>2105</v>
+      </c>
+      <c r="C98">
+        <v>2</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E98" s="2">
+        <v>4005</v>
+      </c>
+      <c r="F98">
+        <v>2</v>
+      </c>
+      <c r="G98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B99">
+        <v>2106</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E99" s="2">
+        <v>4006</v>
+      </c>
+      <c r="F99">
+        <v>2</v>
+      </c>
+      <c r="G99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B100">
+        <v>2107</v>
+      </c>
+      <c r="C100">
+        <v>2</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E100" s="2">
+        <v>4007</v>
+      </c>
+      <c r="F100">
+        <v>2</v>
+      </c>
+      <c r="G100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B101">
+        <v>2108</v>
+      </c>
+      <c r="C101">
+        <v>2</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E101" s="2">
+        <v>4008</v>
+      </c>
+      <c r="F101">
+        <v>2</v>
+      </c>
+      <c r="G101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B102">
+        <v>2109</v>
+      </c>
+      <c r="C102">
+        <v>2</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E102" s="2">
+        <v>4009</v>
+      </c>
+      <c r="F102">
+        <v>2</v>
+      </c>
+      <c r="G102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B103">
+        <v>2110</v>
+      </c>
+      <c r="C103">
+        <v>2</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E103" s="2">
+        <v>4010</v>
+      </c>
+      <c r="F103">
+        <v>2</v>
+      </c>
+      <c r="G103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B104">
+        <v>2111</v>
+      </c>
+      <c r="C104">
+        <v>2</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E104">
+        <v>11</v>
+      </c>
+      <c r="F104">
+        <v>2</v>
+      </c>
+      <c r="G104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B105">
+        <v>4000</v>
+      </c>
+      <c r="C105" s="3">
+        <v>0</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E105" s="9">
+        <v>1600</v>
+      </c>
+      <c r="F105">
+        <v>2</v>
+      </c>
+      <c r="G105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A106" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B106">
+        <v>4001</v>
+      </c>
+      <c r="C106" s="3">
+        <v>0</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E106" s="9">
+        <v>1601</v>
+      </c>
+      <c r="F106">
+        <v>2</v>
+      </c>
+      <c r="G106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A107" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B107">
+        <v>4002</v>
+      </c>
+      <c r="C107" s="3">
+        <v>0</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E107" s="9">
+        <v>1602</v>
+      </c>
+      <c r="F107">
+        <v>2</v>
+      </c>
+      <c r="G107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A108" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B108">
+        <v>4003</v>
+      </c>
+      <c r="C108" s="3">
+        <v>0</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E108" s="9">
+        <v>1603</v>
+      </c>
+      <c r="F108">
+        <v>2</v>
+      </c>
+      <c r="G108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A109" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B109">
+        <v>4004</v>
+      </c>
+      <c r="C109" s="3">
+        <v>0</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E109" s="9">
+        <v>1604</v>
+      </c>
+      <c r="F109">
+        <v>2</v>
+      </c>
+      <c r="G109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A110" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B110">
+        <v>4005</v>
+      </c>
+      <c r="C110" s="3">
+        <v>0</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E110" s="9">
+        <v>1605</v>
+      </c>
+      <c r="F110">
+        <v>2</v>
+      </c>
+      <c r="G110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A111" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B111">
+        <v>4006</v>
+      </c>
+      <c r="C111" s="3">
+        <v>0</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E111" s="9">
+        <v>1606</v>
+      </c>
+      <c r="F111">
+        <v>2</v>
+      </c>
+      <c r="G111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A112" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B112">
+        <v>4007</v>
+      </c>
+      <c r="C112" s="3">
+        <v>0</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E112" s="9">
+        <v>1607</v>
+      </c>
+      <c r="F112">
+        <v>2</v>
+      </c>
+      <c r="G112">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A113" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B113">
+        <v>4008</v>
+      </c>
+      <c r="C113" s="3">
+        <v>0</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E113" s="9">
+        <v>1608</v>
+      </c>
+      <c r="F113">
+        <v>2</v>
+      </c>
+      <c r="G113">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A114" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B114">
+        <v>4009</v>
+      </c>
+      <c r="C114" s="3">
+        <v>0</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E114" s="9">
+        <v>1609</v>
+      </c>
+      <c r="F114">
+        <v>2</v>
+      </c>
+      <c r="G114">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A115" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B115">
+        <v>4010</v>
+      </c>
+      <c r="C115" s="3">
+        <v>0</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="E115" s="9">
+        <v>1610</v>
+      </c>
+      <c r="F115">
+        <v>2</v>
+      </c>
+      <c r="G115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A116" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B116">
+        <v>4011</v>
+      </c>
+      <c r="C116" s="3">
+        <v>0</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E116" s="9">
+        <v>1611</v>
+      </c>
+      <c r="F116">
+        <v>2</v>
+      </c>
+      <c r="G116">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A117" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B117">
+        <v>4012</v>
+      </c>
+      <c r="C117" s="3">
+        <v>0</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E117" s="9">
+        <v>1612</v>
+      </c>
+      <c r="F117">
+        <v>2</v>
+      </c>
+      <c r="G117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A118" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B118">
+        <v>4013</v>
+      </c>
+      <c r="C118" s="3">
+        <v>0</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E118" s="9">
+        <v>1613</v>
+      </c>
+      <c r="F118">
+        <v>2</v>
+      </c>
+      <c r="G118">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A119" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B119">
+        <v>4014</v>
+      </c>
+      <c r="C119" s="3">
+        <v>0</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E119" s="9">
+        <v>1614</v>
+      </c>
+      <c r="F119">
+        <v>2</v>
+      </c>
+      <c r="G119">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B120">
+        <v>4015</v>
+      </c>
+      <c r="C120" s="3">
+        <v>1</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E120" s="9">
+        <v>1615</v>
+      </c>
+      <c r="F120">
+        <v>2</v>
+      </c>
+      <c r="G120">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B121">
+        <v>4016</v>
+      </c>
+      <c r="C121" s="3">
+        <v>1</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E121" s="9">
+        <v>1616</v>
+      </c>
+      <c r="F121">
+        <v>2</v>
+      </c>
+      <c r="G121">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B122">
+        <v>4017</v>
+      </c>
+      <c r="C122" s="3">
+        <v>1</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E122" s="9">
+        <v>1617</v>
+      </c>
+      <c r="F122">
+        <v>2</v>
+      </c>
+      <c r="G122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B123">
+        <v>4018</v>
+      </c>
+      <c r="C123" s="3">
+        <v>1</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="E123" s="9">
+        <v>1618</v>
+      </c>
+      <c r="F123">
+        <v>2</v>
+      </c>
+      <c r="G123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A124" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B124">
+        <v>4019</v>
+      </c>
+      <c r="C124" s="3">
+        <v>0</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E124" s="9">
+        <v>1619</v>
+      </c>
+      <c r="F124">
+        <v>2</v>
+      </c>
+      <c r="G124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A125" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B125">
+        <v>4020</v>
+      </c>
+      <c r="C125" s="3">
+        <v>0</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E125" s="9">
+        <v>1620</v>
+      </c>
+      <c r="F125">
+        <v>2</v>
+      </c>
+      <c r="G125">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B126">
+        <v>4021</v>
+      </c>
+      <c r="C126" s="3">
+        <v>1</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E126" s="9">
+        <v>1650</v>
+      </c>
+      <c r="F126">
+        <v>2</v>
+      </c>
+      <c r="G126">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B127">
+        <v>4022</v>
+      </c>
+      <c r="C127" s="3">
+        <v>1</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E127" s="9">
+        <v>1651</v>
+      </c>
+      <c r="F127">
+        <v>2</v>
+      </c>
+      <c r="G127">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B128">
+        <v>4023</v>
+      </c>
+      <c r="C128" s="3">
+        <v>1</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E128" s="9">
+        <v>1652</v>
+      </c>
+      <c r="F128">
+        <v>2</v>
+      </c>
+      <c r="G128">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B129">
+        <v>4024</v>
+      </c>
+      <c r="C129" s="3">
+        <v>1</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E129" s="9">
+        <v>1653</v>
+      </c>
+      <c r="F129">
+        <v>2</v>
+      </c>
+      <c r="G129">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B130">
+        <v>4025</v>
+      </c>
+      <c r="C130" s="3">
+        <v>0</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E130" s="9">
+        <v>1654</v>
+      </c>
+      <c r="F130">
+        <v>2</v>
+      </c>
+      <c r="G130">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="B131">
+        <v>4026</v>
+      </c>
+      <c r="C131" s="3">
+        <v>0</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E131" s="9">
+        <v>1655</v>
+      </c>
+      <c r="F131">
+        <v>2</v>
+      </c>
+      <c r="G131">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B132">
+        <v>4027</v>
+      </c>
+      <c r="C132" s="3">
+        <v>0</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E132" s="9">
+        <v>1656</v>
+      </c>
+      <c r="F132">
+        <v>2</v>
+      </c>
+      <c r="G132">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B133">
+        <v>4028</v>
+      </c>
+      <c r="C133" s="3">
+        <v>1</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E133" s="9">
+        <v>1657</v>
+      </c>
+      <c r="F133">
+        <v>2</v>
+      </c>
+      <c r="G133">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B134">
+        <v>4029</v>
+      </c>
+      <c r="C134" s="3">
+        <v>1</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E134" s="9">
+        <v>1658</v>
+      </c>
+      <c r="F134">
+        <v>2</v>
+      </c>
+      <c r="G134">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="B135">
+        <v>4030</v>
+      </c>
+      <c r="C135" s="3">
+        <v>1</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E135" s="9">
+        <v>1659</v>
+      </c>
+      <c r="F135">
+        <v>2</v>
+      </c>
+      <c r="G135">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="B136">
+        <v>4031</v>
+      </c>
+      <c r="C136" s="3">
+        <v>1</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E136" s="9">
+        <v>1660</v>
+      </c>
+      <c r="F136">
+        <v>2</v>
+      </c>
+      <c r="G136">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B137">
+        <v>4032</v>
+      </c>
+      <c r="C137" s="3">
+        <v>1</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E137" s="9">
+        <v>1661</v>
+      </c>
+      <c r="F137">
+        <v>2</v>
+      </c>
+      <c r="G137">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B138">
+        <v>4033</v>
+      </c>
+      <c r="C138" s="3">
+        <v>0</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E138" s="9">
+        <v>1662</v>
+      </c>
+      <c r="F138">
+        <v>2</v>
+      </c>
+      <c r="G138">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="B139">
+        <v>4034</v>
+      </c>
+      <c r="C139" s="3">
+        <v>1</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E139" s="9">
+        <v>1663</v>
+      </c>
+      <c r="F139">
+        <v>2</v>
+      </c>
+      <c r="G139">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B140">
+        <v>4035</v>
+      </c>
+      <c r="C140" s="3">
+        <v>1</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E140" s="9">
+        <v>1664</v>
+      </c>
+      <c r="F140">
+        <v>2</v>
+      </c>
+      <c r="G140">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B141">
+        <v>4036</v>
+      </c>
+      <c r="C141" s="3">
+        <v>1</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E141" s="9">
+        <v>1665</v>
+      </c>
+      <c r="F141">
+        <v>2</v>
+      </c>
+      <c r="G141">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B142">
+        <v>4037</v>
+      </c>
+      <c r="C142" s="3">
+        <v>1</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E142" s="9">
+        <v>1666</v>
+      </c>
+      <c r="F142">
+        <v>2</v>
+      </c>
+      <c r="G142">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="B143">
+        <v>4038</v>
+      </c>
+      <c r="C143" s="3">
+        <v>1</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E143" s="9">
+        <v>1700</v>
+      </c>
+      <c r="F143">
+        <v>2</v>
+      </c>
+      <c r="G143">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B144">
+        <v>4039</v>
+      </c>
+      <c r="C144" s="3">
+        <v>1</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E144" s="9">
+        <v>1701</v>
+      </c>
+      <c r="F144">
+        <v>2</v>
+      </c>
+      <c r="G144">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B145">
+        <v>4040</v>
+      </c>
+      <c r="C145" s="3">
+        <v>0</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="E145" s="9">
+        <v>1702</v>
+      </c>
+      <c r="F145">
+        <v>2</v>
+      </c>
+      <c r="G145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="B146">
+        <v>4041</v>
+      </c>
+      <c r="C146" s="3">
+        <v>1</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E146" s="9">
+        <v>1703</v>
+      </c>
+      <c r="F146">
+        <v>2</v>
+      </c>
+      <c r="G146">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B147">
+        <v>4042</v>
+      </c>
+      <c r="C147" s="3">
+        <v>1</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E147" s="9">
+        <v>1704</v>
+      </c>
+      <c r="F147">
+        <v>2</v>
+      </c>
+      <c r="G147">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="B148">
+        <v>4043</v>
+      </c>
+      <c r="C148" s="3">
+        <v>1</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E148" s="9">
+        <v>1705</v>
+      </c>
+      <c r="F148">
+        <v>2</v>
+      </c>
+      <c r="G148">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="B149">
+        <v>4044</v>
+      </c>
+      <c r="C149" s="3">
+        <v>1</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="E149" s="9">
+        <v>1706</v>
+      </c>
+      <c r="F149">
+        <v>2</v>
+      </c>
+      <c r="G149">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="B150">
+        <v>4045</v>
+      </c>
+      <c r="C150" s="3">
+        <v>0</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E150" s="9">
+        <v>1707</v>
+      </c>
+      <c r="F150">
+        <v>2</v>
+      </c>
+      <c r="G150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B151">
+        <v>4046</v>
+      </c>
+      <c r="C151" s="3">
+        <v>1</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E151" s="9">
+        <v>1708</v>
+      </c>
+      <c r="F151">
+        <v>2</v>
+      </c>
+      <c r="G151">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B152">
+        <v>4047</v>
+      </c>
+      <c r="C152" s="3">
+        <v>1</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E152" s="9">
+        <v>1709</v>
+      </c>
+      <c r="F152">
+        <v>2</v>
+      </c>
+      <c r="G152">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="B153">
+        <v>4048</v>
+      </c>
+      <c r="C153" s="3">
+        <v>1</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E153" s="9">
+        <v>1710</v>
+      </c>
+      <c r="F153">
+        <v>2</v>
+      </c>
+      <c r="G153">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:G86"/>
+  <autoFilter ref="A3:G153">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -2989,4 +4954,374 @@
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A4:C64"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>4000</v>
+      </c>
+      <c r="C4" t="str">
+        <f>B4&amp;","&amp;0</f>
+        <v>4000,0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>4001</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" ref="C5:C26" si="0">C4&amp;"|"&amp;B5&amp;","&amp;0</f>
+        <v>4000,0|4001,0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>4002</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B7">
+        <v>4003</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>4004</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0|4004,0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>4005</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B10">
+        <v>4006</v>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>4007</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>4008</v>
+      </c>
+      <c r="C12" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B13">
+        <v>4009</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0|4009,0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B14">
+        <v>4010</v>
+      </c>
+      <c r="C14" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0|4009,0|4010,0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B15">
+        <v>4011</v>
+      </c>
+      <c r="C15" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0|4009,0|4010,0|4011,0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <v>4012</v>
+      </c>
+      <c r="C16" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0|4009,0|4010,0|4011,0|4012,0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B17">
+        <v>4013</v>
+      </c>
+      <c r="C17" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0|4009,0|4010,0|4011,0|4012,0|4013,0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B18">
+        <v>4014</v>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0|4009,0|4010,0|4011,0|4012,0|4013,0|4014,0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B19">
+        <v>4019</v>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0|4009,0|4010,0|4011,0|4012,0|4013,0|4014,0|4019,0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>4020</v>
+      </c>
+      <c r="C20" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0|4009,0|4010,0|4011,0|4012,0|4013,0|4014,0|4019,0|4020,0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>4025</v>
+      </c>
+      <c r="C21" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0|4009,0|4010,0|4011,0|4012,0|4013,0|4014,0|4019,0|4020,0|4025,0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>4026</v>
+      </c>
+      <c r="C22" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0|4009,0|4010,0|4011,0|4012,0|4013,0|4014,0|4019,0|4020,0|4025,0|4026,0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <v>4027</v>
+      </c>
+      <c r="C23" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0|4009,0|4010,0|4011,0|4012,0|4013,0|4014,0|4019,0|4020,0|4025,0|4026,0|4027,0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B24">
+        <v>4033</v>
+      </c>
+      <c r="C24" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0|4009,0|4010,0|4011,0|4012,0|4013,0|4014,0|4019,0|4020,0|4025,0|4026,0|4027,0|4033,0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B25">
+        <v>4040</v>
+      </c>
+      <c r="C25" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0|4009,0|4010,0|4011,0|4012,0|4013,0|4014,0|4019,0|4020,0|4025,0|4026,0|4027,0|4033,0|4040,0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B26">
+        <v>4045</v>
+      </c>
+      <c r="C26" t="str">
+        <f t="shared" si="0"/>
+        <v>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0|4009,0|4010,0|4011,0|4012,0|4013,0|4014,0|4019,0|4020,0|4025,0|4026,0|4027,0|4033,0|4040,0|4045,0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="5"/>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="5"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="5"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="5"/>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="5"/>
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="5"/>
+      <c r="C32" s="3"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="5"/>
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="5"/>
+      <c r="C34" s="3"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="7"/>
+      <c r="C35" s="3"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="7"/>
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="6"/>
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="6"/>
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="6"/>
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="6"/>
+      <c r="C40" s="3"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="6"/>
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="6"/>
+      <c r="C42" s="3"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="6"/>
+      <c r="C43" s="3"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="6"/>
+      <c r="C44" s="3"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="6"/>
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="6"/>
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="6"/>
+      <c r="C47" s="3"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="6"/>
+      <c r="C48" s="3"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="6"/>
+      <c r="C49" s="3"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="6"/>
+      <c r="C50" s="3"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="6"/>
+      <c r="C51" s="3"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="6"/>
+      <c r="C52" s="3"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="8"/>
+      <c r="C53" s="3"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="8"/>
+      <c r="C54" s="3"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="8"/>
+      <c r="C55" s="3"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="8"/>
+      <c r="C56" s="3"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="8"/>
+      <c r="C57" s="3"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="8"/>
+      <c r="C58" s="3"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="8"/>
+      <c r="C59" s="3"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="8"/>
+      <c r="C60" s="3"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="8"/>
+      <c r="C61" s="3"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="8"/>
+      <c r="C62" s="3"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="8"/>
+      <c r="C63" s="3"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="8"/>
+      <c r="C64" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Datas/FormulaData.xlsx
+++ b/Datas/FormulaData.xlsx
@@ -39,7 +39,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>铸造 = 0,缝纫 = 1,书写=2, 劈砍=3,加工=4，粉磨 = 10, 徒手 = 11,蒸煮 = 12,烘烤 = 13,酿造 = 14,搅拌=15</t>
+          <t>铸造 = 0,缝纫 = 1,书写=2, 劈砍=3,纺线=4，织布=5，制革=6，粉磨 = 10, 徒手 = 11,蒸煮 = 12,烘烤 = 13,酿造 = 14,搅拌=15</t>
         </r>
         <r>
           <rPr>
@@ -1432,7 +1432,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A2:G153"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1488,7 +1487,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1511,7 +1510,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1534,7 +1533,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>178</v>
       </c>
@@ -1557,7 +1556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1580,7 +1579,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1603,7 +1602,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1626,7 +1625,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1649,7 +1648,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1672,7 +1671,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -1695,7 +1694,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1718,7 +1717,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1741,7 +1740,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -1764,7 +1763,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -1787,7 +1786,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -1810,7 +1809,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1833,7 +1832,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1856,7 +1855,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1879,7 +1878,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -1902,7 +1901,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -1925,7 +1924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -1948,7 +1947,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -1971,7 +1970,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -1994,7 +1993,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -2017,7 +2016,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -2040,7 +2039,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -2063,7 +2062,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -2086,7 +2085,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -2109,7 +2108,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -2132,7 +2131,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -2155,7 +2154,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -2178,7 +2177,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -2201,7 +2200,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -2224,7 +2223,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -2247,7 +2246,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -2270,7 +2269,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -2293,7 +2292,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -2316,7 +2315,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -2339,7 +2338,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -2362,7 +2361,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -2385,7 +2384,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -2408,7 +2407,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -2431,7 +2430,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -2454,7 +2453,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -2477,7 +2476,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -2500,7 +2499,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -2523,7 +2522,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -2546,7 +2545,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -2569,7 +2568,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>56</v>
       </c>
@@ -2592,7 +2591,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>57</v>
       </c>
@@ -2615,7 +2614,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>58</v>
       </c>
@@ -2638,7 +2637,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>59</v>
       </c>
@@ -2661,7 +2660,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>60</v>
       </c>
@@ -2684,7 +2683,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -2707,7 +2706,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>62</v>
       </c>
@@ -2730,7 +2729,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>63</v>
       </c>
@@ -2753,7 +2752,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -2776,7 +2775,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>65</v>
       </c>
@@ -2799,7 +2798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -2822,7 +2821,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>67</v>
       </c>
@@ -2845,7 +2844,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>68</v>
       </c>
@@ -2868,7 +2867,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>69</v>
       </c>
@@ -2891,7 +2890,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>70</v>
       </c>
@@ -2914,7 +2913,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>71</v>
       </c>
@@ -2937,7 +2936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>72</v>
       </c>
@@ -2960,7 +2959,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>73</v>
       </c>
@@ -2983,7 +2982,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>74</v>
       </c>
@@ -3006,7 +3005,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>75</v>
       </c>
@@ -3029,7 +3028,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>76</v>
       </c>
@@ -3052,7 +3051,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>77</v>
       </c>
@@ -3075,7 +3074,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>78</v>
       </c>
@@ -3098,7 +3097,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>79</v>
       </c>
@@ -3121,7 +3120,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>80</v>
       </c>
@@ -3144,7 +3143,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>81</v>
       </c>
@@ -3167,7 +3166,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>82</v>
       </c>
@@ -3190,7 +3189,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>83</v>
       </c>
@@ -3213,7 +3212,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>84</v>
       </c>
@@ -3236,7 +3235,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>85</v>
       </c>
@@ -3259,7 +3258,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>86</v>
       </c>
@@ -3282,7 +3281,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>87</v>
       </c>
@@ -3305,7 +3304,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>88</v>
       </c>
@@ -3328,7 +3327,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>89</v>
       </c>
@@ -3351,7 +3350,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>90</v>
       </c>
@@ -3374,7 +3373,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>91</v>
       </c>
@@ -3397,7 +3396,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>174</v>
       </c>
@@ -3420,7 +3419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>175</v>
       </c>
@@ -3443,7 +3442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>175</v>
       </c>
@@ -3466,7 +3465,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
         <v>180</v>
       </c>
@@ -3489,7 +3488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
         <v>181</v>
       </c>
@@ -3497,7 +3496,7 @@
         <v>2011</v>
       </c>
       <c r="C91">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D91" s="2">
         <v>277</v>
@@ -3512,7 +3511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
         <v>182</v>
       </c>
@@ -3520,7 +3519,7 @@
         <v>2012</v>
       </c>
       <c r="C92">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D92" s="2">
         <v>203</v>
@@ -3535,7 +3534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>183</v>
       </c>
@@ -3558,7 +3557,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>184</v>
       </c>
@@ -3581,7 +3580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>185</v>
       </c>
@@ -3604,7 +3603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>186</v>
       </c>
@@ -3627,7 +3626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>187</v>
       </c>
@@ -3650,7 +3649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>188</v>
       </c>
@@ -3673,7 +3672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>189</v>
       </c>
@@ -3696,7 +3695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>190</v>
       </c>
@@ -3719,7 +3718,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>191</v>
       </c>
@@ -3742,7 +3741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
         <v>192</v>
       </c>
@@ -3765,7 +3764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>193</v>
       </c>
@@ -3788,7 +3787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
         <v>303</v>
       </c>
@@ -4156,7 +4155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
         <v>220</v>
       </c>
@@ -4179,7 +4178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
         <v>221</v>
       </c>
@@ -4202,7 +4201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
         <v>222</v>
       </c>
@@ -4225,7 +4224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
         <v>223</v>
       </c>
@@ -4294,7 +4293,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="6" t="s">
         <v>226</v>
       </c>
@@ -4317,7 +4316,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="6" t="s">
         <v>227</v>
       </c>
@@ -4340,7 +4339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
         <v>228</v>
       </c>
@@ -4363,7 +4362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="6" t="s">
         <v>229</v>
       </c>
@@ -4455,7 +4454,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="6" t="s">
         <v>233</v>
       </c>
@@ -4478,7 +4477,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="6" t="s">
         <v>234</v>
       </c>
@@ -4501,7 +4500,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="6" t="s">
         <v>235</v>
       </c>
@@ -4524,7 +4523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="6" t="s">
         <v>236</v>
       </c>
@@ -4547,7 +4546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="6" t="s">
         <v>237</v>
       </c>
@@ -4593,7 +4592,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="6" t="s">
         <v>239</v>
       </c>
@@ -4616,7 +4615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="6" t="s">
         <v>240</v>
       </c>
@@ -4639,7 +4638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="6" t="s">
         <v>241</v>
       </c>
@@ -4662,7 +4661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="8" t="s">
         <v>242</v>
       </c>
@@ -4685,7 +4684,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
         <v>243</v>
       </c>
@@ -4708,7 +4707,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
         <v>244</v>
       </c>
@@ -4754,7 +4753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
         <v>246</v>
       </c>
@@ -4777,7 +4776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
         <v>247</v>
       </c>
@@ -4800,7 +4799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
         <v>248</v>
       </c>
@@ -4823,7 +4822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
         <v>249</v>
       </c>
@@ -4869,7 +4868,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
         <v>251</v>
       </c>
@@ -4892,7 +4891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
         <v>252</v>
       </c>
@@ -4915,7 +4914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
         <v>253</v>
       </c>
@@ -4939,13 +4938,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G153">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="0"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A3:G153"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/Datas/FormulaData.xlsx
+++ b/Datas/FormulaData.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="323">
   <si>
     <t>formulaName</t>
   </si>
@@ -796,253 +796,307 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>红莲之铠</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁龟铠</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>华丽背心</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>鳞铠</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>暗之袍</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>疾风背心</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法铠甲</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>钢刃锁甲</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>丝织长袍</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>水之羽衣</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>贵族长裙</t>
+  </si>
+  <si>
+    <t>幸运之衣</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>布鞋</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>皮鞋</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>登山者之靴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>运动鞋</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>贵族长靴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>武道鞋</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>骑士护胫</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>贤者之履</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>风神之履</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>踏浪长靴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1600,229,205,284</t>
+  </si>
+  <si>
+    <t>1600,218,299,212</t>
+  </si>
+  <si>
+    <t>1600,260,261,253</t>
+  </si>
+  <si>
+    <t>1605,259,237,239</t>
+  </si>
+  <si>
+    <t>1605,227,240,232</t>
+  </si>
+  <si>
+    <t>237,274,256,285</t>
+  </si>
+  <si>
+    <t>269,1605,264,208</t>
+  </si>
+  <si>
+    <t>1609,259,258,263</t>
+  </si>
+  <si>
+    <t>1609,253,260,267</t>
+  </si>
+  <si>
+    <t>270,225,239,1614</t>
+  </si>
+  <si>
+    <t>245,255,268,1615</t>
+  </si>
+  <si>
+    <t>1654,250,229,286</t>
+  </si>
+  <si>
+    <t>264,277,255,246</t>
+  </si>
+  <si>
+    <t>1651,242,247,241</t>
+  </si>
+  <si>
+    <t>1654,274,299,218</t>
+  </si>
+  <si>
+    <t>1656,279,234,247</t>
+  </si>
+  <si>
+    <t>248,1650,245,285</t>
+  </si>
+  <si>
+    <t>1701,234,223,279</t>
+  </si>
+  <si>
+    <t>1700,280,232,272</t>
+  </si>
+  <si>
+    <t>1702,275,240,299</t>
+  </si>
+  <si>
+    <t>1700,281,251,282</t>
+  </si>
+  <si>
+    <t>224,1704,264,258</t>
+  </si>
+  <si>
+    <t>1703,282,232,267</t>
+  </si>
+  <si>
+    <t>298,274</t>
+  </si>
+  <si>
+    <t>1600,220,257</t>
+  </si>
+  <si>
+    <t>1605,275,299</t>
+  </si>
+  <si>
+    <t>299,274,241</t>
+  </si>
+  <si>
+    <t>1609,254,211</t>
+  </si>
+  <si>
+    <t>238,276,214</t>
+  </si>
+  <si>
+    <t>221,276,214</t>
+  </si>
+  <si>
+    <t>1613,213,246</t>
+  </si>
+  <si>
+    <t>1612,211,1612</t>
+  </si>
+  <si>
+    <t>204,277</t>
+  </si>
+  <si>
+    <t>271,278,214</t>
+  </si>
+  <si>
+    <t>1651,227,299</t>
+  </si>
+  <si>
+    <t>298,205</t>
+  </si>
+  <si>
+    <t>202,1654,210</t>
+  </si>
+  <si>
+    <t>272,228,277</t>
+  </si>
+  <si>
+    <t>273,278,271</t>
+  </si>
+  <si>
+    <t>1650,208,224</t>
+  </si>
+  <si>
+    <t>204,214,228</t>
+  </si>
+  <si>
+    <t>1650,232,282</t>
+  </si>
+  <si>
+    <t>271,222,278</t>
+  </si>
+  <si>
+    <t>298,210,202</t>
+  </si>
+  <si>
+    <t>1701,273,238</t>
+  </si>
+  <si>
+    <t>传送卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>224,269,291</t>
+  </si>
+  <si>
+    <t>士兵长靴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>铁铠甲</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>红莲之铠</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁龟铠</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>华丽背心</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>鳞铠</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>暗之袍</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>疾风背心</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>魔法铠甲</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>钢刃锁甲</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>丝织长袍</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>水之羽衣</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>贵族长裙</t>
-  </si>
-  <si>
-    <t>幸运之衣</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>布鞋</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>皮鞋</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>士兵长靴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>登山者之靴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>运动鞋</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>贵族长靴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>武道鞋</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>骑士护胫</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>贤者之履</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>风神之履</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>踏浪长靴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>1600,229,205,284</t>
-  </si>
-  <si>
-    <t>1600,218,299,212</t>
-  </si>
-  <si>
-    <t>1600,260,261,253</t>
-  </si>
-  <si>
-    <t>1605,259,237,239</t>
-  </si>
-  <si>
-    <t>1605,227,240,232</t>
-  </si>
-  <si>
-    <t>237,274,256,285</t>
-  </si>
-  <si>
-    <t>269,1605,264,208</t>
-  </si>
-  <si>
-    <t>1609,259,258,263</t>
-  </si>
-  <si>
-    <t>1609,253,260,267</t>
-  </si>
-  <si>
-    <t>270,225,239,1614</t>
-  </si>
-  <si>
-    <t>245,255,268,1615</t>
-  </si>
-  <si>
-    <t>1654,250,229,286</t>
-  </si>
-  <si>
-    <t>264,277,255,246</t>
-  </si>
-  <si>
-    <t>1651,242,247,241</t>
-  </si>
-  <si>
-    <t>1654,274,299,218</t>
-  </si>
-  <si>
-    <t>1656,279,234,247</t>
-  </si>
-  <si>
-    <t>248,1650,245,285</t>
-  </si>
-  <si>
-    <t>1701,234,223,279</t>
-  </si>
-  <si>
-    <t>1700,280,232,272</t>
-  </si>
-  <si>
-    <t>1702,275,240,299</t>
-  </si>
-  <si>
-    <t>1700,281,251,282</t>
-  </si>
-  <si>
-    <t>224,1704,264,258</t>
-  </si>
-  <si>
-    <t>1703,282,232,267</t>
-  </si>
-  <si>
-    <t>298,274</t>
-  </si>
-  <si>
-    <t>1600,220,257</t>
-  </si>
-  <si>
-    <t>104,298,274</t>
-  </si>
-  <si>
-    <t>1605,275,299</t>
-  </si>
-  <si>
-    <t>299,274,241</t>
-  </si>
-  <si>
-    <t>1609,254,211</t>
-  </si>
-  <si>
-    <t>238,276,214</t>
-  </si>
-  <si>
-    <t>221,276,214</t>
-  </si>
-  <si>
-    <t>1613,213,246</t>
-  </si>
-  <si>
-    <t>1612,211,1612</t>
-  </si>
-  <si>
-    <t>204,277</t>
-  </si>
-  <si>
-    <t>271,278,214</t>
-  </si>
-  <si>
-    <t>1651,227,299</t>
-  </si>
-  <si>
-    <t>1651,223,283</t>
-  </si>
-  <si>
-    <t>298,205</t>
-  </si>
-  <si>
-    <t>202,1654,210</t>
-  </si>
-  <si>
-    <t>272,228,277</t>
-  </si>
-  <si>
-    <t>273,278,271</t>
-  </si>
-  <si>
-    <t>1650,208,224</t>
-  </si>
-  <si>
-    <t>204,214,228</t>
-  </si>
-  <si>
-    <t>1650,232,282</t>
-  </si>
-  <si>
-    <t>204,222,278</t>
-  </si>
-  <si>
-    <t>271,222,278</t>
-  </si>
-  <si>
-    <t>298,210,202</t>
-  </si>
-  <si>
-    <t>1701,273,238</t>
-  </si>
-  <si>
-    <t>1700,208,214</t>
-  </si>
-  <si>
-    <t>传送卷轴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>224,269,291</t>
+    <t>104,222,274</t>
+  </si>
+  <si>
+    <t>1651,223,301</t>
+  </si>
+  <si>
+    <t>204,302,278</t>
+  </si>
+  <si>
+    <t>1700,301,214</t>
+  </si>
+  <si>
+    <t>草帽</t>
+  </si>
+  <si>
+    <t>暮光草帽</t>
+  </si>
+  <si>
+    <t>法师帽</t>
+  </si>
+  <si>
+    <t>士兵头盔</t>
+  </si>
+  <si>
+    <t>尖角头盔</t>
+  </si>
+  <si>
+    <t>幸运头巾</t>
+  </si>
+  <si>
+    <t>绅士礼帽</t>
+  </si>
+  <si>
+    <t>贵族头巾</t>
+  </si>
+  <si>
+    <t>战争头盔</t>
+  </si>
+  <si>
+    <t>105,204</t>
+  </si>
+  <si>
+    <t>1800,285</t>
+  </si>
+  <si>
+    <t>204,286,256</t>
+  </si>
+  <si>
+    <t>298,271</t>
+  </si>
+  <si>
+    <t>1803,241,213</t>
+  </si>
+  <si>
+    <t>272,248,224</t>
+  </si>
+  <si>
+    <t>272,228,251</t>
+  </si>
+  <si>
+    <t>272,279,234</t>
+  </si>
+  <si>
+    <t>1804,288,247</t>
   </si>
 </sst>
 </file>
@@ -1432,13 +1486,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G153"/>
+  <dimension ref="A2:G162"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="13" style="1" customWidth="1"/>
     <col min="5" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -3789,7 +3844,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B104">
         <v>2111</v>
@@ -3798,7 +3853,7 @@
         <v>2</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E104">
         <v>11</v>
@@ -3821,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E105" s="9">
         <v>1600</v>
@@ -3844,7 +3899,7 @@
         <v>0</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E106" s="9">
         <v>1601</v>
@@ -3867,7 +3922,7 @@
         <v>0</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E107" s="9">
         <v>1602</v>
@@ -3890,7 +3945,7 @@
         <v>0</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E108" s="9">
         <v>1603</v>
@@ -3913,7 +3968,7 @@
         <v>0</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E109" s="9">
         <v>1604</v>
@@ -3936,7 +3991,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="E110" s="9">
         <v>1605</v>
@@ -3959,7 +4014,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E111" s="9">
         <v>1606</v>
@@ -3982,7 +4037,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E112" s="9">
         <v>1607</v>
@@ -4005,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E113" s="9">
         <v>1608</v>
@@ -4028,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E114" s="9">
         <v>1609</v>
@@ -4051,7 +4106,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E115" s="9">
         <v>1610</v>
@@ -4074,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E116" s="9">
         <v>1611</v>
@@ -4097,7 +4152,7 @@
         <v>0</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E117" s="9">
         <v>1612</v>
@@ -4120,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E118" s="9">
         <v>1613</v>
@@ -4143,7 +4198,7 @@
         <v>0</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E119" s="9">
         <v>1614</v>
@@ -4166,7 +4221,7 @@
         <v>1</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E120" s="9">
         <v>1615</v>
@@ -4189,7 +4244,7 @@
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E121" s="9">
         <v>1616</v>
@@ -4212,7 +4267,7 @@
         <v>1</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E122" s="9">
         <v>1617</v>
@@ -4235,7 +4290,7 @@
         <v>1</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E123" s="9">
         <v>1618</v>
@@ -4258,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E124" s="9">
         <v>1619</v>
@@ -4281,7 +4336,7 @@
         <v>0</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E125" s="9">
         <v>1620</v>
@@ -4304,7 +4359,7 @@
         <v>1</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E126" s="9">
         <v>1650</v>
@@ -4327,7 +4382,7 @@
         <v>1</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E127" s="9">
         <v>1651</v>
@@ -4350,7 +4405,7 @@
         <v>1</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E128" s="9">
         <v>1652</v>
@@ -4373,7 +4428,7 @@
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="E129" s="9">
         <v>1653</v>
@@ -4387,7 +4442,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="6" t="s">
-        <v>230</v>
+        <v>300</v>
       </c>
       <c r="B130">
         <v>4025</v>
@@ -4396,7 +4451,7 @@
         <v>0</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E130" s="9">
         <v>1654</v>
@@ -4410,7 +4465,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B131">
         <v>4026</v>
@@ -4419,7 +4474,7 @@
         <v>0</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E131" s="9">
         <v>1655</v>
@@ -4433,7 +4488,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B132">
         <v>4027</v>
@@ -4442,7 +4497,7 @@
         <v>0</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E132" s="9">
         <v>1656</v>
@@ -4456,7 +4511,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B133">
         <v>4028</v>
@@ -4465,7 +4520,7 @@
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E133" s="9">
         <v>1657</v>
@@ -4479,7 +4534,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B134">
         <v>4029</v>
@@ -4488,7 +4543,7 @@
         <v>1</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E134" s="9">
         <v>1658</v>
@@ -4502,7 +4557,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B135">
         <v>4030</v>
@@ -4511,7 +4566,7 @@
         <v>1</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E135" s="9">
         <v>1659</v>
@@ -4525,7 +4580,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B136">
         <v>4031</v>
@@ -4534,7 +4589,7 @@
         <v>1</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E136" s="9">
         <v>1660</v>
@@ -4548,7 +4603,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B137">
         <v>4032</v>
@@ -4557,7 +4612,7 @@
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E137" s="9">
         <v>1661</v>
@@ -4571,7 +4626,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B138">
         <v>4033</v>
@@ -4580,7 +4635,7 @@
         <v>0</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E138" s="9">
         <v>1662</v>
@@ -4594,7 +4649,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B139">
         <v>4034</v>
@@ -4603,7 +4658,7 @@
         <v>1</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E139" s="9">
         <v>1663</v>
@@ -4617,7 +4672,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B140">
         <v>4035</v>
@@ -4626,7 +4681,7 @@
         <v>1</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="E140" s="9">
         <v>1664</v>
@@ -4640,7 +4695,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B141">
         <v>4036</v>
@@ -4649,7 +4704,7 @@
         <v>1</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E141" s="9">
         <v>1665</v>
@@ -4663,7 +4718,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B142">
         <v>4037</v>
@@ -4672,7 +4727,7 @@
         <v>1</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E142" s="9">
         <v>1666</v>
@@ -4686,7 +4741,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B143">
         <v>4038</v>
@@ -4695,7 +4750,7 @@
         <v>1</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E143" s="9">
         <v>1700</v>
@@ -4709,7 +4764,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B144">
         <v>4039</v>
@@ -4718,7 +4773,7 @@
         <v>1</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="E144" s="9">
         <v>1701</v>
@@ -4732,7 +4787,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
-        <v>245</v>
+        <v>299</v>
       </c>
       <c r="B145">
         <v>4040</v>
@@ -4741,7 +4796,7 @@
         <v>0</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E145" s="9">
         <v>1702</v>
@@ -4755,7 +4810,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B146">
         <v>4041</v>
@@ -4764,7 +4819,7 @@
         <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="E146" s="9">
         <v>1703</v>
@@ -4778,7 +4833,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B147">
         <v>4042</v>
@@ -4787,7 +4842,7 @@
         <v>1</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E147" s="9">
         <v>1704</v>
@@ -4801,7 +4856,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B148">
         <v>4043</v>
@@ -4810,7 +4865,7 @@
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E148" s="9">
         <v>1705</v>
@@ -4824,7 +4879,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B149">
         <v>4044</v>
@@ -4833,7 +4888,7 @@
         <v>1</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E149" s="9">
         <v>1706</v>
@@ -4847,7 +4902,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B150">
         <v>4045</v>
@@ -4856,7 +4911,7 @@
         <v>0</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E150" s="9">
         <v>1707</v>
@@ -4870,7 +4925,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B151">
         <v>4046</v>
@@ -4879,7 +4934,7 @@
         <v>1</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E151" s="9">
         <v>1708</v>
@@ -4893,7 +4948,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B152">
         <v>4047</v>
@@ -4902,7 +4957,7 @@
         <v>1</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E152" s="9">
         <v>1709</v>
@@ -4916,7 +4971,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B153">
         <v>4048</v>
@@ -4925,7 +4980,7 @@
         <v>1</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E153" s="9">
         <v>1710</v>
@@ -4934,6 +4989,213 @@
         <v>2</v>
       </c>
       <c r="G153">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>305</v>
+      </c>
+      <c r="B154">
+        <v>4049</v>
+      </c>
+      <c r="C154" s="3">
+        <v>1</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="E154">
+        <v>1800</v>
+      </c>
+      <c r="F154">
+        <v>2</v>
+      </c>
+      <c r="G154">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>306</v>
+      </c>
+      <c r="B155">
+        <v>4050</v>
+      </c>
+      <c r="C155" s="3">
+        <v>1</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E155">
+        <v>1801</v>
+      </c>
+      <c r="F155">
+        <v>2</v>
+      </c>
+      <c r="G155">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>307</v>
+      </c>
+      <c r="B156">
+        <v>4051</v>
+      </c>
+      <c r="C156" s="3">
+        <v>1</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E156">
+        <v>1802</v>
+      </c>
+      <c r="F156">
+        <v>2</v>
+      </c>
+      <c r="G156">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>308</v>
+      </c>
+      <c r="B157">
+        <v>4052</v>
+      </c>
+      <c r="C157" s="3">
+        <v>0</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E157">
+        <v>1803</v>
+      </c>
+      <c r="F157">
+        <v>2</v>
+      </c>
+      <c r="G157">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>309</v>
+      </c>
+      <c r="B158">
+        <v>4053</v>
+      </c>
+      <c r="C158" s="3">
+        <v>0</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E158">
+        <v>1804</v>
+      </c>
+      <c r="F158">
+        <v>2</v>
+      </c>
+      <c r="G158">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>310</v>
+      </c>
+      <c r="B159">
+        <v>4054</v>
+      </c>
+      <c r="C159" s="3">
+        <v>1</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E159">
+        <v>1805</v>
+      </c>
+      <c r="F159">
+        <v>2</v>
+      </c>
+      <c r="G159">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>311</v>
+      </c>
+      <c r="B160">
+        <v>4055</v>
+      </c>
+      <c r="C160" s="3">
+        <v>1</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E160">
+        <v>1806</v>
+      </c>
+      <c r="F160">
+        <v>2</v>
+      </c>
+      <c r="G160">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>312</v>
+      </c>
+      <c r="B161">
+        <v>4056</v>
+      </c>
+      <c r="C161" s="3">
+        <v>1</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E161">
+        <v>1807</v>
+      </c>
+      <c r="F161">
+        <v>2</v>
+      </c>
+      <c r="G161">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>313</v>
+      </c>
+      <c r="B162">
+        <v>4057</v>
+      </c>
+      <c r="C162" s="3">
+        <v>0</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E162">
+        <v>1808</v>
+      </c>
+      <c r="F162">
+        <v>2</v>
+      </c>
+      <c r="G162">
         <v>2</v>
       </c>
     </row>

--- a/Datas/FormulaData.xlsx
+++ b/Datas/FormulaData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="FormulaData" sheetId="1" r:id="rId1"/>
@@ -300,9 +300,6 @@
     <t>烤金枪鱼</t>
   </si>
   <si>
-    <t>煮蟹肉</t>
-  </si>
-  <si>
     <t>海鲜浓汤</t>
   </si>
   <si>
@@ -310,9 +307,6 @@
   </si>
   <si>
     <t>鲫鱼蔬菜汤</t>
-  </si>
-  <si>
-    <t>鲮鱼丸</t>
   </si>
   <si>
     <t>鲑鱼刺身</t>
@@ -1097,6 +1091,14 @@
   </si>
   <si>
     <t>1804,288,247</t>
+  </si>
+  <si>
+    <t>鲮鱼丸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>煮蟹肉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1553,7 +1555,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E4">
         <v>3009</v>
@@ -1576,7 +1578,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E5">
         <v>3010</v>
@@ -1590,7 +1592,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B6">
         <v>3011</v>
@@ -1599,7 +1601,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E6" s="2">
         <v>3002</v>
@@ -1622,7 +1624,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E7">
         <v>3011</v>
@@ -1645,7 +1647,7 @@
         <v>11</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E8">
         <v>3100</v>
@@ -1668,7 +1670,7 @@
         <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E9">
         <v>3101</v>
@@ -1691,7 +1693,7 @@
         <v>11</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E10">
         <v>3102</v>
@@ -1714,7 +1716,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E11">
         <v>3103</v>
@@ -1737,7 +1739,7 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E12">
         <v>3104</v>
@@ -1760,7 +1762,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E13">
         <v>3105</v>
@@ -1783,7 +1785,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E14">
         <v>3106</v>
@@ -1806,7 +1808,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E15">
         <v>3107</v>
@@ -1829,7 +1831,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>3108</v>
@@ -1852,7 +1854,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E17">
         <v>3109</v>
@@ -1875,7 +1877,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E18">
         <v>3110</v>
@@ -1898,7 +1900,7 @@
         <v>11</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E19">
         <v>3111</v>
@@ -1921,7 +1923,7 @@
         <v>13</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E20">
         <v>3112</v>
@@ -1944,7 +1946,7 @@
         <v>13</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E21">
         <v>3113</v>
@@ -1967,7 +1969,7 @@
         <v>13</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E22">
         <v>3114</v>
@@ -1990,7 +1992,7 @@
         <v>11</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E23">
         <v>3115</v>
@@ -2013,7 +2015,7 @@
         <v>11</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E24">
         <v>3116</v>
@@ -2036,7 +2038,7 @@
         <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E25">
         <v>3117</v>
@@ -2059,7 +2061,7 @@
         <v>12</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E26">
         <v>3118</v>
@@ -2082,7 +2084,7 @@
         <v>13</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E27">
         <v>3119</v>
@@ -2105,7 +2107,7 @@
         <v>15</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E28">
         <v>3120</v>
@@ -2128,7 +2130,7 @@
         <v>15</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E29">
         <v>3121</v>
@@ -2151,7 +2153,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E30">
         <v>3122</v>
@@ -2174,7 +2176,7 @@
         <v>15</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E31">
         <v>3123</v>
@@ -2197,7 +2199,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E32">
         <v>3124</v>
@@ -2220,7 +2222,7 @@
         <v>15</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E33">
         <v>3125</v>
@@ -2243,7 +2245,7 @@
         <v>15</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E34">
         <v>3126</v>
@@ -2266,7 +2268,7 @@
         <v>15</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E35">
         <v>3127</v>
@@ -2289,7 +2291,7 @@
         <v>13</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E36">
         <v>3128</v>
@@ -2312,7 +2314,7 @@
         <v>15</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E37">
         <v>3129</v>
@@ -2335,7 +2337,7 @@
         <v>14</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E38">
         <v>3130</v>
@@ -2358,7 +2360,7 @@
         <v>13</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E39">
         <v>3131</v>
@@ -2381,7 +2383,7 @@
         <v>12</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E40">
         <v>3132</v>
@@ -2404,7 +2406,7 @@
         <v>12</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E41">
         <v>3133</v>
@@ -2427,7 +2429,7 @@
         <v>13</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E42">
         <v>3134</v>
@@ -2450,7 +2452,7 @@
         <v>12</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E43">
         <v>3135</v>
@@ -2473,7 +2475,7 @@
         <v>12</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E44">
         <v>3136</v>
@@ -2496,7 +2498,7 @@
         <v>15</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E45">
         <v>3137</v>
@@ -2519,7 +2521,7 @@
         <v>15</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E46">
         <v>3138</v>
@@ -2542,7 +2544,7 @@
         <v>11</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E47">
         <v>3139</v>
@@ -2565,7 +2567,7 @@
         <v>15</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E48">
         <v>3140</v>
@@ -2588,7 +2590,7 @@
         <v>15</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E49">
         <v>3141</v>
@@ -2611,7 +2613,7 @@
         <v>14</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E50">
         <v>3142</v>
@@ -2634,7 +2636,7 @@
         <v>14</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E51">
         <v>3143</v>
@@ -2657,7 +2659,7 @@
         <v>14</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E52">
         <v>3144</v>
@@ -2680,7 +2682,7 @@
         <v>14</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E53">
         <v>3145</v>
@@ -2703,7 +2705,7 @@
         <v>14</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E54">
         <v>3146</v>
@@ -2726,7 +2728,7 @@
         <v>14</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E55">
         <v>3147</v>
@@ -2749,7 +2751,7 @@
         <v>14</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E56">
         <v>3148</v>
@@ -2772,7 +2774,7 @@
         <v>14</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E57">
         <v>3149</v>
@@ -2795,7 +2797,7 @@
         <v>13</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E58">
         <v>3150</v>
@@ -2818,7 +2820,7 @@
         <v>13</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E59">
         <v>3151</v>
@@ -2841,7 +2843,7 @@
         <v>13</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E60">
         <v>3152</v>
@@ -2864,7 +2866,7 @@
         <v>13</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E61">
         <v>3153</v>
@@ -2887,7 +2889,7 @@
         <v>13</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E62">
         <v>3154</v>
@@ -2910,7 +2912,7 @@
         <v>13</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E63">
         <v>3155</v>
@@ -2933,7 +2935,7 @@
         <v>13</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E64">
         <v>3156</v>
@@ -2956,7 +2958,7 @@
         <v>13</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E65">
         <v>3157</v>
@@ -2979,7 +2981,7 @@
         <v>13</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E66">
         <v>3158</v>
@@ -3002,7 +3004,7 @@
         <v>13</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E67">
         <v>3159</v>
@@ -3025,7 +3027,7 @@
         <v>13</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E68">
         <v>3160</v>
@@ -3048,7 +3050,7 @@
         <v>13</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E69">
         <v>3161</v>
@@ -3071,7 +3073,7 @@
         <v>13</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E70">
         <v>3162</v>
@@ -3094,7 +3096,7 @@
         <v>13</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E71">
         <v>3163</v>
@@ -3117,7 +3119,7 @@
         <v>13</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E72">
         <v>3164</v>
@@ -3140,7 +3142,7 @@
         <v>13</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E73">
         <v>3165</v>
@@ -3154,7 +3156,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="B74">
         <v>3079</v>
@@ -3163,7 +3165,7 @@
         <v>12</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E74">
         <v>3166</v>
@@ -3177,7 +3179,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B75">
         <v>3080</v>
@@ -3186,7 +3188,7 @@
         <v>12</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E75">
         <v>3167</v>
@@ -3200,7 +3202,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B76">
         <v>3081</v>
@@ -3209,7 +3211,7 @@
         <v>11</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E76">
         <v>3168</v>
@@ -3223,7 +3225,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B77">
         <v>3082</v>
@@ -3232,7 +3234,7 @@
         <v>12</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E77">
         <v>3169</v>
@@ -3246,7 +3248,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>83</v>
+        <v>321</v>
       </c>
       <c r="B78">
         <v>3083</v>
@@ -3255,7 +3257,7 @@
         <v>12</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E78">
         <v>3170</v>
@@ -3269,7 +3271,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B79">
         <v>3084</v>
@@ -3278,7 +3280,7 @@
         <v>11</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E79">
         <v>3171</v>
@@ -3292,7 +3294,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B80">
         <v>3085</v>
@@ -3301,7 +3303,7 @@
         <v>12</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E80">
         <v>3172</v>
@@ -3315,7 +3317,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B81">
         <v>3086</v>
@@ -3324,7 +3326,7 @@
         <v>12</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E81">
         <v>3173</v>
@@ -3338,7 +3340,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B82">
         <v>3087</v>
@@ -3347,7 +3349,7 @@
         <v>11</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E82">
         <v>3174</v>
@@ -3361,7 +3363,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B83">
         <v>3088</v>
@@ -3370,7 +3372,7 @@
         <v>11</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E83">
         <v>3175</v>
@@ -3384,7 +3386,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B84">
         <v>3089</v>
@@ -3393,7 +3395,7 @@
         <v>12</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E84">
         <v>3176</v>
@@ -3407,7 +3409,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B85">
         <v>3090</v>
@@ -3416,7 +3418,7 @@
         <v>11</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E85">
         <v>3177</v>
@@ -3430,7 +3432,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B86">
         <v>3091</v>
@@ -3439,7 +3441,7 @@
         <v>11</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E86">
         <v>3178</v>
@@ -3453,7 +3455,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B87">
         <v>2000</v>
@@ -3476,7 +3478,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B88">
         <v>2001</v>
@@ -3485,7 +3487,7 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E88">
         <v>103</v>
@@ -3499,7 +3501,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B89">
         <v>2003</v>
@@ -3508,7 +3510,7 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E89">
         <v>103</v>
@@ -3522,7 +3524,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B90">
         <v>2010</v>
@@ -3545,7 +3547,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B91">
         <v>2011</v>
@@ -3568,7 +3570,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B92">
         <v>2012</v>
@@ -3591,7 +3593,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B93">
         <v>2100</v>
@@ -3600,7 +3602,7 @@
         <v>2</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E93" s="2">
         <v>4000</v>
@@ -3614,7 +3616,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B94">
         <v>2101</v>
@@ -3623,7 +3625,7 @@
         <v>2</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E94" s="2">
         <v>4001</v>
@@ -3637,7 +3639,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B95">
         <v>2102</v>
@@ -3646,7 +3648,7 @@
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E95" s="2">
         <v>4002</v>
@@ -3660,7 +3662,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B96">
         <v>2103</v>
@@ -3669,7 +3671,7 @@
         <v>2</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E96" s="2">
         <v>4003</v>
@@ -3683,7 +3685,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B97">
         <v>2104</v>
@@ -3692,7 +3694,7 @@
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E97" s="2">
         <v>4004</v>
@@ -3706,7 +3708,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B98">
         <v>2105</v>
@@ -3715,7 +3717,7 @@
         <v>2</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E98" s="2">
         <v>4005</v>
@@ -3729,7 +3731,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B99">
         <v>2106</v>
@@ -3738,7 +3740,7 @@
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E99" s="2">
         <v>4006</v>
@@ -3752,7 +3754,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B100">
         <v>2107</v>
@@ -3761,7 +3763,7 @@
         <v>2</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E100" s="2">
         <v>4007</v>
@@ -3775,7 +3777,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B101">
         <v>2108</v>
@@ -3784,7 +3786,7 @@
         <v>2</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E101" s="2">
         <v>4008</v>
@@ -3798,7 +3800,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B102">
         <v>2109</v>
@@ -3807,7 +3809,7 @@
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E102" s="2">
         <v>4009</v>
@@ -3821,7 +3823,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B103">
         <v>2110</v>
@@ -3830,7 +3832,7 @@
         <v>2</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E103" s="2">
         <v>4010</v>
@@ -3844,7 +3846,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B104">
         <v>2111</v>
@@ -3853,7 +3855,7 @@
         <v>2</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E104">
         <v>11</v>
@@ -3867,7 +3869,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B105">
         <v>4000</v>
@@ -3876,7 +3878,7 @@
         <v>0</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E105" s="9">
         <v>1600</v>
@@ -3890,7 +3892,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B106">
         <v>4001</v>
@@ -3899,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E106" s="9">
         <v>1601</v>
@@ -3913,7 +3915,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B107">
         <v>4002</v>
@@ -3922,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E107" s="9">
         <v>1602</v>
@@ -3936,7 +3938,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B108">
         <v>4003</v>
@@ -3945,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E108" s="9">
         <v>1603</v>
@@ -3959,7 +3961,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B109">
         <v>4004</v>
@@ -3968,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E109" s="9">
         <v>1604</v>
@@ -3982,7 +3984,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B110">
         <v>4005</v>
@@ -3991,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E110" s="9">
         <v>1605</v>
@@ -4005,7 +4007,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B111">
         <v>4006</v>
@@ -4014,7 +4016,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E111" s="9">
         <v>1606</v>
@@ -4028,7 +4030,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B112">
         <v>4007</v>
@@ -4037,7 +4039,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E112" s="9">
         <v>1607</v>
@@ -4051,7 +4053,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B113">
         <v>4008</v>
@@ -4060,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E113" s="9">
         <v>1608</v>
@@ -4074,7 +4076,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B114">
         <v>4009</v>
@@ -4083,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E114" s="9">
         <v>1609</v>
@@ -4097,7 +4099,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B115">
         <v>4010</v>
@@ -4106,7 +4108,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E115" s="9">
         <v>1610</v>
@@ -4120,7 +4122,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B116">
         <v>4011</v>
@@ -4129,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E116" s="9">
         <v>1611</v>
@@ -4143,7 +4145,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B117">
         <v>4012</v>
@@ -4152,7 +4154,7 @@
         <v>0</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E117" s="9">
         <v>1612</v>
@@ -4166,7 +4168,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B118">
         <v>4013</v>
@@ -4175,7 +4177,7 @@
         <v>0</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E118" s="9">
         <v>1613</v>
@@ -4189,7 +4191,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B119">
         <v>4014</v>
@@ -4198,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E119" s="9">
         <v>1614</v>
@@ -4212,7 +4214,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B120">
         <v>4015</v>
@@ -4221,7 +4223,7 @@
         <v>1</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E120" s="9">
         <v>1615</v>
@@ -4235,7 +4237,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B121">
         <v>4016</v>
@@ -4244,7 +4246,7 @@
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E121" s="9">
         <v>1616</v>
@@ -4258,7 +4260,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B122">
         <v>4017</v>
@@ -4267,7 +4269,7 @@
         <v>1</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E122" s="9">
         <v>1617</v>
@@ -4281,7 +4283,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B123">
         <v>4018</v>
@@ -4290,7 +4292,7 @@
         <v>1</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E123" s="9">
         <v>1618</v>
@@ -4304,7 +4306,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B124">
         <v>4019</v>
@@ -4313,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E124" s="9">
         <v>1619</v>
@@ -4327,7 +4329,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B125">
         <v>4020</v>
@@ -4336,7 +4338,7 @@
         <v>0</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E125" s="9">
         <v>1620</v>
@@ -4350,7 +4352,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B126">
         <v>4021</v>
@@ -4359,7 +4361,7 @@
         <v>1</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E126" s="9">
         <v>1650</v>
@@ -4373,7 +4375,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B127">
         <v>4022</v>
@@ -4382,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E127" s="9">
         <v>1651</v>
@@ -4396,7 +4398,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B128">
         <v>4023</v>
@@ -4405,7 +4407,7 @@
         <v>1</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E128" s="9">
         <v>1652</v>
@@ -4419,7 +4421,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B129">
         <v>4024</v>
@@ -4428,7 +4430,7 @@
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E129" s="9">
         <v>1653</v>
@@ -4442,7 +4444,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B130">
         <v>4025</v>
@@ -4451,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E130" s="9">
         <v>1654</v>
@@ -4465,7 +4467,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B131">
         <v>4026</v>
@@ -4474,7 +4476,7 @@
         <v>0</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E131" s="9">
         <v>1655</v>
@@ -4488,7 +4490,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B132">
         <v>4027</v>
@@ -4497,7 +4499,7 @@
         <v>0</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E132" s="9">
         <v>1656</v>
@@ -4511,7 +4513,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B133">
         <v>4028</v>
@@ -4520,7 +4522,7 @@
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E133" s="9">
         <v>1657</v>
@@ -4534,7 +4536,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B134">
         <v>4029</v>
@@ -4543,7 +4545,7 @@
         <v>1</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E134" s="9">
         <v>1658</v>
@@ -4557,7 +4559,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B135">
         <v>4030</v>
@@ -4566,7 +4568,7 @@
         <v>1</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E135" s="9">
         <v>1659</v>
@@ -4580,7 +4582,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B136">
         <v>4031</v>
@@ -4589,7 +4591,7 @@
         <v>1</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E136" s="9">
         <v>1660</v>
@@ -4603,7 +4605,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B137">
         <v>4032</v>
@@ -4612,7 +4614,7 @@
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E137" s="9">
         <v>1661</v>
@@ -4626,7 +4628,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B138">
         <v>4033</v>
@@ -4635,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E138" s="9">
         <v>1662</v>
@@ -4649,7 +4651,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B139">
         <v>4034</v>
@@ -4658,7 +4660,7 @@
         <v>1</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E139" s="9">
         <v>1663</v>
@@ -4672,7 +4674,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B140">
         <v>4035</v>
@@ -4681,7 +4683,7 @@
         <v>1</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E140" s="9">
         <v>1664</v>
@@ -4695,7 +4697,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B141">
         <v>4036</v>
@@ -4704,7 +4706,7 @@
         <v>1</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E141" s="9">
         <v>1665</v>
@@ -4718,7 +4720,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B142">
         <v>4037</v>
@@ -4727,7 +4729,7 @@
         <v>1</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E142" s="9">
         <v>1666</v>
@@ -4741,7 +4743,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B143">
         <v>4038</v>
@@ -4750,7 +4752,7 @@
         <v>1</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E143" s="9">
         <v>1700</v>
@@ -4764,7 +4766,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B144">
         <v>4039</v>
@@ -4773,7 +4775,7 @@
         <v>1</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E144" s="9">
         <v>1701</v>
@@ -4787,7 +4789,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B145">
         <v>4040</v>
@@ -4796,7 +4798,7 @@
         <v>0</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E145" s="9">
         <v>1702</v>
@@ -4810,7 +4812,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B146">
         <v>4041</v>
@@ -4819,7 +4821,7 @@
         <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E146" s="9">
         <v>1703</v>
@@ -4833,7 +4835,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B147">
         <v>4042</v>
@@ -4842,7 +4844,7 @@
         <v>1</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E147" s="9">
         <v>1704</v>
@@ -4856,7 +4858,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B148">
         <v>4043</v>
@@ -4865,7 +4867,7 @@
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E148" s="9">
         <v>1705</v>
@@ -4879,7 +4881,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B149">
         <v>4044</v>
@@ -4888,7 +4890,7 @@
         <v>1</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E149" s="9">
         <v>1706</v>
@@ -4902,7 +4904,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B150">
         <v>4045</v>
@@ -4911,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E150" s="9">
         <v>1707</v>
@@ -4925,7 +4927,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B151">
         <v>4046</v>
@@ -4934,7 +4936,7 @@
         <v>1</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E151" s="9">
         <v>1708</v>
@@ -4948,7 +4950,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B152">
         <v>4047</v>
@@ -4957,7 +4959,7 @@
         <v>1</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E152" s="9">
         <v>1709</v>
@@ -4971,7 +4973,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B153">
         <v>4048</v>
@@ -4980,7 +4982,7 @@
         <v>1</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E153" s="9">
         <v>1710</v>
@@ -4994,7 +4996,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B154">
         <v>4049</v>
@@ -5003,7 +5005,7 @@
         <v>1</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E154">
         <v>1800</v>
@@ -5017,7 +5019,7 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B155">
         <v>4050</v>
@@ -5026,7 +5028,7 @@
         <v>1</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E155">
         <v>1801</v>
@@ -5040,7 +5042,7 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B156">
         <v>4051</v>
@@ -5049,7 +5051,7 @@
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E156">
         <v>1802</v>
@@ -5063,7 +5065,7 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B157">
         <v>4052</v>
@@ -5072,7 +5074,7 @@
         <v>0</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E157">
         <v>1803</v>
@@ -5086,7 +5088,7 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B158">
         <v>4053</v>
@@ -5095,7 +5097,7 @@
         <v>0</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E158">
         <v>1804</v>
@@ -5109,7 +5111,7 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B159">
         <v>4054</v>
@@ -5118,7 +5120,7 @@
         <v>1</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E159">
         <v>1805</v>
@@ -5132,7 +5134,7 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B160">
         <v>4055</v>
@@ -5141,7 +5143,7 @@
         <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E160">
         <v>1806</v>
@@ -5155,7 +5157,7 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B161">
         <v>4056</v>
@@ -5164,7 +5166,7 @@
         <v>1</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E161">
         <v>1807</v>
@@ -5178,7 +5180,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B162">
         <v>4057</v>
@@ -5187,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E162">
         <v>1808</v>

--- a/Datas/FormulaData.xlsx
+++ b/Datas/FormulaData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="FormulaData" sheetId="1" r:id="rId1"/>
@@ -576,9 +576,6 @@
     <t>4116</t>
   </si>
   <si>
-    <t>3164,3134,1006,4021</t>
-  </si>
-  <si>
     <t>木材</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1098,6 +1095,10 @@
   </si>
   <si>
     <t>煮蟹肉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3164,3134,1006,4015</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1592,7 +1593,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B6">
         <v>3011</v>
@@ -1601,7 +1602,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E6" s="2">
         <v>3002</v>
@@ -3156,7 +3157,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B74">
         <v>3079</v>
@@ -3248,7 +3249,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B78">
         <v>3083</v>
@@ -3441,7 +3442,7 @@
         <v>11</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>171</v>
+        <v>322</v>
       </c>
       <c r="E86">
         <v>3178</v>
@@ -3455,7 +3456,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B87">
         <v>2000</v>
@@ -3478,7 +3479,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B88">
         <v>2001</v>
@@ -3487,7 +3488,7 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E88">
         <v>103</v>
@@ -3501,7 +3502,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B89">
         <v>2003</v>
@@ -3510,7 +3511,7 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E89">
         <v>103</v>
@@ -3524,7 +3525,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B90">
         <v>2010</v>
@@ -3547,7 +3548,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B91">
         <v>2011</v>
@@ -3570,7 +3571,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B92">
         <v>2012</v>
@@ -3593,7 +3594,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B93">
         <v>2100</v>
@@ -3602,7 +3603,7 @@
         <v>2</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E93" s="2">
         <v>4000</v>
@@ -3616,7 +3617,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B94">
         <v>2101</v>
@@ -3625,7 +3626,7 @@
         <v>2</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E94" s="2">
         <v>4001</v>
@@ -3639,7 +3640,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B95">
         <v>2102</v>
@@ -3648,7 +3649,7 @@
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E95" s="2">
         <v>4002</v>
@@ -3662,7 +3663,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B96">
         <v>2103</v>
@@ -3671,7 +3672,7 @@
         <v>2</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E96" s="2">
         <v>4003</v>
@@ -3685,7 +3686,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B97">
         <v>2104</v>
@@ -3694,7 +3695,7 @@
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E97" s="2">
         <v>4004</v>
@@ -3708,7 +3709,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B98">
         <v>2105</v>
@@ -3717,7 +3718,7 @@
         <v>2</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E98" s="2">
         <v>4005</v>
@@ -3731,7 +3732,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B99">
         <v>2106</v>
@@ -3740,7 +3741,7 @@
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E99" s="2">
         <v>4006</v>
@@ -3754,7 +3755,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B100">
         <v>2107</v>
@@ -3763,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E100" s="2">
         <v>4007</v>
@@ -3777,7 +3778,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B101">
         <v>2108</v>
@@ -3786,7 +3787,7 @@
         <v>2</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E101" s="2">
         <v>4008</v>
@@ -3800,7 +3801,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B102">
         <v>2109</v>
@@ -3809,7 +3810,7 @@
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E102" s="2">
         <v>4009</v>
@@ -3823,7 +3824,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B103">
         <v>2110</v>
@@ -3832,7 +3833,7 @@
         <v>2</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E103" s="2">
         <v>4010</v>
@@ -3846,7 +3847,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B104">
         <v>2111</v>
@@ -3855,7 +3856,7 @@
         <v>2</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E104">
         <v>11</v>
@@ -3869,7 +3870,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B105">
         <v>4000</v>
@@ -3878,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E105" s="9">
         <v>1600</v>
@@ -3892,7 +3893,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B106">
         <v>4001</v>
@@ -3901,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E106" s="9">
         <v>1601</v>
@@ -3915,7 +3916,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B107">
         <v>4002</v>
@@ -3924,7 +3925,7 @@
         <v>0</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E107" s="9">
         <v>1602</v>
@@ -3938,7 +3939,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B108">
         <v>4003</v>
@@ -3947,7 +3948,7 @@
         <v>0</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E108" s="9">
         <v>1603</v>
@@ -3961,7 +3962,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B109">
         <v>4004</v>
@@ -3970,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E109" s="9">
         <v>1604</v>
@@ -3984,7 +3985,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B110">
         <v>4005</v>
@@ -3993,7 +3994,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E110" s="9">
         <v>1605</v>
@@ -4007,7 +4008,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B111">
         <v>4006</v>
@@ -4016,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E111" s="9">
         <v>1606</v>
@@ -4030,7 +4031,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B112">
         <v>4007</v>
@@ -4039,7 +4040,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E112" s="9">
         <v>1607</v>
@@ -4053,7 +4054,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B113">
         <v>4008</v>
@@ -4062,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E113" s="9">
         <v>1608</v>
@@ -4076,7 +4077,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B114">
         <v>4009</v>
@@ -4085,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E114" s="9">
         <v>1609</v>
@@ -4099,7 +4100,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B115">
         <v>4010</v>
@@ -4108,7 +4109,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E115" s="9">
         <v>1610</v>
@@ -4122,7 +4123,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B116">
         <v>4011</v>
@@ -4131,7 +4132,7 @@
         <v>0</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E116" s="9">
         <v>1611</v>
@@ -4145,7 +4146,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B117">
         <v>4012</v>
@@ -4154,7 +4155,7 @@
         <v>0</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E117" s="9">
         <v>1612</v>
@@ -4168,7 +4169,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B118">
         <v>4013</v>
@@ -4177,7 +4178,7 @@
         <v>0</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E118" s="9">
         <v>1613</v>
@@ -4191,7 +4192,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B119">
         <v>4014</v>
@@ -4200,7 +4201,7 @@
         <v>0</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E119" s="9">
         <v>1614</v>
@@ -4214,7 +4215,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B120">
         <v>4015</v>
@@ -4223,7 +4224,7 @@
         <v>1</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E120" s="9">
         <v>1615</v>
@@ -4237,7 +4238,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B121">
         <v>4016</v>
@@ -4246,7 +4247,7 @@
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E121" s="9">
         <v>1616</v>
@@ -4260,7 +4261,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B122">
         <v>4017</v>
@@ -4269,7 +4270,7 @@
         <v>1</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E122" s="9">
         <v>1617</v>
@@ -4283,7 +4284,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B123">
         <v>4018</v>
@@ -4292,7 +4293,7 @@
         <v>1</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E123" s="9">
         <v>1618</v>
@@ -4306,7 +4307,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B124">
         <v>4019</v>
@@ -4315,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E124" s="9">
         <v>1619</v>
@@ -4329,7 +4330,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B125">
         <v>4020</v>
@@ -4338,7 +4339,7 @@
         <v>0</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E125" s="9">
         <v>1620</v>
@@ -4352,7 +4353,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B126">
         <v>4021</v>
@@ -4361,7 +4362,7 @@
         <v>1</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E126" s="9">
         <v>1650</v>
@@ -4375,7 +4376,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B127">
         <v>4022</v>
@@ -4384,7 +4385,7 @@
         <v>1</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E127" s="9">
         <v>1651</v>
@@ -4398,7 +4399,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B128">
         <v>4023</v>
@@ -4407,7 +4408,7 @@
         <v>1</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E128" s="9">
         <v>1652</v>
@@ -4421,7 +4422,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B129">
         <v>4024</v>
@@ -4430,7 +4431,7 @@
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E129" s="9">
         <v>1653</v>
@@ -4444,7 +4445,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B130">
         <v>4025</v>
@@ -4453,7 +4454,7 @@
         <v>0</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E130" s="9">
         <v>1654</v>
@@ -4467,7 +4468,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B131">
         <v>4026</v>
@@ -4476,7 +4477,7 @@
         <v>0</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E131" s="9">
         <v>1655</v>
@@ -4490,7 +4491,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B132">
         <v>4027</v>
@@ -4499,7 +4500,7 @@
         <v>0</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E132" s="9">
         <v>1656</v>
@@ -4513,7 +4514,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B133">
         <v>4028</v>
@@ -4522,7 +4523,7 @@
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E133" s="9">
         <v>1657</v>
@@ -4536,7 +4537,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B134">
         <v>4029</v>
@@ -4545,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E134" s="9">
         <v>1658</v>
@@ -4559,7 +4560,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B135">
         <v>4030</v>
@@ -4568,7 +4569,7 @@
         <v>1</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E135" s="9">
         <v>1659</v>
@@ -4582,7 +4583,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B136">
         <v>4031</v>
@@ -4591,7 +4592,7 @@
         <v>1</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E136" s="9">
         <v>1660</v>
@@ -4605,7 +4606,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B137">
         <v>4032</v>
@@ -4614,7 +4615,7 @@
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E137" s="9">
         <v>1661</v>
@@ -4628,7 +4629,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B138">
         <v>4033</v>
@@ -4637,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E138" s="9">
         <v>1662</v>
@@ -4651,7 +4652,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B139">
         <v>4034</v>
@@ -4660,7 +4661,7 @@
         <v>1</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E139" s="9">
         <v>1663</v>
@@ -4674,7 +4675,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B140">
         <v>4035</v>
@@ -4683,7 +4684,7 @@
         <v>1</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E140" s="9">
         <v>1664</v>
@@ -4697,7 +4698,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B141">
         <v>4036</v>
@@ -4706,7 +4707,7 @@
         <v>1</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E141" s="9">
         <v>1665</v>
@@ -4720,7 +4721,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B142">
         <v>4037</v>
@@ -4729,7 +4730,7 @@
         <v>1</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E142" s="9">
         <v>1666</v>
@@ -4743,7 +4744,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B143">
         <v>4038</v>
@@ -4752,7 +4753,7 @@
         <v>1</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E143" s="9">
         <v>1700</v>
@@ -4766,7 +4767,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B144">
         <v>4039</v>
@@ -4775,7 +4776,7 @@
         <v>1</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E144" s="9">
         <v>1701</v>
@@ -4789,7 +4790,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B145">
         <v>4040</v>
@@ -4798,7 +4799,7 @@
         <v>0</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E145" s="9">
         <v>1702</v>
@@ -4812,7 +4813,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B146">
         <v>4041</v>
@@ -4821,7 +4822,7 @@
         <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E146" s="9">
         <v>1703</v>
@@ -4835,7 +4836,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B147">
         <v>4042</v>
@@ -4844,7 +4845,7 @@
         <v>1</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E147" s="9">
         <v>1704</v>
@@ -4858,7 +4859,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B148">
         <v>4043</v>
@@ -4867,7 +4868,7 @@
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E148" s="9">
         <v>1705</v>
@@ -4881,7 +4882,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B149">
         <v>4044</v>
@@ -4890,7 +4891,7 @@
         <v>1</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E149" s="9">
         <v>1706</v>
@@ -4904,7 +4905,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B150">
         <v>4045</v>
@@ -4913,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E150" s="9">
         <v>1707</v>
@@ -4927,7 +4928,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B151">
         <v>4046</v>
@@ -4936,7 +4937,7 @@
         <v>1</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E151" s="9">
         <v>1708</v>
@@ -4950,7 +4951,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B152">
         <v>4047</v>
@@ -4959,7 +4960,7 @@
         <v>1</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E152" s="9">
         <v>1709</v>
@@ -4973,7 +4974,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B153">
         <v>4048</v>
@@ -4982,7 +4983,7 @@
         <v>1</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E153" s="9">
         <v>1710</v>
@@ -4996,7 +4997,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B154">
         <v>4049</v>
@@ -5005,7 +5006,7 @@
         <v>1</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E154">
         <v>1800</v>
@@ -5019,7 +5020,7 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B155">
         <v>4050</v>
@@ -5028,7 +5029,7 @@
         <v>1</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E155">
         <v>1801</v>
@@ -5042,7 +5043,7 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B156">
         <v>4051</v>
@@ -5051,7 +5052,7 @@
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E156">
         <v>1802</v>
@@ -5065,7 +5066,7 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B157">
         <v>4052</v>
@@ -5074,7 +5075,7 @@
         <v>0</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E157">
         <v>1803</v>
@@ -5088,7 +5089,7 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B158">
         <v>4053</v>
@@ -5097,7 +5098,7 @@
         <v>0</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E158">
         <v>1804</v>
@@ -5111,7 +5112,7 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B159">
         <v>4054</v>
@@ -5120,7 +5121,7 @@
         <v>1</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E159">
         <v>1805</v>
@@ -5134,7 +5135,7 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B160">
         <v>4055</v>
@@ -5143,7 +5144,7 @@
         <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E160">
         <v>1806</v>
@@ -5157,7 +5158,7 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B161">
         <v>4056</v>
@@ -5166,7 +5167,7 @@
         <v>1</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E161">
         <v>1807</v>
@@ -5180,7 +5181,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B162">
         <v>4057</v>
@@ -5189,7 +5190,7 @@
         <v>0</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E162">
         <v>1808</v>

--- a/Datas/FormulaData.xlsx
+++ b/Datas/FormulaData.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FormulaData!$A$3:$G$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FormulaData!$A$3:$G$162</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1565,7 +1565,7 @@
         <v>2</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -1588,7 +1588,7 @@
         <v>2</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -1611,7 +1611,7 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -1634,7 +1634,7 @@
         <v>2</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -1657,7 +1657,7 @@
         <v>2</v>
       </c>
       <c r="G8">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -1680,7 +1680,7 @@
         <v>2</v>
       </c>
       <c r="G9">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -1703,7 +1703,7 @@
         <v>2</v>
       </c>
       <c r="G10">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -1726,7 +1726,7 @@
         <v>2</v>
       </c>
       <c r="G11">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -1818,7 +1818,7 @@
         <v>2</v>
       </c>
       <c r="G15">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -1910,7 +1910,7 @@
         <v>2</v>
       </c>
       <c r="G19">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -2002,7 +2002,7 @@
         <v>2</v>
       </c>
       <c r="G23">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -2025,7 +2025,7 @@
         <v>2</v>
       </c>
       <c r="G24">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -2117,7 +2117,7 @@
         <v>2</v>
       </c>
       <c r="G28">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
@@ -2140,7 +2140,7 @@
         <v>2</v>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -2163,7 +2163,7 @@
         <v>2</v>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -2186,7 +2186,7 @@
         <v>2</v>
       </c>
       <c r="G31">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
@@ -2209,7 +2209,7 @@
         <v>2</v>
       </c>
       <c r="G32">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
@@ -2232,7 +2232,7 @@
         <v>2</v>
       </c>
       <c r="G33">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
@@ -2255,7 +2255,7 @@
         <v>2</v>
       </c>
       <c r="G34">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -2278,7 +2278,7 @@
         <v>2</v>
       </c>
       <c r="G35">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -2324,7 +2324,7 @@
         <v>2</v>
       </c>
       <c r="G37">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -2347,7 +2347,7 @@
         <v>2</v>
       </c>
       <c r="G38">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
@@ -2508,7 +2508,7 @@
         <v>2</v>
       </c>
       <c r="G45">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
@@ -2531,7 +2531,7 @@
         <v>2</v>
       </c>
       <c r="G46">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
@@ -2554,7 +2554,7 @@
         <v>2</v>
       </c>
       <c r="G47">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
@@ -2577,7 +2577,7 @@
         <v>2</v>
       </c>
       <c r="G48">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
@@ -2600,7 +2600,7 @@
         <v>2</v>
       </c>
       <c r="G49">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
@@ -2623,7 +2623,7 @@
         <v>2</v>
       </c>
       <c r="G50">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
@@ -2646,7 +2646,7 @@
         <v>2</v>
       </c>
       <c r="G51">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
@@ -2669,7 +2669,7 @@
         <v>2</v>
       </c>
       <c r="G52">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
@@ -2692,7 +2692,7 @@
         <v>2</v>
       </c>
       <c r="G53">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
@@ -2715,7 +2715,7 @@
         <v>2</v>
       </c>
       <c r="G54">
-        <v>10</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
@@ -2738,7 +2738,7 @@
         <v>2</v>
       </c>
       <c r="G55">
-        <v>10</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
@@ -2761,7 +2761,7 @@
         <v>2</v>
       </c>
       <c r="G56">
-        <v>10</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
@@ -2784,7 +2784,7 @@
         <v>2</v>
       </c>
       <c r="G57">
-        <v>10</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
@@ -3221,7 +3221,7 @@
         <v>2</v>
       </c>
       <c r="G76">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
@@ -3290,7 +3290,7 @@
         <v>2</v>
       </c>
       <c r="G79">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
@@ -3359,7 +3359,7 @@
         <v>2</v>
       </c>
       <c r="G82">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
@@ -3382,7 +3382,7 @@
         <v>2</v>
       </c>
       <c r="G83">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
@@ -3428,7 +3428,7 @@
         <v>2</v>
       </c>
       <c r="G85">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
@@ -3451,7 +3451,7 @@
         <v>2</v>
       </c>
       <c r="G86">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
@@ -3888,7 +3888,7 @@
         <v>2</v>
       </c>
       <c r="G105">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
@@ -3911,7 +3911,7 @@
         <v>2</v>
       </c>
       <c r="G106">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.2">
@@ -3934,7 +3934,7 @@
         <v>2</v>
       </c>
       <c r="G107">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
@@ -3957,7 +3957,7 @@
         <v>2</v>
       </c>
       <c r="G108">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
@@ -3980,7 +3980,7 @@
         <v>2</v>
       </c>
       <c r="G109">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
@@ -4003,7 +4003,7 @@
         <v>2</v>
       </c>
       <c r="G110">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.2">
@@ -4026,7 +4026,7 @@
         <v>2</v>
       </c>
       <c r="G111">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
@@ -4049,7 +4049,7 @@
         <v>2</v>
       </c>
       <c r="G112">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
@@ -4072,7 +4072,7 @@
         <v>2</v>
       </c>
       <c r="G113">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
@@ -4095,7 +4095,7 @@
         <v>2</v>
       </c>
       <c r="G114">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
@@ -4118,7 +4118,7 @@
         <v>2</v>
       </c>
       <c r="G115">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
@@ -4141,7 +4141,7 @@
         <v>2</v>
       </c>
       <c r="G116">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
@@ -4164,7 +4164,7 @@
         <v>2</v>
       </c>
       <c r="G117">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
@@ -4187,7 +4187,7 @@
         <v>2</v>
       </c>
       <c r="G118">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
@@ -4210,7 +4210,7 @@
         <v>2</v>
       </c>
       <c r="G119">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
@@ -4233,7 +4233,7 @@
         <v>2</v>
       </c>
       <c r="G120">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
@@ -4256,7 +4256,7 @@
         <v>2</v>
       </c>
       <c r="G121">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
@@ -4279,7 +4279,7 @@
         <v>2</v>
       </c>
       <c r="G122">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
@@ -4302,7 +4302,7 @@
         <v>2</v>
       </c>
       <c r="G123">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
@@ -4325,7 +4325,7 @@
         <v>2</v>
       </c>
       <c r="G124">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
@@ -4348,7 +4348,7 @@
         <v>2</v>
       </c>
       <c r="G125">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
@@ -4371,7 +4371,7 @@
         <v>2</v>
       </c>
       <c r="G126">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
@@ -4394,7 +4394,7 @@
         <v>2</v>
       </c>
       <c r="G127">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
@@ -4417,7 +4417,7 @@
         <v>2</v>
       </c>
       <c r="G128">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
@@ -4440,7 +4440,7 @@
         <v>2</v>
       </c>
       <c r="G129">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
@@ -4463,7 +4463,7 @@
         <v>2</v>
       </c>
       <c r="G130">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
@@ -4486,7 +4486,7 @@
         <v>2</v>
       </c>
       <c r="G131">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
@@ -4509,7 +4509,7 @@
         <v>2</v>
       </c>
       <c r="G132">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
@@ -4532,7 +4532,7 @@
         <v>2</v>
       </c>
       <c r="G133">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
@@ -4555,7 +4555,7 @@
         <v>2</v>
       </c>
       <c r="G134">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
@@ -4578,7 +4578,7 @@
         <v>2</v>
       </c>
       <c r="G135">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
@@ -4601,7 +4601,7 @@
         <v>2</v>
       </c>
       <c r="G136">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
@@ -4624,7 +4624,7 @@
         <v>2</v>
       </c>
       <c r="G137">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
@@ -4647,7 +4647,7 @@
         <v>2</v>
       </c>
       <c r="G138">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
@@ -4670,7 +4670,7 @@
         <v>2</v>
       </c>
       <c r="G139">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
@@ -4693,7 +4693,7 @@
         <v>2</v>
       </c>
       <c r="G140">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
@@ -4716,7 +4716,7 @@
         <v>2</v>
       </c>
       <c r="G141">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
@@ -4739,7 +4739,7 @@
         <v>2</v>
       </c>
       <c r="G142">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
@@ -4762,7 +4762,7 @@
         <v>2</v>
       </c>
       <c r="G143">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
@@ -4785,7 +4785,7 @@
         <v>2</v>
       </c>
       <c r="G144">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
@@ -4808,7 +4808,7 @@
         <v>2</v>
       </c>
       <c r="G145">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
@@ -4831,7 +4831,7 @@
         <v>2</v>
       </c>
       <c r="G146">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
@@ -4854,7 +4854,7 @@
         <v>2</v>
       </c>
       <c r="G147">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
@@ -4877,7 +4877,7 @@
         <v>2</v>
       </c>
       <c r="G148">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
@@ -4900,7 +4900,7 @@
         <v>2</v>
       </c>
       <c r="G149">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
@@ -4923,7 +4923,7 @@
         <v>2</v>
       </c>
       <c r="G150">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
@@ -4946,7 +4946,7 @@
         <v>2</v>
       </c>
       <c r="G151">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
@@ -4969,7 +4969,7 @@
         <v>2</v>
       </c>
       <c r="G152">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
@@ -4992,7 +4992,7 @@
         <v>2</v>
       </c>
       <c r="G153">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
@@ -5061,7 +5061,7 @@
         <v>2</v>
       </c>
       <c r="G156">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
@@ -5084,7 +5084,7 @@
         <v>2</v>
       </c>
       <c r="G157">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.2">
@@ -5107,7 +5107,7 @@
         <v>2</v>
       </c>
       <c r="G158">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
@@ -5130,7 +5130,7 @@
         <v>2</v>
       </c>
       <c r="G159">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
@@ -5153,7 +5153,7 @@
         <v>2</v>
       </c>
       <c r="G160">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.2">
@@ -5176,7 +5176,7 @@
         <v>2</v>
       </c>
       <c r="G161">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
@@ -5199,11 +5199,11 @@
         <v>2</v>
       </c>
       <c r="G162">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G153"/>
+  <autoFilter ref="A3:G162"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/Datas/FormulaData.xlsx
+++ b/Datas/FormulaData.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FormulaData!$A$3:$G$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FormulaData!$A$3:$G$163</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="325">
   <si>
     <t>formulaName</t>
   </si>
@@ -1100,6 +1100,12 @@
   <si>
     <t>3164,3134,1006,4015</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凉茶</t>
+  </si>
+  <si>
+    <t>200,207</t>
   </si>
 </sst>
 </file>
@@ -1489,7 +1495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G162"/>
+  <dimension ref="A2:G163"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -3456,42 +3462,42 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>171</v>
+        <v>323</v>
       </c>
       <c r="B87">
-        <v>2000</v>
+        <v>3092</v>
       </c>
       <c r="C87">
-        <v>3</v>
-      </c>
-      <c r="D87">
-        <v>102</v>
+        <v>15</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>324</v>
       </c>
       <c r="E87">
-        <v>101</v>
+        <v>3179</v>
       </c>
       <c r="F87">
         <v>2</v>
       </c>
       <c r="G87">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B88">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C88">
         <v>3</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>173</v>
+      <c r="D88">
+        <v>102</v>
       </c>
       <c r="E88">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F88">
         <v>2</v>
@@ -3505,13 +3511,13 @@
         <v>172</v>
       </c>
       <c r="B89">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="C89">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E89">
         <v>103</v>
@@ -3524,20 +3530,20 @@
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A90" s="3" t="s">
-        <v>177</v>
+      <c r="A90" t="s">
+        <v>172</v>
       </c>
       <c r="B90">
-        <v>2010</v>
+        <v>2003</v>
       </c>
       <c r="C90">
-        <v>4</v>
-      </c>
-      <c r="D90" s="2">
-        <v>283</v>
-      </c>
-      <c r="E90" s="2">
-        <v>277</v>
+        <v>3</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E90">
+        <v>103</v>
       </c>
       <c r="F90">
         <v>2</v>
@@ -3548,19 +3554,19 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B91">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C91">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D91" s="2">
+        <v>283</v>
+      </c>
+      <c r="E91" s="2">
         <v>277</v>
-      </c>
-      <c r="E91" s="2">
-        <v>204</v>
       </c>
       <c r="F91">
         <v>2</v>
@@ -3571,42 +3577,42 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B92">
+        <v>2011</v>
+      </c>
+      <c r="C92">
+        <v>5</v>
+      </c>
+      <c r="D92" s="2">
+        <v>277</v>
+      </c>
+      <c r="E92" s="2">
+        <v>204</v>
+      </c>
+      <c r="F92">
+        <v>2</v>
+      </c>
+      <c r="G92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B92">
+      <c r="B93">
         <v>2012</v>
       </c>
-      <c r="C92">
+      <c r="C93">
         <v>6</v>
       </c>
-      <c r="D92" s="2">
+      <c r="D93" s="2">
         <v>203</v>
       </c>
-      <c r="E92" s="2">
+      <c r="E93" s="2">
         <v>271</v>
-      </c>
-      <c r="F92">
-        <v>2</v>
-      </c>
-      <c r="G92">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A93" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B93">
-        <v>2100</v>
-      </c>
-      <c r="C93">
-        <v>2</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E93" s="2">
-        <v>4000</v>
       </c>
       <c r="F93">
         <v>2</v>
@@ -3617,19 +3623,19 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B94">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="C94">
         <v>2</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E94" s="2">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="F94">
         <v>2</v>
@@ -3640,19 +3646,19 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B95">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="C95">
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E95" s="2">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="F95">
         <v>2</v>
@@ -3663,19 +3669,19 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B96">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="C96">
         <v>2</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E96" s="2">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="F96">
         <v>2</v>
@@ -3686,19 +3692,19 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B97">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="C97">
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E97" s="2">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="F97">
         <v>2</v>
@@ -3709,19 +3715,19 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B98">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="C98">
         <v>2</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E98" s="2">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="F98">
         <v>2</v>
@@ -3732,19 +3738,19 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B99">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="C99">
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E99" s="2">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="F99">
         <v>2</v>
@@ -3755,19 +3761,19 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B100">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="C100">
         <v>2</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E100" s="2">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="F100">
         <v>2</v>
@@ -3778,19 +3784,19 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B101">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="C101">
         <v>2</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E101" s="2">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="F101">
         <v>2</v>
@@ -3801,19 +3807,19 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B102">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="C102">
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E102" s="2">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="F102">
         <v>2</v>
@@ -3824,19 +3830,19 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B103">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="C103">
         <v>2</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E103" s="2">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="F103">
         <v>2</v>
@@ -3847,65 +3853,65 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B104">
+        <v>2110</v>
+      </c>
+      <c r="C104">
+        <v>2</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E104" s="2">
+        <v>4010</v>
+      </c>
+      <c r="F104">
+        <v>2</v>
+      </c>
+      <c r="G104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="B104">
+      <c r="B105">
         <v>2111</v>
       </c>
-      <c r="C104">
-        <v>2</v>
-      </c>
-      <c r="D104" s="1" t="s">
+      <c r="C105">
+        <v>2</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E104">
+      <c r="E105">
         <v>11</v>
       </c>
-      <c r="F104">
-        <v>2</v>
-      </c>
-      <c r="G104">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A105" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="B105">
-        <v>4000</v>
-      </c>
-      <c r="C105" s="3">
-        <v>0</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="E105" s="9">
-        <v>1600</v>
-      </c>
       <c r="F105">
         <v>2</v>
       </c>
       <c r="G105">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B106">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="C106" s="3">
         <v>0</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E106" s="9">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F106">
         <v>2</v>
@@ -3915,43 +3921,43 @@
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A107" s="6" t="s">
-        <v>204</v>
+      <c r="A107" s="5" t="s">
+        <v>203</v>
       </c>
       <c r="B107">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C107" s="3">
         <v>0</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="E107" s="9">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="F107">
         <v>2</v>
       </c>
       <c r="G107">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A108" s="5" t="s">
-        <v>205</v>
+      <c r="A108" s="6" t="s">
+        <v>204</v>
       </c>
       <c r="B108">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C108" s="3">
         <v>0</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E108" s="9">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="F108">
         <v>2</v>
@@ -3962,19 +3968,19 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B109">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C109" s="3">
         <v>0</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E109" s="9">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="F109">
         <v>2</v>
@@ -3985,65 +3991,65 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B110">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="C110" s="3">
         <v>0</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>298</v>
+        <v>251</v>
       </c>
       <c r="E110" s="9">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="F110">
         <v>2</v>
       </c>
       <c r="G110">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B111">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="C111" s="3">
         <v>0</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>252</v>
+        <v>298</v>
       </c>
       <c r="E111" s="9">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="F111">
         <v>2</v>
       </c>
       <c r="G111">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B112">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="C112" s="3">
         <v>0</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="E112" s="9">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="F112">
         <v>2</v>
@@ -4054,19 +4060,19 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B113">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="C113" s="3">
         <v>0</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="E113" s="9">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="F113">
         <v>2</v>
@@ -4076,43 +4082,43 @@
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A114" s="7" t="s">
-        <v>211</v>
+      <c r="A114" s="5" t="s">
+        <v>210</v>
       </c>
       <c r="B114">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="C114" s="3">
         <v>0</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E114" s="9">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="F114">
         <v>2</v>
       </c>
       <c r="G114">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B115">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="C115" s="3">
         <v>0</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E115" s="9">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="F115">
         <v>2</v>
@@ -4122,66 +4128,66 @@
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A116" s="5" t="s">
-        <v>213</v>
+      <c r="A116" s="7" t="s">
+        <v>212</v>
       </c>
       <c r="B116">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="C116" s="3">
         <v>0</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="E116" s="9">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="F116">
         <v>2</v>
       </c>
       <c r="G116">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B117">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="C117" s="3">
         <v>0</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E117" s="9">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="F117">
         <v>2</v>
       </c>
       <c r="G117">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B118">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="C118" s="3">
         <v>0</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="E118" s="9">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F118">
         <v>2</v>
@@ -4192,65 +4198,65 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B119">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="C119" s="3">
         <v>0</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E119" s="9">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="F119">
         <v>2</v>
       </c>
       <c r="G119">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B120">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="C120" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="E120" s="9">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="F120">
         <v>2</v>
       </c>
       <c r="G120">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B121">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="C121" s="3">
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E121" s="9">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="F121">
         <v>2</v>
@@ -4261,88 +4267,88 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B122">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="C122" s="3">
         <v>1</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E122" s="9">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="F122">
         <v>2</v>
       </c>
       <c r="G122">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B123">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="C123" s="3">
         <v>1</v>
       </c>
       <c r="D123" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E123" s="9">
+        <v>1617</v>
+      </c>
+      <c r="F123">
+        <v>2</v>
+      </c>
+      <c r="G123">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A124" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B124">
+        <v>4018</v>
+      </c>
+      <c r="C124" s="3">
+        <v>1</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="E123" s="9">
+      <c r="E124" s="9">
         <v>1618</v>
       </c>
-      <c r="F123">
-        <v>2</v>
-      </c>
-      <c r="G123">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A124" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="B124">
-        <v>4019</v>
-      </c>
-      <c r="C124" s="3">
-        <v>0</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="E124" s="9">
-        <v>1619</v>
-      </c>
       <c r="F124">
         <v>2</v>
       </c>
       <c r="G124">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B125">
-        <v>4020</v>
+        <v>4019</v>
       </c>
       <c r="C125" s="3">
         <v>0</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E125" s="9">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="F125">
         <v>2</v>
@@ -4352,135 +4358,135 @@
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A126" s="6" t="s">
-        <v>223</v>
+      <c r="A126" s="7" t="s">
+        <v>222</v>
       </c>
       <c r="B126">
-        <v>4021</v>
+        <v>4020</v>
       </c>
       <c r="C126" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="E126" s="9">
-        <v>1650</v>
+        <v>1620</v>
       </c>
       <c r="F126">
         <v>2</v>
       </c>
       <c r="G126">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B127">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="C127" s="3">
         <v>1</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E127" s="9">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="F127">
         <v>2</v>
       </c>
       <c r="G127">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B128">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="C128" s="3">
         <v>1</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E128" s="9">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="F128">
         <v>2</v>
       </c>
       <c r="G128">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B129">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="C129" s="3">
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="E129" s="9">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="F129">
         <v>2</v>
       </c>
       <c r="G129">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="6" t="s">
-        <v>297</v>
+        <v>226</v>
       </c>
       <c r="B130">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="C130" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="E130" s="9">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="F130">
         <v>2</v>
       </c>
       <c r="G130">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="6" t="s">
-        <v>227</v>
+        <v>297</v>
       </c>
       <c r="B131">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="C131" s="3">
         <v>0</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="E131" s="9">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="F131">
         <v>2</v>
@@ -4491,19 +4497,19 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B132">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="C132" s="3">
         <v>0</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="E132" s="9">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="F132">
         <v>2</v>
@@ -4514,88 +4520,88 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B133">
-        <v>4028</v>
+        <v>4027</v>
       </c>
       <c r="C133" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E133" s="9">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="F133">
         <v>2</v>
       </c>
       <c r="G133">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B134">
-        <v>4029</v>
+        <v>4028</v>
       </c>
       <c r="C134" s="3">
         <v>1</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E134" s="9">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="F134">
         <v>2</v>
       </c>
       <c r="G134">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B135">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="C135" s="3">
         <v>1</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>261</v>
+        <v>287</v>
       </c>
       <c r="E135" s="9">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="F135">
         <v>2</v>
       </c>
       <c r="G135">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B136">
-        <v>4031</v>
+        <v>4030</v>
       </c>
       <c r="C136" s="3">
         <v>1</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="E136" s="9">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="F136">
         <v>2</v>
@@ -4606,42 +4612,42 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B137">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="C137" s="3">
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="E137" s="9">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="F137">
         <v>2</v>
       </c>
       <c r="G137">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B138">
-        <v>4033</v>
+        <v>4032</v>
       </c>
       <c r="C138" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E138" s="9">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="F138">
         <v>2</v>
@@ -4652,42 +4658,42 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B139">
-        <v>4034</v>
+        <v>4033</v>
       </c>
       <c r="C139" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>289</v>
+        <v>263</v>
       </c>
       <c r="E139" s="9">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="F139">
         <v>2</v>
       </c>
       <c r="G139">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B140">
-        <v>4035</v>
+        <v>4034</v>
       </c>
       <c r="C140" s="3">
         <v>1</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E140" s="9">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="F140">
         <v>2</v>
@@ -4698,19 +4704,19 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B141">
-        <v>4036</v>
+        <v>4035</v>
       </c>
       <c r="C141" s="3">
         <v>1</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="E141" s="9">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="F141">
         <v>2</v>
@@ -4720,20 +4726,20 @@
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A142" s="8" t="s">
-        <v>238</v>
+      <c r="A142" s="6" t="s">
+        <v>237</v>
       </c>
       <c r="B142">
-        <v>4037</v>
+        <v>4036</v>
       </c>
       <c r="C142" s="3">
         <v>1</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E142" s="9">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="F142">
         <v>2</v>
@@ -4744,42 +4750,42 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B143">
-        <v>4038</v>
+        <v>4037</v>
       </c>
       <c r="C143" s="3">
         <v>1</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>300</v>
+        <v>265</v>
       </c>
       <c r="E143" s="9">
-        <v>1700</v>
+        <v>1666</v>
       </c>
       <c r="F143">
         <v>2</v>
       </c>
       <c r="G143">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B144">
-        <v>4039</v>
+        <v>4038</v>
       </c>
       <c r="C144" s="3">
         <v>1</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="E144" s="9">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="F144">
         <v>2</v>
@@ -4790,42 +4796,42 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
-        <v>296</v>
+        <v>240</v>
       </c>
       <c r="B145">
-        <v>4040</v>
+        <v>4039</v>
       </c>
       <c r="C145" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E145" s="9">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="F145">
         <v>2</v>
       </c>
       <c r="G145">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
-        <v>241</v>
+        <v>296</v>
       </c>
       <c r="B146">
-        <v>4041</v>
+        <v>4040</v>
       </c>
       <c r="C146" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E146" s="9">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="F146">
         <v>2</v>
@@ -4836,134 +4842,134 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B147">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="C147" s="3">
         <v>1</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="E147" s="9">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="F147">
         <v>2</v>
       </c>
       <c r="G147">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B148">
-        <v>4043</v>
+        <v>4042</v>
       </c>
       <c r="C148" s="3">
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="E148" s="9">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="F148">
         <v>2</v>
       </c>
       <c r="G148">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B149">
-        <v>4044</v>
+        <v>4043</v>
       </c>
       <c r="C149" s="3">
         <v>1</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E149" s="9">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="F149">
         <v>2</v>
       </c>
       <c r="G149">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B150">
-        <v>4045</v>
+        <v>4044</v>
       </c>
       <c r="C150" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E150" s="9">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="F150">
         <v>2</v>
       </c>
       <c r="G150">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B151">
-        <v>4046</v>
+        <v>4045</v>
       </c>
       <c r="C151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E151" s="9">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="F151">
         <v>2</v>
       </c>
       <c r="G151">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B152">
-        <v>4047</v>
+        <v>4046</v>
       </c>
       <c r="C152" s="3">
         <v>1</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E152" s="9">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="F152">
         <v>2</v>
@@ -4974,65 +4980,65 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B153">
-        <v>4048</v>
+        <v>4047</v>
       </c>
       <c r="C153" s="3">
         <v>1</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E153" s="9">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="F153">
         <v>2</v>
       </c>
       <c r="G153">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A154" t="s">
-        <v>302</v>
+      <c r="A154" s="8" t="s">
+        <v>248</v>
       </c>
       <c r="B154">
-        <v>4049</v>
+        <v>4048</v>
       </c>
       <c r="C154" s="3">
         <v>1</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E154">
-        <v>1800</v>
+        <v>271</v>
+      </c>
+      <c r="E154" s="9">
+        <v>1710</v>
       </c>
       <c r="F154">
         <v>2</v>
       </c>
       <c r="G154">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B155">
-        <v>4050</v>
+        <v>4049</v>
       </c>
       <c r="C155" s="3">
         <v>1</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E155">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="F155">
         <v>2</v>
@@ -5043,65 +5049,65 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B156">
-        <v>4051</v>
+        <v>4050</v>
       </c>
       <c r="C156" s="3">
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E156">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="F156">
         <v>2</v>
       </c>
       <c r="G156">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B157">
-        <v>4052</v>
+        <v>4051</v>
       </c>
       <c r="C157" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E157">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="F157">
         <v>2</v>
       </c>
       <c r="G157">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B158">
-        <v>4053</v>
+        <v>4052</v>
       </c>
       <c r="C158" s="3">
         <v>0</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E158">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="F158">
         <v>2</v>
@@ -5112,42 +5118,42 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B159">
-        <v>4054</v>
+        <v>4053</v>
       </c>
       <c r="C159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E159">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="F159">
         <v>2</v>
       </c>
       <c r="G159">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B160">
-        <v>4055</v>
+        <v>4054</v>
       </c>
       <c r="C160" s="3">
         <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E160">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="F160">
         <v>2</v>
@@ -5158,19 +5164,19 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B161">
-        <v>4056</v>
+        <v>4055</v>
       </c>
       <c r="C161" s="3">
         <v>1</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E161">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="F161">
         <v>2</v>
@@ -5181,32 +5187,55 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
+        <v>309</v>
+      </c>
+      <c r="B162">
+        <v>4056</v>
+      </c>
+      <c r="C162" s="3">
+        <v>1</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E162">
+        <v>1807</v>
+      </c>
+      <c r="F162">
+        <v>2</v>
+      </c>
+      <c r="G162">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
         <v>310</v>
       </c>
-      <c r="B162">
+      <c r="B163">
         <v>4057</v>
       </c>
-      <c r="C162" s="3">
+      <c r="C163" s="3">
         <v>0</v>
       </c>
-      <c r="D162" s="1" t="s">
+      <c r="D163" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="E162">
+      <c r="E163">
         <v>1808</v>
       </c>
-      <c r="F162">
-        <v>2</v>
-      </c>
-      <c r="G162">
+      <c r="F163">
+        <v>2</v>
+      </c>
+      <c r="G163">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G162"/>
+  <autoFilter ref="A3:G163"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="D13:D73" numberStoredAsText="1"/>
   </ignoredErrors>

--- a/Datas/FormulaData.xlsx
+++ b/Datas/FormulaData.xlsx
@@ -10,6 +10,9 @@
     <sheet name="FormulaData" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FormulaData!$A$3:$G$163</definedName>
   </definedNames>
@@ -138,9 +141,6 @@
     <t>饭团</t>
   </si>
   <si>
-    <t>烤面包</t>
-  </si>
-  <si>
     <t>烤海苔</t>
   </si>
   <si>
@@ -713,9 +713,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>血腥之枪</t>
-  </si>
-  <si>
     <t>骑士长枪</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -751,14 +748,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>藤鞭</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>女王鞭</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>蛇牙鞭</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1039,9 +1028,6 @@
     <t>草帽</t>
   </si>
   <si>
-    <t>暮光草帽</t>
-  </si>
-  <si>
     <t>法师帽</t>
   </si>
   <si>
@@ -1106,6 +1092,25 @@
   </si>
   <si>
     <t>200,207</t>
+  </si>
+  <si>
+    <t>面包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血腥之矛</t>
+  </si>
+  <si>
+    <t>荆棘鞭</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>女王之鞭</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>阳光草帽</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1188,7 +1193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1212,14 +1217,32 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1230,6 +1253,3318 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="ItemData"/>
+      <sheetName val="Sheet4"/>
+      <sheetName val="Sheet13"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet5"/>
+      <sheetName val="植物"/>
+      <sheetName val="动物"/>
+      <sheetName val="装备"/>
+      <sheetName val="Sheet8"/>
+      <sheetName val="材料"/>
+      <sheetName val="食物"/>
+      <sheetName val="鱼"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>未知的物品</v>
+          </cell>
+          <cell r="B4">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>失败的徒手</v>
+          </cell>
+          <cell r="B5">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>失败的搅拌</v>
+          </cell>
+          <cell r="B6">
+            <v>21</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>失败的烘烤</v>
+          </cell>
+          <cell r="B7">
+            <v>22</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>失败的蒸煮</v>
+          </cell>
+          <cell r="B8">
+            <v>23</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>失败的酿造</v>
+          </cell>
+          <cell r="B9">
+            <v>24</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>失败的铸造</v>
+          </cell>
+          <cell r="B10">
+            <v>25</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>失败的缝纫</v>
+          </cell>
+          <cell r="B11">
+            <v>26</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>失败的绘写</v>
+          </cell>
+          <cell r="B12">
+            <v>27</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>传送卷轴</v>
+          </cell>
+          <cell r="B13">
+            <v>11</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14" t="str">
+            <v>鱼饵</v>
+          </cell>
+          <cell r="B14">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15" t="str">
+            <v>食物配方</v>
+          </cell>
+          <cell r="B15">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16" t="str">
+            <v>酒水配方</v>
+          </cell>
+          <cell r="B16">
+            <v>21</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17" t="str">
+            <v>铸造配方</v>
+          </cell>
+          <cell r="B17">
+            <v>22</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18" t="str">
+            <v>缝纫配方</v>
+          </cell>
+          <cell r="B18">
+            <v>23</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19" t="str">
+            <v>书写配方</v>
+          </cell>
+          <cell r="B19">
+            <v>24</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20" t="str">
+            <v>牧草</v>
+          </cell>
+          <cell r="B20">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21" t="str">
+            <v>木材</v>
+          </cell>
+          <cell r="B21">
+            <v>101</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22" t="str">
+            <v>原木</v>
+          </cell>
+          <cell r="B22">
+            <v>102</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23" t="str">
+            <v>木柴</v>
+          </cell>
+          <cell r="B23">
+            <v>103</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24" t="str">
+            <v>木棒</v>
+          </cell>
+          <cell r="B24">
+            <v>104</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25" t="str">
+            <v>干草</v>
+          </cell>
+          <cell r="B25">
+            <v>105</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26" t="str">
+            <v>纯净水</v>
+          </cell>
+          <cell r="B26">
+            <v>200</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27" t="str">
+            <v>石块</v>
+          </cell>
+          <cell r="B27">
+            <v>201</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28" t="str">
+            <v>龟壳</v>
+          </cell>
+          <cell r="B28">
+            <v>202</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29" t="str">
+            <v>兽皮</v>
+          </cell>
+          <cell r="B29">
+            <v>203</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30" t="str">
+            <v>布片</v>
+          </cell>
+          <cell r="B30">
+            <v>204</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31" t="str">
+            <v>石英砂</v>
+          </cell>
+          <cell r="B31">
+            <v>205</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32" t="str">
+            <v>草药茶</v>
+          </cell>
+          <cell r="B32">
+            <v>207</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33" t="str">
+            <v>风晶石</v>
+          </cell>
+          <cell r="B33">
+            <v>208</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34" t="str">
+            <v>琥珀</v>
+          </cell>
+          <cell r="B34">
+            <v>210</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35" t="str">
+            <v>狼牙</v>
+          </cell>
+          <cell r="B35">
+            <v>211</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36" t="str">
+            <v>粘土</v>
+          </cell>
+          <cell r="B36">
+            <v>212</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37" t="str">
+            <v>尖刺</v>
+          </cell>
+          <cell r="B37">
+            <v>213</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38" t="str">
+            <v>蛛丝</v>
+          </cell>
+          <cell r="B38">
+            <v>214</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39" t="str">
+            <v>铁矿</v>
+          </cell>
+          <cell r="B39">
+            <v>215</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40" t="str">
+            <v>盐矿</v>
+          </cell>
+          <cell r="B40">
+            <v>216</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41" t="str">
+            <v>肥皂</v>
+          </cell>
+          <cell r="B41">
+            <v>217</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42" t="str">
+            <v>土晶石</v>
+          </cell>
+          <cell r="B42">
+            <v>218</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43" t="str">
+            <v>迷幻菇</v>
+          </cell>
+          <cell r="B43">
+            <v>219</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44" t="str">
+            <v>眼球</v>
+          </cell>
+          <cell r="B44">
+            <v>220</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45" t="str">
+            <v>植物的藤</v>
+          </cell>
+          <cell r="B45">
+            <v>221</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46" t="str">
+            <v>鹿角</v>
+          </cell>
+          <cell r="B46">
+            <v>222</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47" t="str">
+            <v>魔兽皮毛</v>
+          </cell>
+          <cell r="B47">
+            <v>223</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48" t="str">
+            <v>奇美拉之翼</v>
+          </cell>
+          <cell r="B48">
+            <v>224</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49" t="str">
+            <v>电偶瓶</v>
+          </cell>
+          <cell r="B49">
+            <v>225</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50" t="str">
+            <v>海胆</v>
+          </cell>
+          <cell r="B50">
+            <v>226</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51" t="str">
+            <v>珊瑚</v>
+          </cell>
+          <cell r="B51">
+            <v>227</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52" t="str">
+            <v>彩色羽毛</v>
+          </cell>
+          <cell r="B52">
+            <v>228</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53" t="str">
+            <v>火晶石</v>
+          </cell>
+          <cell r="B53">
+            <v>229</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54" t="str">
+            <v>玻璃瓶</v>
+          </cell>
+          <cell r="B54">
+            <v>230</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55" t="str">
+            <v>水晶石</v>
+          </cell>
+          <cell r="B55">
+            <v>232</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56" t="str">
+            <v>珍珠</v>
+          </cell>
+          <cell r="B56">
+            <v>234</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57" t="str">
+            <v>松果</v>
+          </cell>
+          <cell r="B57">
+            <v>235</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58" t="str">
+            <v>神奇泥浆</v>
+          </cell>
+          <cell r="B58">
+            <v>236</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59" t="str">
+            <v>银块</v>
+          </cell>
+          <cell r="B59">
+            <v>237</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60" t="str">
+            <v>蛇皮</v>
+          </cell>
+          <cell r="B60">
+            <v>238</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61" t="str">
+            <v>蜂刺</v>
+          </cell>
+          <cell r="B61">
+            <v>239</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62" t="str">
+            <v>象牙</v>
+          </cell>
+          <cell r="B62">
+            <v>240</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63" t="str">
+            <v>兽角</v>
+          </cell>
+          <cell r="B63">
+            <v>241</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64" t="str">
+            <v>水晶球</v>
+          </cell>
+          <cell r="B64">
+            <v>242</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65" t="str">
+            <v>蝎尾</v>
+          </cell>
+          <cell r="B65">
+            <v>243</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66" t="str">
+            <v>仙人掌</v>
+          </cell>
+          <cell r="B66">
+            <v>244</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67" t="str">
+            <v>脏绷带</v>
+          </cell>
+          <cell r="B67">
+            <v>245</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68" t="str">
+            <v>幽魂</v>
+          </cell>
+          <cell r="B68">
+            <v>246</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69" t="str">
+            <v>金块</v>
+          </cell>
+          <cell r="B69">
+            <v>247</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="A70" t="str">
+            <v>远古的硬币</v>
+          </cell>
+          <cell r="B70">
+            <v>248</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="A71" t="str">
+            <v>铁钉</v>
+          </cell>
+          <cell r="B71">
+            <v>249</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="A72" t="str">
+            <v>遗骨</v>
+          </cell>
+          <cell r="B72">
+            <v>250</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="A73" t="str">
+            <v>妖精粉</v>
+          </cell>
+          <cell r="B73">
+            <v>251</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="A74" t="str">
+            <v>雪球</v>
+          </cell>
+          <cell r="B74">
+            <v>253</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="A75" t="str">
+            <v>毒淤泥</v>
+          </cell>
+          <cell r="B75">
+            <v>254</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="A76" t="str">
+            <v>亡者之土</v>
+          </cell>
+          <cell r="B76">
+            <v>255</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="A77" t="str">
+            <v>咒术药水</v>
+          </cell>
+          <cell r="B77">
+            <v>256</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="A78" t="str">
+            <v>诅咒宝珠</v>
+          </cell>
+          <cell r="B78">
+            <v>257</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="A79" t="str">
+            <v>人狼之证</v>
+          </cell>
+          <cell r="B79">
+            <v>258</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="A80" t="str">
+            <v>魔族之血</v>
+          </cell>
+          <cell r="B80">
+            <v>259</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="A81" t="str">
+            <v>冰晶石</v>
+          </cell>
+          <cell r="B81">
+            <v>260</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="A82" t="str">
+            <v>冰的结晶</v>
+          </cell>
+          <cell r="B82">
+            <v>261</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="A83" t="str">
+            <v>石化之眼</v>
+          </cell>
+          <cell r="B83">
+            <v>263</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="A84" t="str">
+            <v>夜之幕</v>
+          </cell>
+          <cell r="B84">
+            <v>264</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="A85" t="str">
+            <v>星的眼泪</v>
+          </cell>
+          <cell r="B85">
+            <v>265</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="A86" t="str">
+            <v>冰牛角</v>
+          </cell>
+          <cell r="B86">
+            <v>266</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="A87" t="str">
+            <v>寒冰气息</v>
+          </cell>
+          <cell r="B87">
+            <v>267</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="A88" t="str">
+            <v>寒冰火种</v>
+          </cell>
+          <cell r="B88">
+            <v>268</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="A89" t="str">
+            <v>幻影水晶</v>
+          </cell>
+          <cell r="B89">
+            <v>269</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="A90" t="str">
+            <v>雷鸣宝珠</v>
+          </cell>
+          <cell r="B90">
+            <v>270</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="A91" t="str">
+            <v>皮革</v>
+          </cell>
+          <cell r="B91">
+            <v>271</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="A92" t="str">
+            <v>彩色的布</v>
+          </cell>
+          <cell r="B92">
+            <v>272</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="A93" t="str">
+            <v>鳞片</v>
+          </cell>
+          <cell r="B93">
+            <v>273</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="A94" t="str">
+            <v>刀刃</v>
+          </cell>
+          <cell r="B94">
+            <v>274</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="A95" t="str">
+            <v>骑士之证</v>
+          </cell>
+          <cell r="B95">
+            <v>275</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="A96" t="str">
+            <v>马尾</v>
+          </cell>
+          <cell r="B96">
+            <v>276</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="A97" t="str">
+            <v>毛线</v>
+          </cell>
+          <cell r="B97">
+            <v>277</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="A98" t="str">
+            <v>粘液</v>
+          </cell>
+          <cell r="B98">
+            <v>278</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="A99" t="str">
+            <v>贵族徽章</v>
+          </cell>
+          <cell r="B99">
+            <v>279</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="A100" t="str">
+            <v>武道精华</v>
+          </cell>
+          <cell r="B100">
+            <v>280</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="A101" t="str">
+            <v>贤者晶石</v>
+          </cell>
+          <cell r="B101">
+            <v>281</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="A102" t="str">
+            <v>防水皮革</v>
+          </cell>
+          <cell r="B102">
+            <v>282</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="A103" t="str">
+            <v>羊毛</v>
+          </cell>
+          <cell r="B103">
+            <v>283</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="A104" t="str">
+            <v>白磷粉末</v>
+          </cell>
+          <cell r="B104">
+            <v>284</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="A105" t="str">
+            <v>暮光结晶</v>
+          </cell>
+          <cell r="B105">
+            <v>285</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="A106" t="str">
+            <v>魔力之土</v>
+          </cell>
+          <cell r="B106">
+            <v>286</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="A107" t="str">
+            <v>迷幻孢子</v>
+          </cell>
+          <cell r="B107">
+            <v>287</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="A108" t="str">
+            <v>力量果实</v>
+          </cell>
+          <cell r="B108">
+            <v>288</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="A109" t="str">
+            <v>恶魔花瓣</v>
+          </cell>
+          <cell r="B109">
+            <v>289</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="A110" t="str">
+            <v>月之光华</v>
+          </cell>
+          <cell r="B110">
+            <v>290</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="A111" t="str">
+            <v>萤火树汁</v>
+          </cell>
+          <cell r="B111">
+            <v>291</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="A112" t="str">
+            <v>暗夜之露</v>
+          </cell>
+          <cell r="B112">
+            <v>292</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="A113" t="str">
+            <v>魅惑药水</v>
+          </cell>
+          <cell r="B113">
+            <v>293</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="A114" t="str">
+            <v>图腾号角</v>
+          </cell>
+          <cell r="B114">
+            <v>294</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="A115" t="str">
+            <v>空白卷轴</v>
+          </cell>
+          <cell r="B115">
+            <v>295</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="A116" t="str">
+            <v>废铁</v>
+          </cell>
+          <cell r="B116">
+            <v>296</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="A117" t="str">
+            <v>焦炭</v>
+          </cell>
+          <cell r="B117">
+            <v>297</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="A118" t="str">
+            <v>铁块</v>
+          </cell>
+          <cell r="B118">
+            <v>298</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="A119" t="str">
+            <v>钢</v>
+          </cell>
+          <cell r="B119">
+            <v>299</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="A120" t="str">
+            <v>猪粪</v>
+          </cell>
+          <cell r="B120">
+            <v>300</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="A121" t="str">
+            <v>鸭绒</v>
+          </cell>
+          <cell r="B121">
+            <v>301</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="A122" t="str">
+            <v>兔子脚</v>
+          </cell>
+          <cell r="B122">
+            <v>302</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="A123" t="str">
+            <v>芜菁</v>
+          </cell>
+          <cell r="B123">
+            <v>1001</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="A124" t="str">
+            <v>卷心菜</v>
+          </cell>
+          <cell r="B124">
+            <v>1002</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="A125" t="str">
+            <v>葱</v>
+          </cell>
+          <cell r="B125">
+            <v>1003</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="A126" t="str">
+            <v>萝卜</v>
+          </cell>
+          <cell r="B126">
+            <v>1004</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="A127" t="str">
+            <v>紫甘蓝</v>
+          </cell>
+          <cell r="B127">
+            <v>1005</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="A128" t="str">
+            <v>黄瓜</v>
+          </cell>
+          <cell r="B128">
+            <v>1006</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="A129" t="str">
+            <v>西兰花</v>
+          </cell>
+          <cell r="B129">
+            <v>1007</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="A130" t="str">
+            <v>番茄</v>
+          </cell>
+          <cell r="B130">
+            <v>1008</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="A131" t="str">
+            <v>胡萝卜</v>
+          </cell>
+          <cell r="B131">
+            <v>1009</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="A132" t="str">
+            <v>西瓜</v>
+          </cell>
+          <cell r="B132">
+            <v>1010</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="A133" t="str">
+            <v>辣椒</v>
+          </cell>
+          <cell r="B133">
+            <v>1011</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="A134" t="str">
+            <v>奇异果</v>
+          </cell>
+          <cell r="B134">
+            <v>1012</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="A135" t="str">
+            <v>茄子</v>
+          </cell>
+          <cell r="B135">
+            <v>1013</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="A136" t="str">
+            <v>豌豆</v>
+          </cell>
+          <cell r="B136">
+            <v>1014</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="A137" t="str">
+            <v>土豆</v>
+          </cell>
+          <cell r="B137">
+            <v>1015</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="A138" t="str">
+            <v>大蒜</v>
+          </cell>
+          <cell r="B138">
+            <v>1016</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="A139" t="str">
+            <v>芦笋</v>
+          </cell>
+          <cell r="B139">
+            <v>1017</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="A140" t="str">
+            <v>南瓜</v>
+          </cell>
+          <cell r="B140">
+            <v>1018</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="A141" t="str">
+            <v>玉米</v>
+          </cell>
+          <cell r="B141">
+            <v>1019</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="A142" t="str">
+            <v>大麦</v>
+          </cell>
+          <cell r="B142">
+            <v>1020</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="A143" t="str">
+            <v>啤酒花</v>
+          </cell>
+          <cell r="B143">
+            <v>1021</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="A144" t="str">
+            <v>葡萄</v>
+          </cell>
+          <cell r="B144">
+            <v>1022</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="A145" t="str">
+            <v>菠萝</v>
+          </cell>
+          <cell r="B145">
+            <v>1023</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="A146" t="str">
+            <v>咖啡</v>
+          </cell>
+          <cell r="B146">
+            <v>1024</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="A147" t="str">
+            <v>草莓</v>
+          </cell>
+          <cell r="B147">
+            <v>1025</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="A148" t="str">
+            <v>蓝莓</v>
+          </cell>
+          <cell r="B148">
+            <v>1026</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="A149" t="str">
+            <v>红薯</v>
+          </cell>
+          <cell r="B149">
+            <v>1027</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="A150" t="str">
+            <v>甜菜</v>
+          </cell>
+          <cell r="B150">
+            <v>1028</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="A151" t="str">
+            <v>芜菁种子</v>
+          </cell>
+          <cell r="B151">
+            <v>1101</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="A152" t="str">
+            <v>卷心菜种子</v>
+          </cell>
+          <cell r="B152">
+            <v>1102</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="A153" t="str">
+            <v>葱种子</v>
+          </cell>
+          <cell r="B153">
+            <v>1103</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="A154" t="str">
+            <v>萝卜种子</v>
+          </cell>
+          <cell r="B154">
+            <v>1104</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="A155" t="str">
+            <v>紫甘蓝种子</v>
+          </cell>
+          <cell r="B155">
+            <v>1105</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="A156" t="str">
+            <v>黄瓜种子</v>
+          </cell>
+          <cell r="B156">
+            <v>1106</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="A157" t="str">
+            <v>西兰花种子</v>
+          </cell>
+          <cell r="B157">
+            <v>1107</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="A158" t="str">
+            <v>番茄种子</v>
+          </cell>
+          <cell r="B158">
+            <v>1108</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="A159" t="str">
+            <v>胡萝卜种子</v>
+          </cell>
+          <cell r="B159">
+            <v>1109</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="A160" t="str">
+            <v>西瓜种子</v>
+          </cell>
+          <cell r="B160">
+            <v>1110</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="A161" t="str">
+            <v>辣椒种子</v>
+          </cell>
+          <cell r="B161">
+            <v>1111</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="A162" t="str">
+            <v>奇异果种子</v>
+          </cell>
+          <cell r="B162">
+            <v>1112</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="A163" t="str">
+            <v>茄子种子</v>
+          </cell>
+          <cell r="B163">
+            <v>1113</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="A164" t="str">
+            <v>豌豆种子</v>
+          </cell>
+          <cell r="B164">
+            <v>1114</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="A165" t="str">
+            <v>土豆种子</v>
+          </cell>
+          <cell r="B165">
+            <v>1115</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="A166" t="str">
+            <v>大蒜种子</v>
+          </cell>
+          <cell r="B166">
+            <v>1116</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="A167" t="str">
+            <v>芦笋种子</v>
+          </cell>
+          <cell r="B167">
+            <v>1117</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="A168" t="str">
+            <v>南瓜种子</v>
+          </cell>
+          <cell r="B168">
+            <v>1118</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="A169" t="str">
+            <v>玉米种子</v>
+          </cell>
+          <cell r="B169">
+            <v>1119</v>
+          </cell>
+        </row>
+        <row r="170">
+          <cell r="A170" t="str">
+            <v>大麦种子</v>
+          </cell>
+          <cell r="B170">
+            <v>1120</v>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="A171" t="str">
+            <v>啤酒花种子</v>
+          </cell>
+          <cell r="B171">
+            <v>1121</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="A172" t="str">
+            <v>葡萄种子</v>
+          </cell>
+          <cell r="B172">
+            <v>1122</v>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="A173" t="str">
+            <v>菠萝种子</v>
+          </cell>
+          <cell r="B173">
+            <v>1123</v>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="A174" t="str">
+            <v>咖啡种子</v>
+          </cell>
+          <cell r="B174">
+            <v>1124</v>
+          </cell>
+        </row>
+        <row r="175">
+          <cell r="A175" t="str">
+            <v>草莓种子</v>
+          </cell>
+          <cell r="B175">
+            <v>1125</v>
+          </cell>
+        </row>
+        <row r="176">
+          <cell r="A176" t="str">
+            <v>蓝莓种子</v>
+          </cell>
+          <cell r="B176">
+            <v>1126</v>
+          </cell>
+        </row>
+        <row r="177">
+          <cell r="A177" t="str">
+            <v>红薯种子</v>
+          </cell>
+          <cell r="B177">
+            <v>1127</v>
+          </cell>
+        </row>
+        <row r="178">
+          <cell r="A178" t="str">
+            <v>甜菜种子</v>
+          </cell>
+          <cell r="B178">
+            <v>1128</v>
+          </cell>
+        </row>
+        <row r="179">
+          <cell r="A179" t="str">
+            <v>长剑</v>
+          </cell>
+          <cell r="B179">
+            <v>1600</v>
+          </cell>
+        </row>
+        <row r="180">
+          <cell r="A180" t="str">
+            <v>诅咒之剑</v>
+          </cell>
+          <cell r="B180">
+            <v>1601</v>
+          </cell>
+        </row>
+        <row r="181">
+          <cell r="A181" t="str">
+            <v>烈焰之刃</v>
+          </cell>
+          <cell r="B181">
+            <v>1602</v>
+          </cell>
+        </row>
+        <row r="182">
+          <cell r="A182" t="str">
+            <v>大地之剑</v>
+          </cell>
+          <cell r="B182">
+            <v>1603</v>
+          </cell>
+        </row>
+        <row r="183">
+          <cell r="A183" t="str">
+            <v>冰之刃</v>
+          </cell>
+          <cell r="B183">
+            <v>1604</v>
+          </cell>
+        </row>
+        <row r="184">
+          <cell r="A184" t="str">
+            <v>铁枪</v>
+          </cell>
+          <cell r="B184">
+            <v>1605</v>
+          </cell>
+        </row>
+        <row r="185">
+          <cell r="A185" t="str">
+            <v>骑士长枪</v>
+          </cell>
+          <cell r="B185">
+            <v>1606</v>
+          </cell>
+        </row>
+        <row r="186">
+          <cell r="A186" t="str">
+            <v>血腥之矛</v>
+          </cell>
+          <cell r="B186">
+            <v>1607</v>
+          </cell>
+        </row>
+        <row r="187">
+          <cell r="A187" t="str">
+            <v>三叉戟</v>
+          </cell>
+          <cell r="B187">
+            <v>1608</v>
+          </cell>
+        </row>
+        <row r="188">
+          <cell r="A188" t="str">
+            <v>战斧</v>
+          </cell>
+          <cell r="B188">
+            <v>1609</v>
+          </cell>
+        </row>
+        <row r="189">
+          <cell r="A189" t="str">
+            <v>毒蜥之牙</v>
+          </cell>
+          <cell r="B189">
+            <v>1610</v>
+          </cell>
+        </row>
+        <row r="190">
+          <cell r="A190" t="str">
+            <v>恶魔之斧</v>
+          </cell>
+          <cell r="B190">
+            <v>1611</v>
+          </cell>
+        </row>
+        <row r="191">
+          <cell r="A191" t="str">
+            <v>蛇皮鞭</v>
+          </cell>
+          <cell r="B191">
+            <v>1612</v>
+          </cell>
+        </row>
+        <row r="192">
+          <cell r="A192" t="str">
+            <v>荆棘鞭</v>
+          </cell>
+          <cell r="B192">
+            <v>1613</v>
+          </cell>
+        </row>
+        <row r="193">
+          <cell r="A193" t="str">
+            <v>女王之鞭</v>
+          </cell>
+          <cell r="B193">
+            <v>1614</v>
+          </cell>
+        </row>
+        <row r="194">
+          <cell r="A194" t="str">
+            <v>蛇牙鞭</v>
+          </cell>
+          <cell r="B194">
+            <v>1615</v>
+          </cell>
+        </row>
+        <row r="195">
+          <cell r="A195" t="str">
+            <v>暴雪斧</v>
+          </cell>
+          <cell r="B195">
+            <v>1616</v>
+          </cell>
+        </row>
+        <row r="196">
+          <cell r="A196" t="str">
+            <v>秘银长剑</v>
+          </cell>
+          <cell r="B196">
+            <v>1617</v>
+          </cell>
+        </row>
+        <row r="197">
+          <cell r="A197" t="str">
+            <v>幻影长枪</v>
+          </cell>
+          <cell r="B197">
+            <v>1618</v>
+          </cell>
+        </row>
+        <row r="198">
+          <cell r="A198" t="str">
+            <v>雷神之鞭</v>
+          </cell>
+          <cell r="B198">
+            <v>1619</v>
+          </cell>
+        </row>
+        <row r="199">
+          <cell r="A199" t="str">
+            <v>死亡之鞭</v>
+          </cell>
+          <cell r="B199">
+            <v>1620</v>
+          </cell>
+        </row>
+        <row r="200">
+          <cell r="A200" t="str">
+            <v>布衣</v>
+          </cell>
+          <cell r="B200">
+            <v>1650</v>
+          </cell>
+        </row>
+        <row r="201">
+          <cell r="A201" t="str">
+            <v>皮铠</v>
+          </cell>
+          <cell r="B201">
+            <v>1651</v>
+          </cell>
+        </row>
+        <row r="202">
+          <cell r="A202" t="str">
+            <v>锁子甲</v>
+          </cell>
+          <cell r="B202">
+            <v>1652</v>
+          </cell>
+        </row>
+        <row r="203">
+          <cell r="A203" t="str">
+            <v>毛皮斗篷</v>
+          </cell>
+          <cell r="B203">
+            <v>1653</v>
+          </cell>
+        </row>
+        <row r="204">
+          <cell r="A204" t="str">
+            <v>铁铠甲</v>
+          </cell>
+          <cell r="B204">
+            <v>1654</v>
+          </cell>
+        </row>
+        <row r="205">
+          <cell r="A205" t="str">
+            <v>红莲之铠</v>
+          </cell>
+          <cell r="B205">
+            <v>1655</v>
+          </cell>
+        </row>
+        <row r="206">
+          <cell r="A206" t="str">
+            <v>铁龟铠</v>
+          </cell>
+          <cell r="B206">
+            <v>1656</v>
+          </cell>
+        </row>
+        <row r="207">
+          <cell r="A207" t="str">
+            <v>华丽背心</v>
+          </cell>
+          <cell r="B207">
+            <v>1657</v>
+          </cell>
+        </row>
+        <row r="208">
+          <cell r="A208" t="str">
+            <v>鳞铠</v>
+          </cell>
+          <cell r="B208">
+            <v>1658</v>
+          </cell>
+        </row>
+        <row r="209">
+          <cell r="A209" t="str">
+            <v>暗之袍</v>
+          </cell>
+          <cell r="B209">
+            <v>1659</v>
+          </cell>
+        </row>
+        <row r="210">
+          <cell r="A210" t="str">
+            <v>疾风背心</v>
+          </cell>
+          <cell r="B210">
+            <v>1660</v>
+          </cell>
+        </row>
+        <row r="211">
+          <cell r="A211" t="str">
+            <v>魔法铠甲</v>
+          </cell>
+          <cell r="B211">
+            <v>1661</v>
+          </cell>
+        </row>
+        <row r="212">
+          <cell r="A212" t="str">
+            <v>钢刃锁甲</v>
+          </cell>
+          <cell r="B212">
+            <v>1662</v>
+          </cell>
+        </row>
+        <row r="213">
+          <cell r="A213" t="str">
+            <v>丝织长袍</v>
+          </cell>
+          <cell r="B213">
+            <v>1663</v>
+          </cell>
+        </row>
+        <row r="214">
+          <cell r="A214" t="str">
+            <v>水之羽衣</v>
+          </cell>
+          <cell r="B214">
+            <v>1664</v>
+          </cell>
+        </row>
+        <row r="215">
+          <cell r="A215" t="str">
+            <v>贵族长裙</v>
+          </cell>
+          <cell r="B215">
+            <v>1665</v>
+          </cell>
+        </row>
+        <row r="216">
+          <cell r="A216" t="str">
+            <v>幸运之衣</v>
+          </cell>
+          <cell r="B216">
+            <v>1666</v>
+          </cell>
+        </row>
+        <row r="217">
+          <cell r="A217" t="str">
+            <v>布鞋</v>
+          </cell>
+          <cell r="B217">
+            <v>1700</v>
+          </cell>
+        </row>
+        <row r="218">
+          <cell r="A218" t="str">
+            <v>皮鞋</v>
+          </cell>
+          <cell r="B218">
+            <v>1701</v>
+          </cell>
+        </row>
+        <row r="219">
+          <cell r="A219" t="str">
+            <v>士兵长靴</v>
+          </cell>
+          <cell r="B219">
+            <v>1702</v>
+          </cell>
+        </row>
+        <row r="220">
+          <cell r="A220" t="str">
+            <v>登山者之靴</v>
+          </cell>
+          <cell r="B220">
+            <v>1703</v>
+          </cell>
+        </row>
+        <row r="221">
+          <cell r="A221" t="str">
+            <v>运动鞋</v>
+          </cell>
+          <cell r="B221">
+            <v>1704</v>
+          </cell>
+        </row>
+        <row r="222">
+          <cell r="A222" t="str">
+            <v>贵族长靴</v>
+          </cell>
+          <cell r="B222">
+            <v>1705</v>
+          </cell>
+        </row>
+        <row r="223">
+          <cell r="A223" t="str">
+            <v>武道鞋</v>
+          </cell>
+          <cell r="B223">
+            <v>1706</v>
+          </cell>
+        </row>
+        <row r="224">
+          <cell r="A224" t="str">
+            <v>骑士护胫</v>
+          </cell>
+          <cell r="B224">
+            <v>1707</v>
+          </cell>
+        </row>
+        <row r="225">
+          <cell r="A225" t="str">
+            <v>贤者之履</v>
+          </cell>
+          <cell r="B225">
+            <v>1708</v>
+          </cell>
+        </row>
+        <row r="226">
+          <cell r="A226" t="str">
+            <v>风神之履</v>
+          </cell>
+          <cell r="B226">
+            <v>1709</v>
+          </cell>
+        </row>
+        <row r="227">
+          <cell r="A227" t="str">
+            <v>踏浪长靴</v>
+          </cell>
+          <cell r="B227">
+            <v>1710</v>
+          </cell>
+        </row>
+        <row r="228">
+          <cell r="A228" t="str">
+            <v>草帽</v>
+          </cell>
+          <cell r="B228">
+            <v>1800</v>
+          </cell>
+        </row>
+        <row r="229">
+          <cell r="A229" t="str">
+            <v>阳光草帽</v>
+          </cell>
+          <cell r="B229">
+            <v>1801</v>
+          </cell>
+        </row>
+        <row r="230">
+          <cell r="A230" t="str">
+            <v>法师帽</v>
+          </cell>
+          <cell r="B230">
+            <v>1802</v>
+          </cell>
+        </row>
+        <row r="231">
+          <cell r="A231" t="str">
+            <v>士兵头盔</v>
+          </cell>
+          <cell r="B231">
+            <v>1803</v>
+          </cell>
+        </row>
+        <row r="232">
+          <cell r="A232" t="str">
+            <v>尖角头盔</v>
+          </cell>
+          <cell r="B232">
+            <v>1804</v>
+          </cell>
+        </row>
+        <row r="233">
+          <cell r="A233" t="str">
+            <v>幸运头巾</v>
+          </cell>
+          <cell r="B233">
+            <v>1805</v>
+          </cell>
+        </row>
+        <row r="234">
+          <cell r="A234" t="str">
+            <v>绅士礼帽</v>
+          </cell>
+          <cell r="B234">
+            <v>1806</v>
+          </cell>
+        </row>
+        <row r="235">
+          <cell r="A235" t="str">
+            <v>贵族头巾</v>
+          </cell>
+          <cell r="B235">
+            <v>1807</v>
+          </cell>
+        </row>
+        <row r="236">
+          <cell r="A236" t="str">
+            <v>战争头盔</v>
+          </cell>
+          <cell r="B236">
+            <v>1808</v>
+          </cell>
+        </row>
+        <row r="237">
+          <cell r="A237" t="str">
+            <v>锄头</v>
+          </cell>
+          <cell r="B237">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="238">
+          <cell r="A238" t="str">
+            <v>铁皮壶</v>
+          </cell>
+          <cell r="B238">
+            <v>2001</v>
+          </cell>
+        </row>
+        <row r="239">
+          <cell r="A239" t="str">
+            <v>斧头</v>
+          </cell>
+          <cell r="B239">
+            <v>2002</v>
+          </cell>
+        </row>
+        <row r="240">
+          <cell r="A240" t="str">
+            <v>镰刀</v>
+          </cell>
+          <cell r="B240">
+            <v>2003</v>
+          </cell>
+        </row>
+        <row r="241">
+          <cell r="A241" t="str">
+            <v>鱼竿</v>
+          </cell>
+          <cell r="B241">
+            <v>2004</v>
+          </cell>
+        </row>
+        <row r="242">
+          <cell r="A242" t="str">
+            <v>缝纫机</v>
+          </cell>
+          <cell r="B242">
+            <v>2100</v>
+          </cell>
+        </row>
+        <row r="243">
+          <cell r="A243" t="str">
+            <v>锻造炉</v>
+          </cell>
+          <cell r="B243">
+            <v>2101</v>
+          </cell>
+        </row>
+        <row r="244">
+          <cell r="A244" t="str">
+            <v>烘烤炉</v>
+          </cell>
+          <cell r="B244">
+            <v>2102</v>
+          </cell>
+        </row>
+        <row r="245">
+          <cell r="A245" t="str">
+            <v>炖煮锅</v>
+          </cell>
+          <cell r="B245">
+            <v>2103</v>
+          </cell>
+        </row>
+        <row r="246">
+          <cell r="A246" t="str">
+            <v>冷餐台</v>
+          </cell>
+          <cell r="B246">
+            <v>2104</v>
+          </cell>
+        </row>
+        <row r="247">
+          <cell r="A247" t="str">
+            <v>酿造桶</v>
+          </cell>
+          <cell r="B247">
+            <v>2105</v>
+          </cell>
+        </row>
+        <row r="248">
+          <cell r="A248" t="str">
+            <v>绘写台</v>
+          </cell>
+          <cell r="B248">
+            <v>2106</v>
+          </cell>
+        </row>
+        <row r="249">
+          <cell r="A249" t="str">
+            <v>冰箱</v>
+          </cell>
+          <cell r="B249">
+            <v>2107</v>
+          </cell>
+        </row>
+        <row r="250">
+          <cell r="A250" t="str">
+            <v>储物箱(木)</v>
+          </cell>
+          <cell r="B250">
+            <v>2108</v>
+          </cell>
+        </row>
+        <row r="251">
+          <cell r="A251" t="str">
+            <v>储物箱(银)</v>
+          </cell>
+          <cell r="B251">
+            <v>2109</v>
+          </cell>
+        </row>
+        <row r="252">
+          <cell r="A252" t="str">
+            <v>储物箱(金)</v>
+          </cell>
+          <cell r="B252">
+            <v>2110</v>
+          </cell>
+        </row>
+        <row r="253">
+          <cell r="A253" t="str">
+            <v>普通柜台</v>
+          </cell>
+          <cell r="B253">
+            <v>2111</v>
+          </cell>
+        </row>
+        <row r="254">
+          <cell r="A254" t="str">
+            <v>服饰架</v>
+          </cell>
+          <cell r="B254">
+            <v>2113</v>
+          </cell>
+        </row>
+        <row r="255">
+          <cell r="A255" t="str">
+            <v>搅拌器</v>
+          </cell>
+          <cell r="B255">
+            <v>2114</v>
+          </cell>
+        </row>
+        <row r="256">
+          <cell r="A256" t="str">
+            <v>银皮壶</v>
+          </cell>
+          <cell r="B256">
+            <v>2115</v>
+          </cell>
+        </row>
+        <row r="257">
+          <cell r="A257" t="str">
+            <v>金皮壶</v>
+          </cell>
+          <cell r="B257">
+            <v>2116</v>
+          </cell>
+        </row>
+        <row r="258">
+          <cell r="A258" t="str">
+            <v>双人床</v>
+          </cell>
+          <cell r="B258">
+            <v>2200</v>
+          </cell>
+        </row>
+        <row r="259">
+          <cell r="A259" t="str">
+            <v>沙发(红)</v>
+          </cell>
+          <cell r="B259">
+            <v>2201</v>
+          </cell>
+        </row>
+        <row r="260">
+          <cell r="A260" t="str">
+            <v>沙发(蓝)</v>
+          </cell>
+          <cell r="B260">
+            <v>2202</v>
+          </cell>
+        </row>
+        <row r="261">
+          <cell r="A261" t="str">
+            <v>盆栽1</v>
+          </cell>
+          <cell r="B261">
+            <v>2203</v>
+          </cell>
+        </row>
+        <row r="262">
+          <cell r="A262" t="str">
+            <v>盆栽2</v>
+          </cell>
+          <cell r="B262">
+            <v>2204</v>
+          </cell>
+        </row>
+        <row r="263">
+          <cell r="A263" t="str">
+            <v>盆栽3</v>
+          </cell>
+          <cell r="B263">
+            <v>2205</v>
+          </cell>
+        </row>
+        <row r="264">
+          <cell r="A264" t="str">
+            <v>盆栽4</v>
+          </cell>
+          <cell r="B264">
+            <v>2206</v>
+          </cell>
+        </row>
+        <row r="265">
+          <cell r="A265" t="str">
+            <v>盆栽5</v>
+          </cell>
+          <cell r="B265">
+            <v>2207</v>
+          </cell>
+        </row>
+        <row r="266">
+          <cell r="A266" t="str">
+            <v>盆栽6</v>
+          </cell>
+          <cell r="B266">
+            <v>2208</v>
+          </cell>
+        </row>
+        <row r="267">
+          <cell r="A267" t="str">
+            <v>壁炉</v>
+          </cell>
+          <cell r="B267">
+            <v>2209</v>
+          </cell>
+        </row>
+        <row r="268">
+          <cell r="A268" t="str">
+            <v>鲫鱼</v>
+          </cell>
+          <cell r="B268">
+            <v>4000</v>
+          </cell>
+        </row>
+        <row r="269">
+          <cell r="A269" t="str">
+            <v>小龙虾</v>
+          </cell>
+          <cell r="B269">
+            <v>4003</v>
+          </cell>
+        </row>
+        <row r="270">
+          <cell r="A270" t="str">
+            <v>鲤鱼</v>
+          </cell>
+          <cell r="B270">
+            <v>4004</v>
+          </cell>
+        </row>
+        <row r="271">
+          <cell r="A271" t="str">
+            <v>鲮鱼</v>
+          </cell>
+          <cell r="B271">
+            <v>4006</v>
+          </cell>
+        </row>
+        <row r="272">
+          <cell r="A272" t="str">
+            <v>河蟹</v>
+          </cell>
+          <cell r="B272">
+            <v>4007</v>
+          </cell>
+        </row>
+        <row r="273">
+          <cell r="A273" t="str">
+            <v>鲶鱼</v>
+          </cell>
+          <cell r="B273">
+            <v>4008</v>
+          </cell>
+        </row>
+        <row r="274">
+          <cell r="A274" t="str">
+            <v>丁鱼</v>
+          </cell>
+          <cell r="B274">
+            <v>4009</v>
+          </cell>
+        </row>
+        <row r="275">
+          <cell r="A275" t="str">
+            <v>锦鲤</v>
+          </cell>
+          <cell r="B275">
+            <v>4010</v>
+          </cell>
+        </row>
+        <row r="276">
+          <cell r="A276" t="str">
+            <v>金线鱼</v>
+          </cell>
+          <cell r="B276">
+            <v>4011</v>
+          </cell>
+        </row>
+        <row r="277">
+          <cell r="A277" t="str">
+            <v>梭鲈</v>
+          </cell>
+          <cell r="B277">
+            <v>4012</v>
+          </cell>
+        </row>
+        <row r="278">
+          <cell r="A278" t="str">
+            <v>兰寿金鱼</v>
+          </cell>
+          <cell r="B278">
+            <v>4013</v>
+          </cell>
+        </row>
+        <row r="279">
+          <cell r="A279" t="str">
+            <v>樱桃鲑鱼</v>
+          </cell>
+          <cell r="B279">
+            <v>4014</v>
+          </cell>
+        </row>
+        <row r="280">
+          <cell r="A280" t="str">
+            <v>虹鳟鱼</v>
+          </cell>
+          <cell r="B280">
+            <v>4015</v>
+          </cell>
+        </row>
+        <row r="281">
+          <cell r="A281" t="str">
+            <v>鲷鱼</v>
+          </cell>
+          <cell r="B281">
+            <v>4016</v>
+          </cell>
+        </row>
+        <row r="282">
+          <cell r="A282" t="str">
+            <v>金鳟鱼</v>
+          </cell>
+          <cell r="B282">
+            <v>4017</v>
+          </cell>
+        </row>
+        <row r="283">
+          <cell r="A283" t="str">
+            <v>霓虹脂鲤</v>
+          </cell>
+          <cell r="B283">
+            <v>4018</v>
+          </cell>
+        </row>
+        <row r="284">
+          <cell r="A284" t="str">
+            <v>桃花鱼</v>
+          </cell>
+          <cell r="B284">
+            <v>4020</v>
+          </cell>
+        </row>
+        <row r="285">
+          <cell r="A285" t="str">
+            <v>鲑鱼</v>
+          </cell>
+          <cell r="B285">
+            <v>4021</v>
+          </cell>
+        </row>
+        <row r="286">
+          <cell r="A286" t="str">
+            <v>孔雀鱼</v>
+          </cell>
+          <cell r="B286">
+            <v>4022</v>
+          </cell>
+        </row>
+        <row r="287">
+          <cell r="A287" t="str">
+            <v>银龙鱼</v>
+          </cell>
+          <cell r="B287">
+            <v>4023</v>
+          </cell>
+        </row>
+        <row r="288">
+          <cell r="A288" t="str">
+            <v>洞穴天使鱼</v>
+          </cell>
+          <cell r="B288">
+            <v>4024</v>
+          </cell>
+        </row>
+        <row r="289">
+          <cell r="A289" t="str">
+            <v>沙丁鱼</v>
+          </cell>
+          <cell r="B289">
+            <v>4100</v>
+          </cell>
+        </row>
+        <row r="290">
+          <cell r="A290" t="str">
+            <v>竹荚鱼</v>
+          </cell>
+          <cell r="B290">
+            <v>4101</v>
+          </cell>
+        </row>
+        <row r="291">
+          <cell r="A291" t="str">
+            <v>海鳗</v>
+          </cell>
+          <cell r="B291">
+            <v>4103</v>
+          </cell>
+        </row>
+        <row r="292">
+          <cell r="A292" t="str">
+            <v>章鱼</v>
+          </cell>
+          <cell r="B292">
+            <v>4105</v>
+          </cell>
+        </row>
+        <row r="293">
+          <cell r="A293" t="str">
+            <v>比目鱼</v>
+          </cell>
+          <cell r="B293">
+            <v>4106</v>
+          </cell>
+        </row>
+        <row r="294">
+          <cell r="A294" t="str">
+            <v>河豚</v>
+          </cell>
+          <cell r="B294">
+            <v>4109</v>
+          </cell>
+        </row>
+        <row r="295">
+          <cell r="A295" t="str">
+            <v>水母</v>
+          </cell>
+          <cell r="B295">
+            <v>4110</v>
+          </cell>
+        </row>
+        <row r="296">
+          <cell r="A296" t="str">
+            <v>条石鲷</v>
+          </cell>
+          <cell r="B296">
+            <v>4111</v>
+          </cell>
+        </row>
+        <row r="297">
+          <cell r="A297" t="str">
+            <v>红鲷鱼</v>
+          </cell>
+          <cell r="B297">
+            <v>4112</v>
+          </cell>
+        </row>
+        <row r="298">
+          <cell r="A298" t="str">
+            <v>蓝蟹</v>
+          </cell>
+          <cell r="B298">
+            <v>4113</v>
+          </cell>
+        </row>
+        <row r="299">
+          <cell r="A299" t="str">
+            <v>鲯鳅鱼</v>
+          </cell>
+          <cell r="B299">
+            <v>4114</v>
+          </cell>
+        </row>
+        <row r="300">
+          <cell r="A300" t="str">
+            <v>龙虾</v>
+          </cell>
+          <cell r="B300">
+            <v>4115</v>
+          </cell>
+        </row>
+        <row r="301">
+          <cell r="A301" t="str">
+            <v>金枪鱼</v>
+          </cell>
+          <cell r="B301">
+            <v>4116</v>
+          </cell>
+        </row>
+        <row r="302">
+          <cell r="A302" t="str">
+            <v>斑马狮子鱼</v>
+          </cell>
+          <cell r="B302">
+            <v>4117</v>
+          </cell>
+        </row>
+        <row r="303">
+          <cell r="A303" t="str">
+            <v>米饭</v>
+          </cell>
+          <cell r="B303">
+            <v>3000</v>
+          </cell>
+        </row>
+        <row r="304">
+          <cell r="A304" t="str">
+            <v>发酵粉</v>
+          </cell>
+          <cell r="B304">
+            <v>3001</v>
+          </cell>
+        </row>
+        <row r="305">
+          <cell r="A305" t="str">
+            <v>盐</v>
+          </cell>
+          <cell r="B305">
+            <v>3002</v>
+          </cell>
+        </row>
+        <row r="306">
+          <cell r="A306" t="str">
+            <v>酸味香料</v>
+          </cell>
+          <cell r="B306">
+            <v>3003</v>
+          </cell>
+        </row>
+        <row r="307">
+          <cell r="A307" t="str">
+            <v>蜂蜜</v>
+          </cell>
+          <cell r="B307">
+            <v>3005</v>
+          </cell>
+        </row>
+        <row r="308">
+          <cell r="A308" t="str">
+            <v>牛奶</v>
+          </cell>
+          <cell r="B308">
+            <v>3006</v>
+          </cell>
+        </row>
+        <row r="309">
+          <cell r="A309" t="str">
+            <v>鸡蛋</v>
+          </cell>
+          <cell r="B309">
+            <v>3007</v>
+          </cell>
+        </row>
+        <row r="310">
+          <cell r="A310" t="str">
+            <v>猪肉</v>
+          </cell>
+          <cell r="B310">
+            <v>3008</v>
+          </cell>
+        </row>
+        <row r="311">
+          <cell r="A311" t="str">
+            <v>面粉</v>
+          </cell>
+          <cell r="B311">
+            <v>3009</v>
+          </cell>
+        </row>
+        <row r="312">
+          <cell r="A312" t="str">
+            <v>咖啡粉</v>
+          </cell>
+          <cell r="B312">
+            <v>3010</v>
+          </cell>
+        </row>
+        <row r="313">
+          <cell r="A313" t="str">
+            <v>海苔</v>
+          </cell>
+          <cell r="B313">
+            <v>3011</v>
+          </cell>
+        </row>
+        <row r="314">
+          <cell r="A314" t="str">
+            <v>黄油</v>
+          </cell>
+          <cell r="B314">
+            <v>3011</v>
+          </cell>
+        </row>
+        <row r="315">
+          <cell r="A315" t="str">
+            <v>腌芜菁</v>
+          </cell>
+          <cell r="B315">
+            <v>3100</v>
+          </cell>
+        </row>
+        <row r="316">
+          <cell r="A316" t="str">
+            <v>蔬菜沙拉</v>
+          </cell>
+          <cell r="B316">
+            <v>3101</v>
+          </cell>
+        </row>
+        <row r="317">
+          <cell r="A317" t="str">
+            <v>三明治</v>
+          </cell>
+          <cell r="B317">
+            <v>3102</v>
+          </cell>
+        </row>
+        <row r="318">
+          <cell r="A318" t="str">
+            <v>腌萝卜</v>
+          </cell>
+          <cell r="B318">
+            <v>3103</v>
+          </cell>
+        </row>
+        <row r="319">
+          <cell r="A319" t="str">
+            <v>拉面</v>
+          </cell>
+          <cell r="B319">
+            <v>3104</v>
+          </cell>
+        </row>
+        <row r="320">
+          <cell r="A320" t="str">
+            <v>蜂蜜蛋糕</v>
+          </cell>
+          <cell r="B320">
+            <v>3105</v>
+          </cell>
+        </row>
+        <row r="321">
+          <cell r="A321" t="str">
+            <v>披萨</v>
+          </cell>
+          <cell r="B321">
+            <v>3106</v>
+          </cell>
+        </row>
+        <row r="322">
+          <cell r="A322" t="str">
+            <v>腌黄瓜</v>
+          </cell>
+          <cell r="B322">
+            <v>3107</v>
+          </cell>
+        </row>
+        <row r="323">
+          <cell r="A323" t="str">
+            <v>烤西兰花</v>
+          </cell>
+          <cell r="B323">
+            <v>3108</v>
+          </cell>
+        </row>
+        <row r="324">
+          <cell r="A324" t="str">
+            <v>水煮蛋</v>
+          </cell>
+          <cell r="B324">
+            <v>3109</v>
+          </cell>
+        </row>
+        <row r="325">
+          <cell r="A325" t="str">
+            <v>烤肉串</v>
+          </cell>
+          <cell r="B325">
+            <v>3110</v>
+          </cell>
+        </row>
+        <row r="326">
+          <cell r="A326" t="str">
+            <v>饭团</v>
+          </cell>
+          <cell r="B326">
+            <v>3111</v>
+          </cell>
+        </row>
+        <row r="327">
+          <cell r="A327" t="str">
+            <v>面包</v>
+          </cell>
+          <cell r="B327">
+            <v>3112</v>
+          </cell>
+        </row>
+        <row r="328">
+          <cell r="A328" t="str">
+            <v>烤海苔</v>
+          </cell>
+          <cell r="B328">
+            <v>3113</v>
+          </cell>
+        </row>
+        <row r="329">
+          <cell r="A329" t="str">
+            <v>烤肉饼</v>
+          </cell>
+          <cell r="B329">
+            <v>3114</v>
+          </cell>
+        </row>
+        <row r="330">
+          <cell r="A330" t="str">
+            <v>汉堡</v>
+          </cell>
+          <cell r="B330">
+            <v>3115</v>
+          </cell>
+        </row>
+        <row r="331">
+          <cell r="A331" t="str">
+            <v>辣蟹堡</v>
+          </cell>
+          <cell r="B331">
+            <v>3116</v>
+          </cell>
+        </row>
+        <row r="332">
+          <cell r="A332" t="str">
+            <v>土豆泥</v>
+          </cell>
+          <cell r="B332">
+            <v>3117</v>
+          </cell>
+        </row>
+        <row r="333">
+          <cell r="A333" t="str">
+            <v>海鲜饭</v>
+          </cell>
+          <cell r="B333">
+            <v>3118</v>
+          </cell>
+        </row>
+        <row r="334">
+          <cell r="A334" t="str">
+            <v>烤玉米</v>
+          </cell>
+          <cell r="B334">
+            <v>3119</v>
+          </cell>
+        </row>
+        <row r="335">
+          <cell r="A335" t="str">
+            <v>蔬菜汁</v>
+          </cell>
+          <cell r="B335">
+            <v>3120</v>
+          </cell>
+        </row>
+        <row r="336">
+          <cell r="A336" t="str">
+            <v>西瓜果汁</v>
+          </cell>
+          <cell r="B336">
+            <v>3121</v>
+          </cell>
+        </row>
+        <row r="337">
+          <cell r="A337" t="str">
+            <v>奇异果汁</v>
+          </cell>
+          <cell r="B337">
+            <v>3122</v>
+          </cell>
+        </row>
+        <row r="338">
+          <cell r="A338" t="str">
+            <v>葡萄汁</v>
+          </cell>
+          <cell r="B338">
+            <v>3123</v>
+          </cell>
+        </row>
+        <row r="339">
+          <cell r="A339" t="str">
+            <v>菠萝汁</v>
+          </cell>
+          <cell r="B339">
+            <v>3124</v>
+          </cell>
+        </row>
+        <row r="340">
+          <cell r="A340" t="str">
+            <v>草莓汁</v>
+          </cell>
+          <cell r="B340">
+            <v>3125</v>
+          </cell>
+        </row>
+        <row r="341">
+          <cell r="A341" t="str">
+            <v>蓝莓汁</v>
+          </cell>
+          <cell r="B341">
+            <v>3126</v>
+          </cell>
+        </row>
+        <row r="342">
+          <cell r="A342" t="str">
+            <v>玉米汁</v>
+          </cell>
+          <cell r="B342">
+            <v>3127</v>
+          </cell>
+        </row>
+        <row r="343">
+          <cell r="A343" t="str">
+            <v>烤蜜薯</v>
+          </cell>
+          <cell r="B343">
+            <v>3128</v>
+          </cell>
+        </row>
+        <row r="344">
+          <cell r="A344" t="str">
+            <v>甜菜汁</v>
+          </cell>
+          <cell r="B344">
+            <v>3129</v>
+          </cell>
+        </row>
+        <row r="345">
+          <cell r="A345" t="str">
+            <v>奶酪</v>
+          </cell>
+          <cell r="B345">
+            <v>3130</v>
+          </cell>
+        </row>
+        <row r="346">
+          <cell r="A346" t="str">
+            <v>烤茄子</v>
+          </cell>
+          <cell r="B346">
+            <v>3131</v>
+          </cell>
+        </row>
+        <row r="347">
+          <cell r="A347" t="str">
+            <v>饺子</v>
+          </cell>
+          <cell r="B347">
+            <v>3132</v>
+          </cell>
+        </row>
+        <row r="348">
+          <cell r="A348" t="str">
+            <v>炖菜</v>
+          </cell>
+          <cell r="B348">
+            <v>3133</v>
+          </cell>
+        </row>
+        <row r="349">
+          <cell r="A349" t="str">
+            <v>烤芦笋</v>
+          </cell>
+          <cell r="B349">
+            <v>3134</v>
+          </cell>
+        </row>
+        <row r="350">
+          <cell r="A350" t="str">
+            <v>红菜汤</v>
+          </cell>
+          <cell r="B350">
+            <v>3135</v>
+          </cell>
+        </row>
+        <row r="351">
+          <cell r="A351" t="str">
+            <v>豌豆汤</v>
+          </cell>
+          <cell r="B351">
+            <v>3136</v>
+          </cell>
+        </row>
+        <row r="352">
+          <cell r="A352" t="str">
+            <v>草莓牛奶</v>
+          </cell>
+          <cell r="B352">
+            <v>3137</v>
+          </cell>
+        </row>
+        <row r="353">
+          <cell r="A353" t="str">
+            <v>莓莓果汁</v>
+          </cell>
+          <cell r="B353">
+            <v>3138</v>
+          </cell>
+        </row>
+        <row r="354">
+          <cell r="A354" t="str">
+            <v>鲑鱼饭团</v>
+          </cell>
+          <cell r="B354">
+            <v>3139</v>
+          </cell>
+        </row>
+        <row r="355">
+          <cell r="A355" t="str">
+            <v>拿铁</v>
+          </cell>
+          <cell r="B355">
+            <v>3140</v>
+          </cell>
+        </row>
+        <row r="356">
+          <cell r="A356" t="str">
+            <v>黑咖啡</v>
+          </cell>
+          <cell r="B356">
+            <v>3141</v>
+          </cell>
+        </row>
+        <row r="357">
+          <cell r="A357" t="str">
+            <v>葡萄酒</v>
+          </cell>
+          <cell r="B357">
+            <v>3142</v>
+          </cell>
+        </row>
+        <row r="358">
+          <cell r="A358" t="str">
+            <v>伏特加</v>
+          </cell>
+          <cell r="B358">
+            <v>3143</v>
+          </cell>
+        </row>
+        <row r="359">
+          <cell r="A359" t="str">
+            <v>啤酒</v>
+          </cell>
+          <cell r="B359">
+            <v>3144</v>
+          </cell>
+        </row>
+        <row r="360">
+          <cell r="A360" t="str">
+            <v>朗姆</v>
+          </cell>
+          <cell r="B360">
+            <v>3145</v>
+          </cell>
+        </row>
+        <row r="361">
+          <cell r="A361" t="str">
+            <v>野蜂拉格</v>
+          </cell>
+          <cell r="B361">
+            <v>3146</v>
+          </cell>
+        </row>
+        <row r="362">
+          <cell r="A362" t="str">
+            <v>双莓白兰地</v>
+          </cell>
+          <cell r="B362">
+            <v>3147</v>
+          </cell>
+        </row>
+        <row r="363">
+          <cell r="A363" t="str">
+            <v>绯红之吻</v>
+          </cell>
+          <cell r="B363">
+            <v>3148</v>
+          </cell>
+        </row>
+        <row r="364">
+          <cell r="A364" t="str">
+            <v>阳光男孩</v>
+          </cell>
+          <cell r="B364">
+            <v>3149</v>
+          </cell>
+        </row>
+        <row r="365">
+          <cell r="A365" t="str">
+            <v>盐烤鲮鱼</v>
+          </cell>
+          <cell r="B365">
+            <v>3150</v>
+          </cell>
+        </row>
+        <row r="366">
+          <cell r="A366" t="str">
+            <v>盐烤丁鱼</v>
+          </cell>
+          <cell r="B366">
+            <v>3151</v>
+          </cell>
+        </row>
+        <row r="367">
+          <cell r="A367" t="str">
+            <v>盐烤虹鳟鱼</v>
+          </cell>
+          <cell r="B367">
+            <v>3152</v>
+          </cell>
+        </row>
+        <row r="368">
+          <cell r="A368" t="str">
+            <v>烤鲷鱼</v>
+          </cell>
+          <cell r="B368">
+            <v>3153</v>
+          </cell>
+        </row>
+        <row r="369">
+          <cell r="A369" t="str">
+            <v>盐烤金鳟鱼</v>
+          </cell>
+          <cell r="B369">
+            <v>3154</v>
+          </cell>
+        </row>
+        <row r="370">
+          <cell r="A370" t="str">
+            <v>盐烤鲑鱼</v>
+          </cell>
+          <cell r="B370">
+            <v>3155</v>
+          </cell>
+        </row>
+        <row r="371">
+          <cell r="A371" t="str">
+            <v>烤沙丁鱼串</v>
+          </cell>
+          <cell r="B371">
+            <v>3156</v>
+          </cell>
+        </row>
+        <row r="372">
+          <cell r="A372" t="str">
+            <v>烤竹荚鱼</v>
+          </cell>
+          <cell r="B372">
+            <v>3157</v>
+          </cell>
+        </row>
+        <row r="373">
+          <cell r="A373" t="str">
+            <v>烤海鳗</v>
+          </cell>
+          <cell r="B373">
+            <v>3158</v>
+          </cell>
+        </row>
+        <row r="374">
+          <cell r="A374" t="str">
+            <v>烤比目鱼</v>
+          </cell>
+          <cell r="B374">
+            <v>3159</v>
+          </cell>
+        </row>
+        <row r="375">
+          <cell r="A375" t="str">
+            <v>烤河豚鱼</v>
+          </cell>
+          <cell r="B375">
+            <v>3160</v>
+          </cell>
+        </row>
+        <row r="376">
+          <cell r="A376" t="str">
+            <v>烤条石鲷</v>
+          </cell>
+          <cell r="B376">
+            <v>3161</v>
+          </cell>
+        </row>
+        <row r="377">
+          <cell r="A377" t="str">
+            <v>烤红鲷鱼</v>
+          </cell>
+          <cell r="B377">
+            <v>3162</v>
+          </cell>
+        </row>
+        <row r="378">
+          <cell r="A378" t="str">
+            <v>烤蓝蟹</v>
+          </cell>
+          <cell r="B378">
+            <v>3163</v>
+          </cell>
+        </row>
+        <row r="379">
+          <cell r="A379" t="str">
+            <v>烤龙虾</v>
+          </cell>
+          <cell r="B379">
+            <v>3164</v>
+          </cell>
+        </row>
+        <row r="380">
+          <cell r="A380" t="str">
+            <v>烤金枪鱼</v>
+          </cell>
+          <cell r="B380">
+            <v>3165</v>
+          </cell>
+        </row>
+        <row r="381">
+          <cell r="A381" t="str">
+            <v>煮蟹肉</v>
+          </cell>
+          <cell r="B381">
+            <v>3166</v>
+          </cell>
+        </row>
+        <row r="382">
+          <cell r="A382" t="str">
+            <v>海鲜浓汤</v>
+          </cell>
+          <cell r="B382">
+            <v>3167</v>
+          </cell>
+        </row>
+        <row r="383">
+          <cell r="A383" t="str">
+            <v>鳗鱼饭</v>
+          </cell>
+          <cell r="B383">
+            <v>3168</v>
+          </cell>
+        </row>
+        <row r="384">
+          <cell r="A384" t="str">
+            <v>鲫鱼蔬菜汤</v>
+          </cell>
+          <cell r="B384">
+            <v>3169</v>
+          </cell>
+        </row>
+        <row r="385">
+          <cell r="A385" t="str">
+            <v>鲮鱼丸</v>
+          </cell>
+          <cell r="B385">
+            <v>3170</v>
+          </cell>
+        </row>
+        <row r="386">
+          <cell r="A386" t="str">
+            <v>鲑鱼刺身</v>
+          </cell>
+          <cell r="B386">
+            <v>3171</v>
+          </cell>
+        </row>
+        <row r="387">
+          <cell r="A387" t="str">
+            <v>章鱼小丸子</v>
+          </cell>
+          <cell r="B387">
+            <v>3172</v>
+          </cell>
+        </row>
+        <row r="388">
+          <cell r="A388" t="str">
+            <v>炖煮条石鲷</v>
+          </cell>
+          <cell r="B388">
+            <v>3173</v>
+          </cell>
+        </row>
+        <row r="389">
+          <cell r="A389" t="str">
+            <v>红鲷刺身</v>
+          </cell>
+          <cell r="B389">
+            <v>3174</v>
+          </cell>
+        </row>
+        <row r="390">
+          <cell r="A390" t="str">
+            <v>河豚刺身</v>
+          </cell>
+          <cell r="B390">
+            <v>3175</v>
+          </cell>
+        </row>
+        <row r="391">
+          <cell r="A391" t="str">
+            <v>螃蟹煲</v>
+          </cell>
+          <cell r="B391">
+            <v>3176</v>
+          </cell>
+        </row>
+        <row r="392">
+          <cell r="A392" t="str">
+            <v>金枪鱼刺身</v>
+          </cell>
+          <cell r="B392">
+            <v>3177</v>
+          </cell>
+        </row>
+        <row r="393">
+          <cell r="A393" t="str">
+            <v>龙虾鱼子酱</v>
+          </cell>
+          <cell r="B393">
+            <v>3178</v>
+          </cell>
+        </row>
+        <row r="394">
+          <cell r="A394" t="str">
+            <v>凉茶</v>
+          </cell>
+          <cell r="B394">
+            <v>3179</v>
+          </cell>
+        </row>
+        <row r="395">
+          <cell r="A395" t="str">
+            <v>鸡</v>
+          </cell>
+          <cell r="B395">
+            <v>3500</v>
+          </cell>
+        </row>
+        <row r="396">
+          <cell r="A396" t="str">
+            <v>鸭</v>
+          </cell>
+          <cell r="B396">
+            <v>3501</v>
+          </cell>
+        </row>
+        <row r="397">
+          <cell r="A397" t="str">
+            <v>家兔</v>
+          </cell>
+          <cell r="B397">
+            <v>3502</v>
+          </cell>
+        </row>
+        <row r="398">
+          <cell r="A398" t="str">
+            <v>绵羊</v>
+          </cell>
+          <cell r="B398">
+            <v>3503</v>
+          </cell>
+        </row>
+        <row r="399">
+          <cell r="A399" t="str">
+            <v>奶牛</v>
+          </cell>
+          <cell r="B399">
+            <v>3504</v>
+          </cell>
+        </row>
+        <row r="400">
+          <cell r="A400" t="str">
+            <v>猪</v>
+          </cell>
+          <cell r="B400">
+            <v>3505</v>
+          </cell>
+        </row>
+        <row r="401">
+          <cell r="A401" t="str">
+            <v>马</v>
+          </cell>
+          <cell r="B401">
+            <v>3506</v>
+          </cell>
+        </row>
+        <row r="402">
+          <cell r="A402" t="str">
+            <v>回春卷轴</v>
+          </cell>
+          <cell r="B402">
+            <v>5000</v>
+          </cell>
+        </row>
+        <row r="403">
+          <cell r="A403" t="str">
+            <v>振奋卷轴</v>
+          </cell>
+          <cell r="B403">
+            <v>5001</v>
+          </cell>
+        </row>
+        <row r="404">
+          <cell r="A404" t="str">
+            <v>昏睡卷轴</v>
+          </cell>
+          <cell r="B404">
+            <v>5002</v>
+          </cell>
+        </row>
+        <row r="405">
+          <cell r="A405" t="str">
+            <v>感电卷轴</v>
+          </cell>
+          <cell r="B405">
+            <v>5003</v>
+          </cell>
+        </row>
+        <row r="406">
+          <cell r="A406" t="str">
+            <v>冰氛卷轴</v>
+          </cell>
+          <cell r="B406">
+            <v>5004</v>
+          </cell>
+        </row>
+        <row r="407">
+          <cell r="A407" t="str">
+            <v>火氛卷轴</v>
+          </cell>
+          <cell r="B407">
+            <v>5005</v>
+          </cell>
+        </row>
+        <row r="408">
+          <cell r="A408" t="str">
+            <v>沉默卷轴</v>
+          </cell>
+          <cell r="B408">
+            <v>5006</v>
+          </cell>
+        </row>
+        <row r="409">
+          <cell r="A409" t="str">
+            <v>减速卷轴</v>
+          </cell>
+          <cell r="B409">
+            <v>5007</v>
+          </cell>
+        </row>
+        <row r="410">
+          <cell r="A410" t="str">
+            <v>闪避卷轴</v>
+          </cell>
+          <cell r="B410">
+            <v>5008</v>
+          </cell>
+        </row>
+        <row r="411">
+          <cell r="A411" t="str">
+            <v>力量卷轴</v>
+          </cell>
+          <cell r="B411">
+            <v>5009</v>
+          </cell>
+        </row>
+        <row r="412">
+          <cell r="A412" t="str">
+            <v>魅惑卷轴</v>
+          </cell>
+          <cell r="B412">
+            <v>5010</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1562,9 +4897,10 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E4">
+        <f>VLOOKUP(A4,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3009</v>
       </c>
       <c r="F4">
@@ -1585,9 +4921,10 @@
         <v>10</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E5">
+        <f>VLOOKUP(A5,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3010</v>
       </c>
       <c r="F5">
@@ -1599,7 +4936,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B6">
         <v>3011</v>
@@ -1608,9 +4945,10 @@
         <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E6" s="2">
+        <v>175</v>
+      </c>
+      <c r="E6">
+        <f>VLOOKUP(A6,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3002</v>
       </c>
       <c r="F6">
@@ -1631,9 +4969,10 @@
         <v>11</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E7">
+        <f>VLOOKUP(A7,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3011</v>
       </c>
       <c r="F7">
@@ -1654,9 +4993,10 @@
         <v>11</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E8">
+        <f>VLOOKUP(A8,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3100</v>
       </c>
       <c r="F8">
@@ -1677,9 +5017,10 @@
         <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E9">
+        <f>VLOOKUP(A9,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3101</v>
       </c>
       <c r="F9">
@@ -1700,9 +5041,10 @@
         <v>11</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E10">
+        <f>VLOOKUP(A10,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3102</v>
       </c>
       <c r="F10">
@@ -1723,9 +5065,10 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E11">
+        <f>VLOOKUP(A11,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3103</v>
       </c>
       <c r="F11">
@@ -1746,9 +5089,10 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E12">
+        <f>VLOOKUP(A12,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3104</v>
       </c>
       <c r="F12">
@@ -1769,9 +5113,10 @@
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E13">
+        <f>VLOOKUP(A13,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3105</v>
       </c>
       <c r="F13">
@@ -1792,9 +5137,10 @@
         <v>13</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E14">
+        <f>VLOOKUP(A14,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3106</v>
       </c>
       <c r="F14">
@@ -1815,9 +5161,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E15">
+        <f>VLOOKUP(A15,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3107</v>
       </c>
       <c r="F15">
@@ -1838,9 +5185,10 @@
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E16">
+        <f>VLOOKUP(A16,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3108</v>
       </c>
       <c r="F16">
@@ -1861,9 +5209,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E17">
+        <f>VLOOKUP(A17,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3109</v>
       </c>
       <c r="F17">
@@ -1884,9 +5233,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E18">
+        <f>VLOOKUP(A18,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3110</v>
       </c>
       <c r="F18">
@@ -1907,9 +5257,10 @@
         <v>11</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E19">
+        <f>VLOOKUP(A19,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3111</v>
       </c>
       <c r="F19">
@@ -1921,7 +5272,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>320</v>
       </c>
       <c r="B20">
         <v>3025</v>
@@ -1930,9 +5281,10 @@
         <v>13</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E20">
+        <f>VLOOKUP(A20,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3112</v>
       </c>
       <c r="F20">
@@ -1944,7 +5296,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21">
         <v>3026</v>
@@ -1953,9 +5305,10 @@
         <v>13</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E21">
+        <f>VLOOKUP(A21,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3113</v>
       </c>
       <c r="F21">
@@ -1967,7 +5320,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22">
         <v>3027</v>
@@ -1976,9 +5329,10 @@
         <v>13</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E22">
+        <f>VLOOKUP(A22,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3114</v>
       </c>
       <c r="F22">
@@ -1990,7 +5344,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23">
         <v>3028</v>
@@ -1999,9 +5353,10 @@
         <v>11</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E23">
+        <f>VLOOKUP(A23,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3115</v>
       </c>
       <c r="F23">
@@ -2013,7 +5368,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B24">
         <v>3029</v>
@@ -2022,9 +5377,10 @@
         <v>11</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E24">
+        <f>VLOOKUP(A24,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3116</v>
       </c>
       <c r="F24">
@@ -2036,7 +5392,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25">
         <v>3030</v>
@@ -2045,9 +5401,10 @@
         <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E25">
+        <f>VLOOKUP(A25,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3117</v>
       </c>
       <c r="F25">
@@ -2059,7 +5416,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26">
         <v>3031</v>
@@ -2068,9 +5425,10 @@
         <v>12</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E26">
+        <f>VLOOKUP(A26,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3118</v>
       </c>
       <c r="F26">
@@ -2082,7 +5440,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27">
         <v>3032</v>
@@ -2091,9 +5449,10 @@
         <v>13</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E27">
+        <f>VLOOKUP(A27,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3119</v>
       </c>
       <c r="F27">
@@ -2105,7 +5464,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28">
         <v>3033</v>
@@ -2114,9 +5473,10 @@
         <v>15</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E28">
+        <f>VLOOKUP(A28,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3120</v>
       </c>
       <c r="F28">
@@ -2128,7 +5488,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29">
         <v>3034</v>
@@ -2137,9 +5497,10 @@
         <v>15</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E29">
+        <f>VLOOKUP(A29,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3121</v>
       </c>
       <c r="F29">
@@ -2151,7 +5512,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30">
         <v>3035</v>
@@ -2160,9 +5521,10 @@
         <v>15</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E30">
+        <f>VLOOKUP(A30,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3122</v>
       </c>
       <c r="F30">
@@ -2174,7 +5536,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31">
         <v>3036</v>
@@ -2183,9 +5545,10 @@
         <v>15</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E31">
+        <f>VLOOKUP(A31,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3123</v>
       </c>
       <c r="F31">
@@ -2197,7 +5560,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B32">
         <v>3037</v>
@@ -2206,9 +5569,10 @@
         <v>15</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E32">
+        <f>VLOOKUP(A32,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3124</v>
       </c>
       <c r="F32">
@@ -2220,7 +5584,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33">
         <v>3038</v>
@@ -2229,9 +5593,10 @@
         <v>15</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E33">
+        <f>VLOOKUP(A33,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3125</v>
       </c>
       <c r="F33">
@@ -2243,7 +5608,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34">
         <v>3039</v>
@@ -2252,9 +5617,10 @@
         <v>15</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E34">
+        <f>VLOOKUP(A34,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3126</v>
       </c>
       <c r="F34">
@@ -2266,7 +5632,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35">
         <v>3040</v>
@@ -2275,9 +5641,10 @@
         <v>15</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E35">
+        <f>VLOOKUP(A35,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3127</v>
       </c>
       <c r="F35">
@@ -2289,7 +5656,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36">
         <v>3041</v>
@@ -2298,9 +5665,10 @@
         <v>13</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E36">
+        <f>VLOOKUP(A36,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3128</v>
       </c>
       <c r="F36">
@@ -2312,7 +5680,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B37">
         <v>3042</v>
@@ -2321,9 +5689,10 @@
         <v>15</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E37">
+        <f>VLOOKUP(A37,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3129</v>
       </c>
       <c r="F37">
@@ -2335,7 +5704,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B38">
         <v>3043</v>
@@ -2344,9 +5713,10 @@
         <v>14</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E38">
+        <f>VLOOKUP(A38,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3130</v>
       </c>
       <c r="F38">
@@ -2358,7 +5728,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B39">
         <v>3044</v>
@@ -2367,9 +5737,10 @@
         <v>13</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E39">
+        <f>VLOOKUP(A39,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3131</v>
       </c>
       <c r="F39">
@@ -2381,7 +5752,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B40">
         <v>3045</v>
@@ -2390,9 +5761,10 @@
         <v>12</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E40">
+        <f>VLOOKUP(A40,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3132</v>
       </c>
       <c r="F40">
@@ -2404,7 +5776,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B41">
         <v>3046</v>
@@ -2413,9 +5785,10 @@
         <v>12</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E41">
+        <f>VLOOKUP(A41,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3133</v>
       </c>
       <c r="F41">
@@ -2427,7 +5800,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42">
         <v>3047</v>
@@ -2436,9 +5809,10 @@
         <v>13</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E42">
+        <f>VLOOKUP(A42,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3134</v>
       </c>
       <c r="F42">
@@ -2450,7 +5824,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B43">
         <v>3048</v>
@@ -2459,9 +5833,10 @@
         <v>12</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E43">
+        <f>VLOOKUP(A43,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3135</v>
       </c>
       <c r="F43">
@@ -2473,7 +5848,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B44">
         <v>3049</v>
@@ -2482,9 +5857,10 @@
         <v>12</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E44">
+        <f>VLOOKUP(A44,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3136</v>
       </c>
       <c r="F44">
@@ -2496,7 +5872,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B45">
         <v>3050</v>
@@ -2505,9 +5881,10 @@
         <v>15</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E45">
+        <f>VLOOKUP(A45,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3137</v>
       </c>
       <c r="F45">
@@ -2519,7 +5896,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B46">
         <v>3051</v>
@@ -2528,9 +5905,10 @@
         <v>15</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E46">
+        <f>VLOOKUP(A46,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3138</v>
       </c>
       <c r="F46">
@@ -2542,7 +5920,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B47">
         <v>3052</v>
@@ -2551,9 +5929,10 @@
         <v>11</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E47">
+        <f>VLOOKUP(A47,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3139</v>
       </c>
       <c r="F47">
@@ -2565,7 +5944,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B48">
         <v>3053</v>
@@ -2574,9 +5953,10 @@
         <v>15</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E48">
+        <f>VLOOKUP(A48,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3140</v>
       </c>
       <c r="F48">
@@ -2588,7 +5968,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B49">
         <v>3054</v>
@@ -2597,9 +5977,10 @@
         <v>15</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E49">
+        <f>VLOOKUP(A49,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3141</v>
       </c>
       <c r="F49">
@@ -2611,7 +5992,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B50">
         <v>3055</v>
@@ -2620,9 +6001,10 @@
         <v>14</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E50">
+        <f>VLOOKUP(A50,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3142</v>
       </c>
       <c r="F50">
@@ -2634,7 +6016,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B51">
         <v>3056</v>
@@ -2643,9 +6025,10 @@
         <v>14</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E51">
+        <f>VLOOKUP(A51,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3143</v>
       </c>
       <c r="F51">
@@ -2657,7 +6040,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B52">
         <v>3057</v>
@@ -2666,9 +6049,10 @@
         <v>14</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E52">
+        <f>VLOOKUP(A52,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3144</v>
       </c>
       <c r="F52">
@@ -2680,7 +6064,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B53">
         <v>3058</v>
@@ -2689,9 +6073,10 @@
         <v>14</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E53">
+        <f>VLOOKUP(A53,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3145</v>
       </c>
       <c r="F53">
@@ -2703,7 +6088,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B54">
         <v>3059</v>
@@ -2712,9 +6097,10 @@
         <v>14</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E54">
+        <f>VLOOKUP(A54,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3146</v>
       </c>
       <c r="F54">
@@ -2726,7 +6112,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B55">
         <v>3060</v>
@@ -2735,9 +6121,10 @@
         <v>14</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E55">
+        <f>VLOOKUP(A55,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3147</v>
       </c>
       <c r="F55">
@@ -2749,7 +6136,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B56">
         <v>3061</v>
@@ -2758,9 +6145,10 @@
         <v>14</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E56">
+        <f>VLOOKUP(A56,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3148</v>
       </c>
       <c r="F56">
@@ -2772,7 +6160,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B57">
         <v>3062</v>
@@ -2781,9 +6169,10 @@
         <v>14</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E57">
+        <f>VLOOKUP(A57,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3149</v>
       </c>
       <c r="F57">
@@ -2795,7 +6184,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B58">
         <v>3063</v>
@@ -2804,9 +6193,10 @@
         <v>13</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E58">
+        <f>VLOOKUP(A58,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3150</v>
       </c>
       <c r="F58">
@@ -2818,7 +6208,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B59">
         <v>3064</v>
@@ -2827,9 +6217,10 @@
         <v>13</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E59">
+        <f>VLOOKUP(A59,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3151</v>
       </c>
       <c r="F59">
@@ -2841,7 +6232,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B60">
         <v>3065</v>
@@ -2850,9 +6241,10 @@
         <v>13</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E60">
+        <f>VLOOKUP(A60,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3152</v>
       </c>
       <c r="F60">
@@ -2864,7 +6256,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B61">
         <v>3066</v>
@@ -2873,9 +6265,10 @@
         <v>13</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E61">
+        <f>VLOOKUP(A61,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3153</v>
       </c>
       <c r="F61">
@@ -2887,7 +6280,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B62">
         <v>3067</v>
@@ -2896,9 +6289,10 @@
         <v>13</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E62">
+        <f>VLOOKUP(A62,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3154</v>
       </c>
       <c r="F62">
@@ -2910,7 +6304,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B63">
         <v>3068</v>
@@ -2919,9 +6313,10 @@
         <v>13</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E63">
+        <f>VLOOKUP(A63,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3155</v>
       </c>
       <c r="F63">
@@ -2933,7 +6328,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B64">
         <v>3069</v>
@@ -2942,9 +6337,10 @@
         <v>13</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E64">
+        <f>VLOOKUP(A64,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3156</v>
       </c>
       <c r="F64">
@@ -2956,7 +6352,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B65">
         <v>3070</v>
@@ -2965,9 +6361,10 @@
         <v>13</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E65">
+        <f>VLOOKUP(A65,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3157</v>
       </c>
       <c r="F65">
@@ -2979,7 +6376,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B66">
         <v>3071</v>
@@ -2988,9 +6385,10 @@
         <v>13</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E66">
+        <f>VLOOKUP(A66,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3158</v>
       </c>
       <c r="F66">
@@ -3002,7 +6400,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B67">
         <v>3072</v>
@@ -3011,9 +6409,10 @@
         <v>13</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E67">
+        <f>VLOOKUP(A67,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3159</v>
       </c>
       <c r="F67">
@@ -3025,7 +6424,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B68">
         <v>3073</v>
@@ -3034,9 +6433,10 @@
         <v>13</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E68">
+        <f>VLOOKUP(A68,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3160</v>
       </c>
       <c r="F68">
@@ -3048,7 +6448,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B69">
         <v>3074</v>
@@ -3057,9 +6457,10 @@
         <v>13</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E69">
+        <f>VLOOKUP(A69,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3161</v>
       </c>
       <c r="F69">
@@ -3071,7 +6472,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B70">
         <v>3075</v>
@@ -3080,9 +6481,10 @@
         <v>13</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E70">
+        <f>VLOOKUP(A70,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3162</v>
       </c>
       <c r="F70">
@@ -3094,7 +6496,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B71">
         <v>3076</v>
@@ -3103,9 +6505,10 @@
         <v>13</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E71">
+        <f>VLOOKUP(A71,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3163</v>
       </c>
       <c r="F71">
@@ -3117,7 +6520,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B72">
         <v>3077</v>
@@ -3126,9 +6529,10 @@
         <v>13</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E72">
+        <f>VLOOKUP(A72,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3164</v>
       </c>
       <c r="F72">
@@ -3140,7 +6544,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B73">
         <v>3078</v>
@@ -3149,9 +6553,10 @@
         <v>13</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E73">
+        <f>VLOOKUP(A73,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3165</v>
       </c>
       <c r="F73">
@@ -3163,7 +6568,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B74">
         <v>3079</v>
@@ -3172,9 +6577,10 @@
         <v>12</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E74">
+        <f>VLOOKUP(A74,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3166</v>
       </c>
       <c r="F74">
@@ -3186,7 +6592,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B75">
         <v>3080</v>
@@ -3195,9 +6601,10 @@
         <v>12</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E75">
+        <f>VLOOKUP(A75,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3167</v>
       </c>
       <c r="F75">
@@ -3209,7 +6616,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B76">
         <v>3081</v>
@@ -3218,9 +6625,10 @@
         <v>11</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E76">
+        <f>VLOOKUP(A76,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3168</v>
       </c>
       <c r="F76">
@@ -3232,7 +6640,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B77">
         <v>3082</v>
@@ -3241,9 +6649,10 @@
         <v>12</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E77">
+        <f>VLOOKUP(A77,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3169</v>
       </c>
       <c r="F77">
@@ -3255,7 +6664,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B78">
         <v>3083</v>
@@ -3264,9 +6673,10 @@
         <v>12</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E78">
+        <f>VLOOKUP(A78,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3170</v>
       </c>
       <c r="F78">
@@ -3278,7 +6688,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79">
         <v>3084</v>
@@ -3287,9 +6697,10 @@
         <v>11</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E79">
+        <f>VLOOKUP(A79,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3171</v>
       </c>
       <c r="F79">
@@ -3301,7 +6712,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80">
         <v>3085</v>
@@ -3310,9 +6721,10 @@
         <v>12</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E80">
+        <f>VLOOKUP(A80,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3172</v>
       </c>
       <c r="F80">
@@ -3324,7 +6736,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81">
         <v>3086</v>
@@ -3333,9 +6745,10 @@
         <v>12</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E81">
+        <f>VLOOKUP(A81,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3173</v>
       </c>
       <c r="F81">
@@ -3347,7 +6760,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82">
         <v>3087</v>
@@ -3356,9 +6769,10 @@
         <v>11</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E82">
+        <f>VLOOKUP(A82,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3174</v>
       </c>
       <c r="F82">
@@ -3370,7 +6784,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83">
         <v>3088</v>
@@ -3379,9 +6793,10 @@
         <v>11</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E83">
+        <f>VLOOKUP(A83,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3175</v>
       </c>
       <c r="F83">
@@ -3393,7 +6808,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84">
         <v>3089</v>
@@ -3402,9 +6817,10 @@
         <v>12</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E84">
+        <f>VLOOKUP(A84,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3176</v>
       </c>
       <c r="F84">
@@ -3416,7 +6832,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85">
         <v>3090</v>
@@ -3425,9 +6841,10 @@
         <v>11</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E85">
+        <f>VLOOKUP(A85,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3177</v>
       </c>
       <c r="F85">
@@ -3439,7 +6856,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86">
         <v>3091</v>
@@ -3448,9 +6865,10 @@
         <v>11</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="E86">
+        <f>VLOOKUP(A86,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3178</v>
       </c>
       <c r="F86">
@@ -3462,7 +6880,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B87">
         <v>3092</v>
@@ -3471,9 +6889,10 @@
         <v>15</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E87">
+        <f>VLOOKUP(A87,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>3179</v>
       </c>
       <c r="F87">
@@ -3485,7 +6904,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B88">
         <v>2000</v>
@@ -3497,6 +6916,7 @@
         <v>102</v>
       </c>
       <c r="E88">
+        <f>VLOOKUP(A88,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>101</v>
       </c>
       <c r="F88">
@@ -3508,7 +6928,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B89">
         <v>2001</v>
@@ -3517,9 +6937,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E89">
+        <f>VLOOKUP(A89,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>103</v>
       </c>
       <c r="F89">
@@ -3531,7 +6952,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B90">
         <v>2003</v>
@@ -3540,9 +6961,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E90">
+        <f>VLOOKUP(A90,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>103</v>
       </c>
       <c r="F90">
@@ -3554,7 +6976,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B91">
         <v>2010</v>
@@ -3565,7 +6987,8 @@
       <c r="D91" s="2">
         <v>283</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91">
+        <f>VLOOKUP(A91,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>277</v>
       </c>
       <c r="F91">
@@ -3577,7 +7000,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B92">
         <v>2011</v>
@@ -3588,7 +7011,8 @@
       <c r="D92" s="2">
         <v>277</v>
       </c>
-      <c r="E92" s="2">
+      <c r="E92">
+        <f>VLOOKUP(A92,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>204</v>
       </c>
       <c r="F92">
@@ -3600,7 +7024,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B93">
         <v>2012</v>
@@ -3611,7 +7035,8 @@
       <c r="D93" s="2">
         <v>203</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E93">
+        <f>VLOOKUP(A93,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>271</v>
       </c>
       <c r="F93">
@@ -3623,7 +7048,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B94">
         <v>2100</v>
@@ -3632,10 +7057,11 @@
         <v>2</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E94" s="2">
-        <v>4000</v>
+        <v>190</v>
+      </c>
+      <c r="E94">
+        <f>VLOOKUP(A94,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>5000</v>
       </c>
       <c r="F94">
         <v>2</v>
@@ -3646,7 +7072,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B95">
         <v>2101</v>
@@ -3655,10 +7081,11 @@
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E95" s="2">
-        <v>4001</v>
+        <v>191</v>
+      </c>
+      <c r="E95">
+        <f>VLOOKUP(A95,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>5001</v>
       </c>
       <c r="F95">
         <v>2</v>
@@ -3669,7 +7096,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B96">
         <v>2102</v>
@@ -3678,10 +7105,11 @@
         <v>2</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E96" s="2">
-        <v>4002</v>
+        <v>192</v>
+      </c>
+      <c r="E96">
+        <f>VLOOKUP(A96,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>5002</v>
       </c>
       <c r="F96">
         <v>2</v>
@@ -3692,7 +7120,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B97">
         <v>2103</v>
@@ -3701,10 +7129,11 @@
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="E97" s="2">
-        <v>4003</v>
+        <v>193</v>
+      </c>
+      <c r="E97">
+        <f>VLOOKUP(A97,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>5003</v>
       </c>
       <c r="F97">
         <v>2</v>
@@ -3715,7 +7144,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B98">
         <v>2104</v>
@@ -3724,10 +7153,11 @@
         <v>2</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E98" s="2">
-        <v>4004</v>
+        <v>194</v>
+      </c>
+      <c r="E98">
+        <f>VLOOKUP(A98,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>5004</v>
       </c>
       <c r="F98">
         <v>2</v>
@@ -3738,7 +7168,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B99">
         <v>2105</v>
@@ -3747,10 +7177,11 @@
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="E99" s="2">
-        <v>4005</v>
+        <v>195</v>
+      </c>
+      <c r="E99">
+        <f>VLOOKUP(A99,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>5005</v>
       </c>
       <c r="F99">
         <v>2</v>
@@ -3761,7 +7192,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B100">
         <v>2106</v>
@@ -3770,10 +7201,11 @@
         <v>2</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="E100" s="2">
-        <v>4006</v>
+        <v>196</v>
+      </c>
+      <c r="E100">
+        <f>VLOOKUP(A100,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>5006</v>
       </c>
       <c r="F100">
         <v>2</v>
@@ -3784,7 +7216,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B101">
         <v>2107</v>
@@ -3793,10 +7225,11 @@
         <v>2</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="E101" s="2">
-        <v>4007</v>
+        <v>197</v>
+      </c>
+      <c r="E101">
+        <f>VLOOKUP(A101,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>5007</v>
       </c>
       <c r="F101">
         <v>2</v>
@@ -3807,7 +7240,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B102">
         <v>2108</v>
@@ -3816,10 +7249,11 @@
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E102" s="2">
-        <v>4008</v>
+        <v>198</v>
+      </c>
+      <c r="E102">
+        <f>VLOOKUP(A102,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>5008</v>
       </c>
       <c r="F102">
         <v>2</v>
@@ -3830,7 +7264,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B103">
         <v>2109</v>
@@ -3839,10 +7273,11 @@
         <v>2</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E103" s="2">
-        <v>4009</v>
+        <v>199</v>
+      </c>
+      <c r="E103">
+        <f>VLOOKUP(A103,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>5009</v>
       </c>
       <c r="F103">
         <v>2</v>
@@ -3853,7 +7288,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B104">
         <v>2110</v>
@@ -3862,10 +7297,11 @@
         <v>2</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E104" s="2">
-        <v>4010</v>
+        <v>200</v>
+      </c>
+      <c r="E104">
+        <f>VLOOKUP(A104,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>5010</v>
       </c>
       <c r="F104">
         <v>2</v>
@@ -3876,7 +7312,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B105">
         <v>2111</v>
@@ -3885,9 +7321,10 @@
         <v>2</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E105">
+        <f>VLOOKUP(A105,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>11</v>
       </c>
       <c r="F105">
@@ -3899,7 +7336,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B106">
         <v>4000</v>
@@ -3908,9 +7345,10 @@
         <v>0</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="E106" s="9">
+        <v>268</v>
+      </c>
+      <c r="E106">
+        <f>VLOOKUP(A106,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1600</v>
       </c>
       <c r="F106">
@@ -3922,7 +7360,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B107">
         <v>4001</v>
@@ -3931,9 +7369,10 @@
         <v>0</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E107" s="9">
+        <v>269</v>
+      </c>
+      <c r="E107">
+        <f>VLOOKUP(A107,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1601</v>
       </c>
       <c r="F107">
@@ -3945,7 +7384,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B108">
         <v>4002</v>
@@ -3954,9 +7393,10 @@
         <v>0</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="E108" s="9">
+        <v>245</v>
+      </c>
+      <c r="E108">
+        <f>VLOOKUP(A108,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1602</v>
       </c>
       <c r="F108">
@@ -3968,7 +7408,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B109">
         <v>4003</v>
@@ -3977,9 +7417,10 @@
         <v>0</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="E109" s="9">
+        <v>246</v>
+      </c>
+      <c r="E109">
+        <f>VLOOKUP(A109,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1603</v>
       </c>
       <c r="F109">
@@ -3991,7 +7432,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B110">
         <v>4004</v>
@@ -4000,9 +7441,10 @@
         <v>0</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="E110" s="9">
+        <v>247</v>
+      </c>
+      <c r="E110">
+        <f>VLOOKUP(A110,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1604</v>
       </c>
       <c r="F110">
@@ -4014,7 +7456,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B111">
         <v>4005</v>
@@ -4023,9 +7465,10 @@
         <v>0</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="E111" s="9">
+        <v>294</v>
+      </c>
+      <c r="E111">
+        <f>VLOOKUP(A111,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1605</v>
       </c>
       <c r="F111">
@@ -4037,7 +7480,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>208</v>
+        <v>321</v>
       </c>
       <c r="B112">
         <v>4006</v>
@@ -4046,10 +7489,11 @@
         <v>0</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E112" s="9">
-        <v>1606</v>
+        <v>248</v>
+      </c>
+      <c r="E112">
+        <f>VLOOKUP(A112,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>1607</v>
       </c>
       <c r="F112">
         <v>2</v>
@@ -4060,7 +7504,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B113">
         <v>4007</v>
@@ -4069,10 +7513,11 @@
         <v>0</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E113" s="9">
-        <v>1607</v>
+        <v>270</v>
+      </c>
+      <c r="E113">
+        <f>VLOOKUP(A113,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>1606</v>
       </c>
       <c r="F113">
         <v>2</v>
@@ -4083,7 +7528,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B114">
         <v>4008</v>
@@ -4092,9 +7537,10 @@
         <v>0</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E114" s="9">
+        <v>249</v>
+      </c>
+      <c r="E114">
+        <f>VLOOKUP(A114,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1608</v>
       </c>
       <c r="F114">
@@ -4106,7 +7552,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B115">
         <v>4009</v>
@@ -4115,10 +7561,11 @@
         <v>0</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E115" s="9">
-        <v>1609</v>
+        <v>250</v>
+      </c>
+      <c r="E115">
+        <f>VLOOKUP(A115,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>1617</v>
       </c>
       <c r="F115">
         <v>2</v>
@@ -4129,7 +7576,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B116">
         <v>4010</v>
@@ -4138,10 +7585,11 @@
         <v>0</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E116" s="9">
-        <v>1610</v>
+        <v>251</v>
+      </c>
+      <c r="E116">
+        <f>VLOOKUP(A116,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>1618</v>
       </c>
       <c r="F116">
         <v>2</v>
@@ -4152,7 +7600,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B117">
         <v>4011</v>
@@ -4161,10 +7609,11 @@
         <v>0</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="E117" s="9">
-        <v>1611</v>
+        <v>271</v>
+      </c>
+      <c r="E117">
+        <f>VLOOKUP(A117,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>1609</v>
       </c>
       <c r="F117">
         <v>2</v>
@@ -4175,7 +7624,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B118">
         <v>4012</v>
@@ -4184,10 +7633,11 @@
         <v>0</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="E118" s="9">
-        <v>1612</v>
+        <v>272</v>
+      </c>
+      <c r="E118">
+        <f>VLOOKUP(A118,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>1610</v>
       </c>
       <c r="F118">
         <v>2</v>
@@ -4198,7 +7648,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B119">
         <v>4013</v>
@@ -4207,10 +7657,11 @@
         <v>0</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="E119" s="9">
-        <v>1613</v>
+        <v>252</v>
+      </c>
+      <c r="E119">
+        <f>VLOOKUP(A119,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>1611</v>
       </c>
       <c r="F119">
         <v>2</v>
@@ -4221,7 +7672,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B120">
         <v>4014</v>
@@ -4230,10 +7681,11 @@
         <v>0</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="E120" s="9">
-        <v>1614</v>
+        <v>253</v>
+      </c>
+      <c r="E120">
+        <f>VLOOKUP(A120,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>1616</v>
       </c>
       <c r="F120">
         <v>2</v>
@@ -4244,7 +7696,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B121">
         <v>4015</v>
@@ -4253,10 +7705,11 @@
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E121" s="9">
-        <v>1615</v>
+        <v>273</v>
+      </c>
+      <c r="E121">
+        <f>VLOOKUP(A121,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>1612</v>
       </c>
       <c r="F121">
         <v>2</v>
@@ -4266,8 +7719,8 @@
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A122" s="5" t="s">
-        <v>218</v>
+      <c r="A122" s="2" t="s">
+        <v>322</v>
       </c>
       <c r="B122">
         <v>4016</v>
@@ -4276,10 +7729,11 @@
         <v>1</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E122" s="9">
-        <v>1616</v>
+        <v>274</v>
+      </c>
+      <c r="E122">
+        <f>VLOOKUP(A122,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>1613</v>
       </c>
       <c r="F122">
         <v>2</v>
@@ -4289,8 +7743,8 @@
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A123" s="5" t="s">
-        <v>219</v>
+      <c r="A123" s="2" t="s">
+        <v>323</v>
       </c>
       <c r="B123">
         <v>4017</v>
@@ -4299,10 +7753,11 @@
         <v>1</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E123" s="9">
-        <v>1617</v>
+        <v>275</v>
+      </c>
+      <c r="E123">
+        <f>VLOOKUP(A123,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>1614</v>
       </c>
       <c r="F123">
         <v>2</v>
@@ -4313,7 +7768,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B124">
         <v>4018</v>
@@ -4322,10 +7777,11 @@
         <v>1</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="E124" s="9">
-        <v>1618</v>
+        <v>276</v>
+      </c>
+      <c r="E124">
+        <f>VLOOKUP(A124,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>1615</v>
       </c>
       <c r="F124">
         <v>2</v>
@@ -4336,7 +7792,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="7" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B125">
         <v>4019</v>
@@ -4345,9 +7801,10 @@
         <v>0</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="E125" s="9">
+        <v>254</v>
+      </c>
+      <c r="E125">
+        <f>VLOOKUP(A125,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1619</v>
       </c>
       <c r="F125">
@@ -4359,7 +7816,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="7" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B126">
         <v>4020</v>
@@ -4368,9 +7825,10 @@
         <v>0</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="E126" s="9">
+        <v>255</v>
+      </c>
+      <c r="E126">
+        <f>VLOOKUP(A126,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1620</v>
       </c>
       <c r="F126">
@@ -4382,7 +7840,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="6" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B127">
         <v>4021</v>
@@ -4391,9 +7849,10 @@
         <v>1</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="E127" s="9">
+        <v>277</v>
+      </c>
+      <c r="E127">
+        <f>VLOOKUP(A127,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1650</v>
       </c>
       <c r="F127">
@@ -4405,7 +7864,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B128">
         <v>4022</v>
@@ -4414,9 +7873,10 @@
         <v>1</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="E128" s="9">
+        <v>278</v>
+      </c>
+      <c r="E128">
+        <f>VLOOKUP(A128,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1651</v>
       </c>
       <c r="F128">
@@ -4428,7 +7888,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="6" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B129">
         <v>4023</v>
@@ -4437,9 +7897,10 @@
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E129" s="9">
+        <v>279</v>
+      </c>
+      <c r="E129">
+        <f>VLOOKUP(A129,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1652</v>
       </c>
       <c r="F129">
@@ -4451,7 +7912,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B130">
         <v>4024</v>
@@ -4460,9 +7921,10 @@
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="E130" s="9">
+        <v>295</v>
+      </c>
+      <c r="E130">
+        <f>VLOOKUP(A130,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1653</v>
       </c>
       <c r="F130">
@@ -4474,7 +7936,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="6" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B131">
         <v>4025</v>
@@ -4483,9 +7945,10 @@
         <v>0</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="E131" s="9">
+        <v>280</v>
+      </c>
+      <c r="E131">
+        <f>VLOOKUP(A131,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1654</v>
       </c>
       <c r="F131">
@@ -4497,7 +7960,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B132">
         <v>4026</v>
@@ -4506,9 +7969,10 @@
         <v>0</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="E132" s="9">
+        <v>256</v>
+      </c>
+      <c r="E132">
+        <f>VLOOKUP(A132,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1655</v>
       </c>
       <c r="F132">
@@ -4520,7 +7984,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="6" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B133">
         <v>4027</v>
@@ -4529,9 +7993,10 @@
         <v>0</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E133" s="9">
+        <v>281</v>
+      </c>
+      <c r="E133">
+        <f>VLOOKUP(A133,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1656</v>
       </c>
       <c r="F133">
@@ -4543,7 +8008,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B134">
         <v>4028</v>
@@ -4552,9 +8017,10 @@
         <v>1</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="E134" s="9">
+        <v>282</v>
+      </c>
+      <c r="E134">
+        <f>VLOOKUP(A134,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1657</v>
       </c>
       <c r="F134">
@@ -4566,7 +8032,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="6" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B135">
         <v>4029</v>
@@ -4575,9 +8041,10 @@
         <v>1</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E135" s="9">
+        <v>283</v>
+      </c>
+      <c r="E135">
+        <f>VLOOKUP(A135,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1658</v>
       </c>
       <c r="F135">
@@ -4589,7 +8056,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="6" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B136">
         <v>4030</v>
@@ -4598,9 +8065,10 @@
         <v>1</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="E136" s="9">
+        <v>257</v>
+      </c>
+      <c r="E136">
+        <f>VLOOKUP(A136,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1659</v>
       </c>
       <c r="F136">
@@ -4612,7 +8080,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="6" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B137">
         <v>4031</v>
@@ -4621,9 +8089,10 @@
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="E137" s="9">
+        <v>284</v>
+      </c>
+      <c r="E137">
+        <f>VLOOKUP(A137,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1660</v>
       </c>
       <c r="F137">
@@ -4635,7 +8104,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="6" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B138">
         <v>4032</v>
@@ -4644,9 +8113,10 @@
         <v>1</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E138" s="9">
+        <v>258</v>
+      </c>
+      <c r="E138">
+        <f>VLOOKUP(A138,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1661</v>
       </c>
       <c r="F138">
@@ -4658,7 +8128,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B139">
         <v>4033</v>
@@ -4667,9 +8137,10 @@
         <v>0</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="E139" s="9">
+        <v>259</v>
+      </c>
+      <c r="E139">
+        <f>VLOOKUP(A139,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1662</v>
       </c>
       <c r="F139">
@@ -4681,7 +8152,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="6" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B140">
         <v>4034</v>
@@ -4690,9 +8161,10 @@
         <v>1</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="E140" s="9">
+        <v>285</v>
+      </c>
+      <c r="E140">
+        <f>VLOOKUP(A140,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1663</v>
       </c>
       <c r="F140">
@@ -4704,7 +8176,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="6" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B141">
         <v>4035</v>
@@ -4713,9 +8185,10 @@
         <v>1</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="E141" s="9">
+        <v>286</v>
+      </c>
+      <c r="E141">
+        <f>VLOOKUP(A141,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1664</v>
       </c>
       <c r="F141">
@@ -4727,7 +8200,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B142">
         <v>4036</v>
@@ -4736,9 +8209,10 @@
         <v>1</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="E142" s="9">
+        <v>260</v>
+      </c>
+      <c r="E142">
+        <f>VLOOKUP(A142,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1665</v>
       </c>
       <c r="F142">
@@ -4750,7 +8224,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B143">
         <v>4037</v>
@@ -4759,9 +8233,10 @@
         <v>1</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="E143" s="9">
+        <v>261</v>
+      </c>
+      <c r="E143">
+        <f>VLOOKUP(A143,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1666</v>
       </c>
       <c r="F143">
@@ -4773,7 +8248,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B144">
         <v>4038</v>
@@ -4782,9 +8257,10 @@
         <v>1</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="E144" s="9">
+        <v>296</v>
+      </c>
+      <c r="E144">
+        <f>VLOOKUP(A144,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1700</v>
       </c>
       <c r="F144">
@@ -4796,7 +8272,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B145">
         <v>4039</v>
@@ -4805,9 +8281,10 @@
         <v>1</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E145" s="9">
+        <v>287</v>
+      </c>
+      <c r="E145">
+        <f>VLOOKUP(A145,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1701</v>
       </c>
       <c r="F145">
@@ -4819,7 +8296,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B146">
         <v>4040</v>
@@ -4828,9 +8305,10 @@
         <v>0</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E146" s="9">
+        <v>288</v>
+      </c>
+      <c r="E146">
+        <f>VLOOKUP(A146,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1702</v>
       </c>
       <c r="F146">
@@ -4842,7 +8320,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B147">
         <v>4041</v>
@@ -4851,9 +8329,10 @@
         <v>1</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E147" s="9">
+        <v>289</v>
+      </c>
+      <c r="E147">
+        <f>VLOOKUP(A147,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1703</v>
       </c>
       <c r="F147">
@@ -4865,7 +8344,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B148">
         <v>4042</v>
@@ -4874,9 +8353,10 @@
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="E148" s="9">
+        <v>297</v>
+      </c>
+      <c r="E148">
+        <f>VLOOKUP(A148,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1704</v>
       </c>
       <c r="F148">
@@ -4888,7 +8368,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B149">
         <v>4043</v>
@@ -4897,9 +8377,10 @@
         <v>1</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="E149" s="9">
+        <v>262</v>
+      </c>
+      <c r="E149">
+        <f>VLOOKUP(A149,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1705</v>
       </c>
       <c r="F149">
@@ -4911,7 +8392,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B150">
         <v>4044</v>
@@ -4920,9 +8401,10 @@
         <v>1</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="E150" s="9">
+        <v>263</v>
+      </c>
+      <c r="E150">
+        <f>VLOOKUP(A150,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1706</v>
       </c>
       <c r="F150">
@@ -4934,7 +8416,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B151">
         <v>4045</v>
@@ -4943,9 +8425,10 @@
         <v>0</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="E151" s="9">
+        <v>264</v>
+      </c>
+      <c r="E151">
+        <f>VLOOKUP(A151,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1707</v>
       </c>
       <c r="F151">
@@ -4957,7 +8440,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B152">
         <v>4046</v>
@@ -4966,9 +8449,10 @@
         <v>1</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="E152" s="9">
+        <v>265</v>
+      </c>
+      <c r="E152">
+        <f>VLOOKUP(A152,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1708</v>
       </c>
       <c r="F152">
@@ -4980,7 +8464,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B153">
         <v>4047</v>
@@ -4989,9 +8473,10 @@
         <v>1</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E153" s="9">
+        <v>266</v>
+      </c>
+      <c r="E153">
+        <f>VLOOKUP(A153,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1709</v>
       </c>
       <c r="F153">
@@ -5003,7 +8488,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" s="8" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B154">
         <v>4048</v>
@@ -5012,9 +8497,10 @@
         <v>1</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E154" s="9">
+        <v>267</v>
+      </c>
+      <c r="E154">
+        <f>VLOOKUP(A154,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1710</v>
       </c>
       <c r="F154">
@@ -5026,7 +8512,7 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B155">
         <v>4049</v>
@@ -5035,9 +8521,10 @@
         <v>1</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="E155">
+        <f>VLOOKUP(A155,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1800</v>
       </c>
       <c r="F155">
@@ -5048,8 +8535,8 @@
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A156" t="s">
-        <v>303</v>
+      <c r="A156" s="2" t="s">
+        <v>324</v>
       </c>
       <c r="B156">
         <v>4050</v>
@@ -5058,9 +8545,10 @@
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="E156">
+        <f>VLOOKUP(A156,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1801</v>
       </c>
       <c r="F156">
@@ -5072,7 +8560,7 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B157">
         <v>4051</v>
@@ -5081,9 +8569,10 @@
         <v>1</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="E157">
+        <f>VLOOKUP(A157,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1802</v>
       </c>
       <c r="F157">
@@ -5095,7 +8584,7 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B158">
         <v>4052</v>
@@ -5104,9 +8593,10 @@
         <v>0</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="E158">
+        <f>VLOOKUP(A158,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1803</v>
       </c>
       <c r="F158">
@@ -5118,7 +8608,7 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B159">
         <v>4053</v>
@@ -5127,9 +8617,10 @@
         <v>0</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="E159">
+        <f>VLOOKUP(A159,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1804</v>
       </c>
       <c r="F159">
@@ -5141,7 +8632,7 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B160">
         <v>4054</v>
@@ -5150,9 +8641,10 @@
         <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E160">
+        <f>VLOOKUP(A160,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1805</v>
       </c>
       <c r="F160">
@@ -5164,7 +8656,7 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B161">
         <v>4055</v>
@@ -5173,9 +8665,10 @@
         <v>1</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E161">
+        <f>VLOOKUP(A161,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1806</v>
       </c>
       <c r="F161">
@@ -5187,7 +8680,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B162">
         <v>4056</v>
@@ -5196,9 +8689,10 @@
         <v>1</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="E162">
+        <f>VLOOKUP(A162,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1807</v>
       </c>
       <c r="F162">
@@ -5210,7 +8704,7 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B163">
         <v>4057</v>
@@ -5219,9 +8713,10 @@
         <v>0</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E163">
+        <f>VLOOKUP(A163,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1808</v>
       </c>
       <c r="F163">
@@ -5234,6 +8729,12 @@
   </sheetData>
   <autoFilter ref="A3:G163"/>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A122:A123">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A156">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>

--- a/Datas/FormulaData.xlsx
+++ b/Datas/FormulaData.xlsx
@@ -14,7 +14,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FormulaData!$A$3:$G$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FormulaData!$A$3:$G$164</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="326">
   <si>
     <t>formulaName</t>
   </si>
@@ -600,7 +600,499 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>毛线</t>
+    <t>皮革</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>回春卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>振奋卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>昏睡卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>感电卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰氛卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>火氛卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>沉默卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>减速卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪避卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>力量卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>魅惑卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>290,292,244</t>
+  </si>
+  <si>
+    <t>294,265,207</t>
+  </si>
+  <si>
+    <t>251,287,257</t>
+  </si>
+  <si>
+    <t>290,225,286</t>
+  </si>
+  <si>
+    <t>267,261,286</t>
+  </si>
+  <si>
+    <t>284,291,286</t>
+  </si>
+  <si>
+    <t>263,255,210</t>
+  </si>
+  <si>
+    <t>236,259,250</t>
+  </si>
+  <si>
+    <t>285,278,281</t>
+  </si>
+  <si>
+    <t>288,256,240</t>
+  </si>
+  <si>
+    <t>293,289,254</t>
+  </si>
+  <si>
+    <t>长剑</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>诅咒之剑</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>烈焰之刃</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>大地之剑</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰之刃</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁枪</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>骑士长枪</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>三叉戟</t>
+  </si>
+  <si>
+    <t>秘银长剑</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>幻影长枪</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斧</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒蜥之牙</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>恶魔之斧</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴雪斧</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>蛇皮鞭</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>蛇牙鞭</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷神之鞭</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡之鞭</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>布衣</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>皮铠</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>锁子甲</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>毛皮斗篷</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>红莲之铠</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁龟铠</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>华丽背心</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>鳞铠</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>暗之袍</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>疾风背心</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法铠甲</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>钢刃锁甲</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>丝织长袍</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>水之羽衣</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>贵族长裙</t>
+  </si>
+  <si>
+    <t>幸运之衣</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>布鞋</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>皮鞋</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>登山者之靴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>运动鞋</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>贵族长靴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>武道鞋</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>骑士护胫</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>贤者之履</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>风神之履</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>踏浪长靴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1600,229,205,284</t>
+  </si>
+  <si>
+    <t>1600,218,299,212</t>
+  </si>
+  <si>
+    <t>1600,260,261,253</t>
+  </si>
+  <si>
+    <t>1605,259,237,239</t>
+  </si>
+  <si>
+    <t>1605,227,240,232</t>
+  </si>
+  <si>
+    <t>237,274,256,285</t>
+  </si>
+  <si>
+    <t>269,1605,264,208</t>
+  </si>
+  <si>
+    <t>1609,259,258,263</t>
+  </si>
+  <si>
+    <t>1609,253,260,267</t>
+  </si>
+  <si>
+    <t>270,225,239,1614</t>
+  </si>
+  <si>
+    <t>245,255,268,1615</t>
+  </si>
+  <si>
+    <t>1654,250,229,286</t>
+  </si>
+  <si>
+    <t>1651,242,247,241</t>
+  </si>
+  <si>
+    <t>1654,274,299,218</t>
+  </si>
+  <si>
+    <t>1656,279,234,247</t>
+  </si>
+  <si>
+    <t>248,1650,245,285</t>
+  </si>
+  <si>
+    <t>1701,234,223,279</t>
+  </si>
+  <si>
+    <t>1700,280,232,272</t>
+  </si>
+  <si>
+    <t>1702,275,240,299</t>
+  </si>
+  <si>
+    <t>1700,281,251,282</t>
+  </si>
+  <si>
+    <t>224,1704,264,258</t>
+  </si>
+  <si>
+    <t>1703,282,232,267</t>
+  </si>
+  <si>
+    <t>298,274</t>
+  </si>
+  <si>
+    <t>1600,220,257</t>
+  </si>
+  <si>
+    <t>1605,275,299</t>
+  </si>
+  <si>
+    <t>299,274,241</t>
+  </si>
+  <si>
+    <t>1609,254,211</t>
+  </si>
+  <si>
+    <t>238,276,214</t>
+  </si>
+  <si>
+    <t>221,276,214</t>
+  </si>
+  <si>
+    <t>1613,213,246</t>
+  </si>
+  <si>
+    <t>1612,211,1612</t>
+  </si>
+  <si>
+    <t>271,278,214</t>
+  </si>
+  <si>
+    <t>1651,227,299</t>
+  </si>
+  <si>
+    <t>298,205</t>
+  </si>
+  <si>
+    <t>202,1654,210</t>
+  </si>
+  <si>
+    <t>273,278,271</t>
+  </si>
+  <si>
+    <t>1650,208,224</t>
+  </si>
+  <si>
+    <t>204,214,228</t>
+  </si>
+  <si>
+    <t>1650,232,282</t>
+  </si>
+  <si>
+    <t>271,222,278</t>
+  </si>
+  <si>
+    <t>298,210,202</t>
+  </si>
+  <si>
+    <t>1701,273,238</t>
+  </si>
+  <si>
+    <t>传送卷轴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>224,269,291</t>
+  </si>
+  <si>
+    <t>士兵长靴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁铠甲</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>104,222,274</t>
+  </si>
+  <si>
+    <t>1651,223,301</t>
+  </si>
+  <si>
+    <t>204,302,278</t>
+  </si>
+  <si>
+    <t>1700,301,214</t>
+  </si>
+  <si>
+    <t>草帽</t>
+  </si>
+  <si>
+    <t>法师帽</t>
+  </si>
+  <si>
+    <t>士兵头盔</t>
+  </si>
+  <si>
+    <t>尖角头盔</t>
+  </si>
+  <si>
+    <t>幸运头巾</t>
+  </si>
+  <si>
+    <t>绅士礼帽</t>
+  </si>
+  <si>
+    <t>贵族头巾</t>
+  </si>
+  <si>
+    <t>战争头盔</t>
+  </si>
+  <si>
+    <t>105,204</t>
+  </si>
+  <si>
+    <t>1800,285</t>
+  </si>
+  <si>
+    <t>204,286,256</t>
+  </si>
+  <si>
+    <t>298,271</t>
+  </si>
+  <si>
+    <t>1803,241,213</t>
+  </si>
+  <si>
+    <t>272,248,224</t>
+  </si>
+  <si>
+    <t>272,228,251</t>
+  </si>
+  <si>
+    <t>272,279,234</t>
+  </si>
+  <si>
+    <t>1804,288,247</t>
+  </si>
+  <si>
+    <t>鲮鱼丸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>煮蟹肉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3164,3134,1006,4015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凉茶</t>
+  </si>
+  <si>
+    <t>200,207</t>
+  </si>
+  <si>
+    <t>面包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血腥之矛</t>
+  </si>
+  <si>
+    <t>荆棘鞭</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>女王之鞭</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>阳光草帽</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -608,509 +1100,24 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>皮革</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>回春卷轴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>振奋卷轴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>昏睡卷轴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>感电卷轴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰氛卷轴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>火氛卷轴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>沉默卷轴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>减速卷轴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪避卷轴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>力量卷轴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>魅惑卷轴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>290,292,244</t>
-  </si>
-  <si>
-    <t>294,265,207</t>
-  </si>
-  <si>
-    <t>251,287,257</t>
-  </si>
-  <si>
-    <t>290,225,286</t>
-  </si>
-  <si>
-    <t>267,261,286</t>
-  </si>
-  <si>
-    <t>284,291,286</t>
-  </si>
-  <si>
-    <t>263,255,210</t>
-  </si>
-  <si>
-    <t>236,259,250</t>
-  </si>
-  <si>
-    <t>285,278,281</t>
-  </si>
-  <si>
-    <t>288,256,240</t>
-  </si>
-  <si>
-    <t>293,289,254</t>
-  </si>
-  <si>
-    <t>长剑</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>诅咒之剑</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>烈焰之刃</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>大地之剑</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰之刃</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁枪</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>骑士长枪</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>三叉戟</t>
-  </si>
-  <si>
-    <t>秘银长剑</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>幻影长枪</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斧</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>毒蜥之牙</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>恶魔之斧</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴雪斧</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>蛇皮鞭</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>蛇牙鞭</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷神之鞭</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡之鞭</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>布衣</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>皮铠</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>锁子甲</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>毛皮斗篷</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>红莲之铠</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁龟铠</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>华丽背心</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>鳞铠</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>暗之袍</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>疾风背心</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>魔法铠甲</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>钢刃锁甲</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>丝织长袍</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>水之羽衣</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>贵族长裙</t>
-  </si>
-  <si>
-    <t>幸运之衣</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>布鞋</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>皮鞋</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>登山者之靴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>运动鞋</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>贵族长靴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>武道鞋</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>骑士护胫</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>贤者之履</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>风神之履</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>踏浪长靴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>1600,229,205,284</t>
-  </si>
-  <si>
-    <t>1600,218,299,212</t>
-  </si>
-  <si>
-    <t>1600,260,261,253</t>
-  </si>
-  <si>
-    <t>1605,259,237,239</t>
-  </si>
-  <si>
-    <t>1605,227,240,232</t>
-  </si>
-  <si>
-    <t>237,274,256,285</t>
-  </si>
-  <si>
-    <t>269,1605,264,208</t>
-  </si>
-  <si>
-    <t>1609,259,258,263</t>
-  </si>
-  <si>
-    <t>1609,253,260,267</t>
-  </si>
-  <si>
-    <t>270,225,239,1614</t>
-  </si>
-  <si>
-    <t>245,255,268,1615</t>
-  </si>
-  <si>
-    <t>1654,250,229,286</t>
-  </si>
-  <si>
-    <t>264,277,255,246</t>
-  </si>
-  <si>
-    <t>1651,242,247,241</t>
-  </si>
-  <si>
-    <t>1654,274,299,218</t>
-  </si>
-  <si>
-    <t>1656,279,234,247</t>
-  </si>
-  <si>
-    <t>248,1650,245,285</t>
-  </si>
-  <si>
-    <t>1701,234,223,279</t>
-  </si>
-  <si>
-    <t>1700,280,232,272</t>
-  </si>
-  <si>
-    <t>1702,275,240,299</t>
-  </si>
-  <si>
-    <t>1700,281,251,282</t>
-  </si>
-  <si>
-    <t>224,1704,264,258</t>
-  </si>
-  <si>
-    <t>1703,282,232,267</t>
-  </si>
-  <si>
-    <t>298,274</t>
-  </si>
-  <si>
-    <t>1600,220,257</t>
-  </si>
-  <si>
-    <t>1605,275,299</t>
-  </si>
-  <si>
-    <t>299,274,241</t>
-  </si>
-  <si>
-    <t>1609,254,211</t>
-  </si>
-  <si>
-    <t>238,276,214</t>
-  </si>
-  <si>
-    <t>221,276,214</t>
-  </si>
-  <si>
-    <t>1613,213,246</t>
-  </si>
-  <si>
-    <t>1612,211,1612</t>
-  </si>
-  <si>
-    <t>204,277</t>
-  </si>
-  <si>
-    <t>271,278,214</t>
-  </si>
-  <si>
-    <t>1651,227,299</t>
-  </si>
-  <si>
-    <t>298,205</t>
-  </si>
-  <si>
-    <t>202,1654,210</t>
-  </si>
-  <si>
-    <t>272,228,277</t>
-  </si>
-  <si>
-    <t>273,278,271</t>
-  </si>
-  <si>
-    <t>1650,208,224</t>
-  </si>
-  <si>
-    <t>204,214,228</t>
-  </si>
-  <si>
-    <t>1650,232,282</t>
-  </si>
-  <si>
-    <t>271,222,278</t>
-  </si>
-  <si>
-    <t>298,210,202</t>
-  </si>
-  <si>
-    <t>1701,273,238</t>
-  </si>
-  <si>
-    <t>传送卷轴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>224,269,291</t>
-  </si>
-  <si>
-    <t>士兵长靴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁铠甲</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>104,222,274</t>
-  </si>
-  <si>
-    <t>1651,223,301</t>
-  </si>
-  <si>
-    <t>204,302,278</t>
-  </si>
-  <si>
-    <t>1700,301,214</t>
-  </si>
-  <si>
-    <t>草帽</t>
-  </si>
-  <si>
-    <t>法师帽</t>
-  </si>
-  <si>
-    <t>士兵头盔</t>
-  </si>
-  <si>
-    <t>尖角头盔</t>
-  </si>
-  <si>
-    <t>幸运头巾</t>
-  </si>
-  <si>
-    <t>绅士礼帽</t>
-  </si>
-  <si>
-    <t>贵族头巾</t>
-  </si>
-  <si>
-    <t>战争头盔</t>
-  </si>
-  <si>
-    <t>105,204</t>
-  </si>
-  <si>
-    <t>1800,285</t>
-  </si>
-  <si>
-    <t>204,286,256</t>
-  </si>
-  <si>
-    <t>298,271</t>
-  </si>
-  <si>
-    <t>1803,241,213</t>
-  </si>
-  <si>
-    <t>272,248,224</t>
-  </si>
-  <si>
-    <t>272,228,251</t>
-  </si>
-  <si>
-    <t>272,279,234</t>
-  </si>
-  <si>
-    <t>1804,288,247</t>
-  </si>
-  <si>
-    <t>鲮鱼丸</t>
+    <t>204,204</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>煮蟹肉</t>
+    <t>272,228,204</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3164,3134,1006,4015</t>
+    <t>264,204,255,246</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>凉茶</t>
-  </si>
-  <si>
-    <t>200,207</t>
-  </si>
-  <si>
-    <t>面包</t>
+    <t>铁块</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>血腥之矛</t>
-  </si>
-  <si>
-    <t>荆棘鞭</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>女王之鞭</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>阳光草帽</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>钢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1193,7 +1200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1216,6 +1223,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1275,7 +1285,7 @@
       <sheetName val="鱼"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="4">
           <cell r="A4" t="str">
             <v>未知的物品</v>
@@ -4549,19 +4559,19 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4830,7 +4840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G163"/>
+  <dimension ref="A2:G164"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -5272,7 +5282,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B20">
         <v>3025</v>
@@ -6568,7 +6578,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B74">
         <v>3079</v>
@@ -6664,7 +6674,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B78">
         <v>3083</v>
@@ -6865,7 +6875,7 @@
         <v>11</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E86">
         <f>VLOOKUP(A86,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6880,7 +6890,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B87">
         <v>3092</v>
@@ -6889,7 +6899,7 @@
         <v>15</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E87">
         <f>VLOOKUP(A87,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6976,20 +6986,20 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>176</v>
+        <v>320</v>
       </c>
       <c r="B91">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="C91">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D91" s="2">
         <v>283</v>
       </c>
       <c r="E91">
         <f>VLOOKUP(A91,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>277</v>
+        <v>204</v>
       </c>
       <c r="F91">
         <v>2</v>
@@ -7000,20 +7010,20 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B92">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C92">
         <v>5</v>
       </c>
       <c r="D92" s="2">
-        <v>277</v>
+        <v>203</v>
       </c>
       <c r="E92">
         <f>VLOOKUP(A92,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>204</v>
+        <v>271</v>
       </c>
       <c r="F92">
         <v>2</v>
@@ -7024,20 +7034,19 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>178</v>
+        <v>324</v>
       </c>
       <c r="B93">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C93">
-        <v>6</v>
-      </c>
-      <c r="D93" s="2">
-        <v>203</v>
+        <v>0</v>
+      </c>
+      <c r="D93" s="9">
+        <v>296296297</v>
       </c>
       <c r="E93">
-        <f>VLOOKUP(A93,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="F93">
         <v>2</v>
@@ -7047,21 +7056,20 @@
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A94" s="4" t="s">
-        <v>179</v>
+      <c r="A94" s="3" t="s">
+        <v>325</v>
       </c>
       <c r="B94">
-        <v>2100</v>
+        <v>2021</v>
       </c>
       <c r="C94">
-        <v>2</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>190</v>
+        <v>0</v>
+      </c>
+      <c r="D94" s="9">
+        <v>298298297</v>
       </c>
       <c r="E94">
-        <f>VLOOKUP(A94,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>5000</v>
+        <v>299</v>
       </c>
       <c r="F94">
         <v>2</v>
@@ -7072,20 +7080,20 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B95">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="C95">
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E95">
         <f>VLOOKUP(A95,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>5001</v>
+        <v>5000</v>
       </c>
       <c r="F95">
         <v>2</v>
@@ -7096,20 +7104,20 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B96">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="C96">
         <v>2</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E96">
         <f>VLOOKUP(A96,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="F96">
         <v>2</v>
@@ -7120,20 +7128,20 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B97">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="C97">
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E97">
         <f>VLOOKUP(A97,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="F97">
         <v>2</v>
@@ -7144,20 +7152,20 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B98">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="C98">
         <v>2</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E98">
         <f>VLOOKUP(A98,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>5004</v>
+        <v>5003</v>
       </c>
       <c r="F98">
         <v>2</v>
@@ -7168,20 +7176,20 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B99">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="C99">
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E99">
         <f>VLOOKUP(A99,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>5005</v>
+        <v>5004</v>
       </c>
       <c r="F99">
         <v>2</v>
@@ -7192,20 +7200,20 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B100">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="C100">
         <v>2</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E100">
         <f>VLOOKUP(A100,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>5006</v>
+        <v>5005</v>
       </c>
       <c r="F100">
         <v>2</v>
@@ -7216,20 +7224,20 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B101">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="C101">
         <v>2</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E101">
         <f>VLOOKUP(A101,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>5007</v>
+        <v>5006</v>
       </c>
       <c r="F101">
         <v>2</v>
@@ -7240,20 +7248,20 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B102">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="C102">
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E102">
         <f>VLOOKUP(A102,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>5008</v>
+        <v>5007</v>
       </c>
       <c r="F102">
         <v>2</v>
@@ -7264,20 +7272,20 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B103">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="C103">
         <v>2</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E103">
         <f>VLOOKUP(A103,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>5009</v>
+        <v>5008</v>
       </c>
       <c r="F103">
         <v>2</v>
@@ -7288,20 +7296,20 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B104">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="C104">
         <v>2</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E104">
         <f>VLOOKUP(A104,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>5010</v>
+        <v>5009</v>
       </c>
       <c r="F104">
         <v>2</v>
@@ -7312,20 +7320,20 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
-        <v>290</v>
+        <v>187</v>
       </c>
       <c r="B105">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="C105">
         <v>2</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>291</v>
+        <v>198</v>
       </c>
       <c r="E105">
         <f>VLOOKUP(A105,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>11</v>
+        <v>5010</v>
       </c>
       <c r="F105">
         <v>2</v>
@@ -7335,45 +7343,45 @@
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A106" s="5" t="s">
-        <v>201</v>
+      <c r="A106" s="4" t="s">
+        <v>285</v>
       </c>
       <c r="B106">
-        <v>4000</v>
-      </c>
-      <c r="C106" s="3">
-        <v>0</v>
+        <v>2111</v>
+      </c>
+      <c r="C106">
+        <v>2</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="E106">
         <f>VLOOKUP(A106,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1600</v>
+        <v>11</v>
       </c>
       <c r="F106">
         <v>2</v>
       </c>
       <c r="G106">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B107">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="C107" s="3">
         <v>0</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E107">
         <f>VLOOKUP(A107,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F107">
         <v>2</v>
@@ -7383,45 +7391,45 @@
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A108" s="6" t="s">
-        <v>203</v>
+      <c r="A108" s="5" t="s">
+        <v>200</v>
       </c>
       <c r="B108">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C108" s="3">
         <v>0</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="E108">
         <f>VLOOKUP(A108,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="F108">
         <v>2</v>
       </c>
       <c r="G108">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A109" s="5" t="s">
-        <v>204</v>
+      <c r="A109" s="6" t="s">
+        <v>201</v>
       </c>
       <c r="B109">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C109" s="3">
         <v>0</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E109">
         <f>VLOOKUP(A109,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="F109">
         <v>2</v>
@@ -7432,20 +7440,20 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B110">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C110" s="3">
         <v>0</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E110">
         <f>VLOOKUP(A110,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="F110">
         <v>2</v>
@@ -7456,68 +7464,68 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B111">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="C111" s="3">
         <v>0</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>294</v>
+        <v>245</v>
       </c>
       <c r="E111">
         <f>VLOOKUP(A111,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="F111">
         <v>2</v>
       </c>
       <c r="G111">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>321</v>
+        <v>204</v>
       </c>
       <c r="B112">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="C112" s="3">
         <v>0</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>248</v>
+        <v>289</v>
       </c>
       <c r="E112">
         <f>VLOOKUP(A112,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="F112">
         <v>2</v>
       </c>
       <c r="G112">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>207</v>
+        <v>316</v>
       </c>
       <c r="B113">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="C113" s="3">
         <v>0</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="E113">
         <f>VLOOKUP(A113,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="F113">
         <v>2</v>
@@ -7528,20 +7536,20 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B114">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="C114" s="3">
         <v>0</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="E114">
         <f>VLOOKUP(A114,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="F114">
         <v>2</v>
@@ -7551,45 +7559,45 @@
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A115" s="7" t="s">
-        <v>209</v>
+      <c r="A115" s="5" t="s">
+        <v>206</v>
       </c>
       <c r="B115">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="C115" s="3">
         <v>0</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E115">
         <f>VLOOKUP(A115,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1617</v>
+        <v>1608</v>
       </c>
       <c r="F115">
         <v>2</v>
       </c>
       <c r="G115">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B116">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="C116" s="3">
         <v>0</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E116">
         <f>VLOOKUP(A116,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="F116">
         <v>2</v>
@@ -7599,69 +7607,69 @@
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A117" s="5" t="s">
-        <v>211</v>
+      <c r="A117" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="B117">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="C117" s="3">
         <v>0</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="E117">
         <f>VLOOKUP(A117,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1609</v>
+        <v>1618</v>
       </c>
       <c r="F117">
         <v>2</v>
       </c>
       <c r="G117">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B118">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="C118" s="3">
         <v>0</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E118">
         <f>VLOOKUP(A118,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="F118">
         <v>2</v>
       </c>
       <c r="G118">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B119">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="C119" s="3">
         <v>0</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="E119">
         <f>VLOOKUP(A119,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="F119">
         <v>2</v>
@@ -7672,68 +7680,68 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B120">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="C120" s="3">
         <v>0</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E120">
         <f>VLOOKUP(A120,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1616</v>
+        <v>1611</v>
       </c>
       <c r="F120">
         <v>2</v>
       </c>
       <c r="G120">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B121">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="C121" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="E121">
         <f>VLOOKUP(A121,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1612</v>
+        <v>1616</v>
       </c>
       <c r="F121">
         <v>2</v>
       </c>
       <c r="G121">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A122" s="2" t="s">
-        <v>322</v>
+      <c r="A122" s="5" t="s">
+        <v>213</v>
       </c>
       <c r="B122">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="C122" s="3">
         <v>1</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E122">
         <f>VLOOKUP(A122,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F122">
         <v>2</v>
@@ -7744,44 +7752,44 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B123">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="C123" s="3">
         <v>1</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E123">
         <f>VLOOKUP(A123,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="F123">
         <v>2</v>
       </c>
       <c r="G123">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A124" s="5" t="s">
-        <v>216</v>
+      <c r="A124" s="2" t="s">
+        <v>318</v>
       </c>
       <c r="B124">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="C124" s="3">
         <v>1</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E124">
         <f>VLOOKUP(A124,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="F124">
         <v>2</v>
@@ -7791,45 +7799,45 @@
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A125" s="7" t="s">
-        <v>217</v>
+      <c r="A125" s="5" t="s">
+        <v>214</v>
       </c>
       <c r="B125">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="C125" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="E125">
         <f>VLOOKUP(A125,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1619</v>
+        <v>1615</v>
       </c>
       <c r="F125">
         <v>2</v>
       </c>
       <c r="G125">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="7" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B126">
-        <v>4020</v>
+        <v>4019</v>
       </c>
       <c r="C126" s="3">
         <v>0</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E126">
         <f>VLOOKUP(A126,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="F126">
         <v>2</v>
@@ -7839,141 +7847,141 @@
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A127" s="6" t="s">
-        <v>219</v>
+      <c r="A127" s="7" t="s">
+        <v>216</v>
       </c>
       <c r="B127">
-        <v>4021</v>
+        <v>4020</v>
       </c>
       <c r="C127" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="E127">
         <f>VLOOKUP(A127,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1650</v>
+        <v>1620</v>
       </c>
       <c r="F127">
         <v>2</v>
       </c>
       <c r="G127">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B128">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="C128" s="3">
         <v>1</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>278</v>
+        <v>321</v>
       </c>
       <c r="E128">
         <f>VLOOKUP(A128,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="F128">
         <v>2</v>
       </c>
       <c r="G128">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B129">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="C129" s="3">
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="E129">
         <f>VLOOKUP(A129,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="F129">
         <v>2</v>
       </c>
       <c r="G129">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B130">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="C130" s="3">
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="E130">
         <f>VLOOKUP(A130,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="F130">
         <v>2</v>
       </c>
       <c r="G130">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="6" t="s">
-        <v>293</v>
+        <v>220</v>
       </c>
       <c r="B131">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="C131" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="E131">
         <f>VLOOKUP(A131,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="F131">
         <v>2</v>
       </c>
       <c r="G131">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="6" t="s">
-        <v>223</v>
+        <v>288</v>
       </c>
       <c r="B132">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="C132" s="3">
         <v>0</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="E132">
         <f>VLOOKUP(A132,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="F132">
         <v>2</v>
@@ -7984,20 +7992,20 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B133">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="C133" s="3">
         <v>0</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="E133">
         <f>VLOOKUP(A133,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="F133">
         <v>2</v>
@@ -8008,92 +8016,92 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B134">
-        <v>4028</v>
+        <v>4027</v>
       </c>
       <c r="C134" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="E134">
         <f>VLOOKUP(A134,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="F134">
         <v>2</v>
       </c>
       <c r="G134">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B135">
-        <v>4029</v>
+        <v>4028</v>
       </c>
       <c r="C135" s="3">
         <v>1</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>283</v>
+        <v>322</v>
       </c>
       <c r="E135">
         <f>VLOOKUP(A135,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="F135">
         <v>2</v>
       </c>
       <c r="G135">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B136">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="C136" s="3">
         <v>1</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="E136">
         <f>VLOOKUP(A136,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="F136">
         <v>2</v>
       </c>
       <c r="G136">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B137">
-        <v>4031</v>
+        <v>4030</v>
       </c>
       <c r="C137" s="3">
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>284</v>
+        <v>323</v>
       </c>
       <c r="E137">
         <f>VLOOKUP(A137,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="F137">
         <v>2</v>
@@ -8104,44 +8112,44 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B138">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="C138" s="3">
         <v>1</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="E138">
         <f>VLOOKUP(A138,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="F138">
         <v>2</v>
       </c>
       <c r="G138">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B139">
-        <v>4033</v>
+        <v>4032</v>
       </c>
       <c r="C139" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E139">
         <f>VLOOKUP(A139,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="F139">
         <v>2</v>
@@ -8152,44 +8160,44 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B140">
-        <v>4034</v>
+        <v>4033</v>
       </c>
       <c r="C140" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="E140">
         <f>VLOOKUP(A140,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="F140">
         <v>2</v>
       </c>
       <c r="G140">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B141">
-        <v>4035</v>
+        <v>4034</v>
       </c>
       <c r="C141" s="3">
         <v>1</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="E141">
         <f>VLOOKUP(A141,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="F141">
         <v>2</v>
@@ -8200,20 +8208,20 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B142">
-        <v>4036</v>
+        <v>4035</v>
       </c>
       <c r="C142" s="3">
         <v>1</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="E142">
         <f>VLOOKUP(A142,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="F142">
         <v>2</v>
@@ -8223,21 +8231,21 @@
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A143" s="8" t="s">
-        <v>234</v>
+      <c r="A143" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="B143">
-        <v>4037</v>
+        <v>4036</v>
       </c>
       <c r="C143" s="3">
         <v>1</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E143">
         <f>VLOOKUP(A143,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="F143">
         <v>2</v>
@@ -8248,44 +8256,44 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B144">
-        <v>4038</v>
+        <v>4037</v>
       </c>
       <c r="C144" s="3">
         <v>1</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="E144">
         <f>VLOOKUP(A144,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1700</v>
+        <v>1666</v>
       </c>
       <c r="F144">
         <v>2</v>
       </c>
       <c r="G144">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B145">
-        <v>4039</v>
+        <v>4038</v>
       </c>
       <c r="C145" s="3">
         <v>1</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E145">
         <f>VLOOKUP(A145,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="F145">
         <v>2</v>
@@ -8296,44 +8304,44 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
-        <v>292</v>
+        <v>234</v>
       </c>
       <c r="B146">
-        <v>4040</v>
+        <v>4039</v>
       </c>
       <c r="C146" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E146">
         <f>VLOOKUP(A146,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="F146">
         <v>2</v>
       </c>
       <c r="G146">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
-        <v>237</v>
+        <v>287</v>
       </c>
       <c r="B147">
-        <v>4041</v>
+        <v>4040</v>
       </c>
       <c r="C147" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="E147">
         <f>VLOOKUP(A147,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="F147">
         <v>2</v>
@@ -8344,140 +8352,140 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B148">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="C148" s="3">
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="E148">
         <f>VLOOKUP(A148,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="F148">
         <v>2</v>
       </c>
       <c r="G148">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B149">
-        <v>4043</v>
+        <v>4042</v>
       </c>
       <c r="C149" s="3">
         <v>1</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="E149">
         <f>VLOOKUP(A149,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="F149">
         <v>2</v>
       </c>
       <c r="G149">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B150">
-        <v>4044</v>
+        <v>4043</v>
       </c>
       <c r="C150" s="3">
         <v>1</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E150">
         <f>VLOOKUP(A150,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="F150">
         <v>2</v>
       </c>
       <c r="G150">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B151">
-        <v>4045</v>
+        <v>4044</v>
       </c>
       <c r="C151" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E151">
         <f>VLOOKUP(A151,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="F151">
         <v>2</v>
       </c>
       <c r="G151">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B152">
-        <v>4046</v>
+        <v>4045</v>
       </c>
       <c r="C152" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E152">
         <f>VLOOKUP(A152,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="F152">
         <v>2</v>
       </c>
       <c r="G152">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B153">
-        <v>4047</v>
+        <v>4046</v>
       </c>
       <c r="C153" s="3">
         <v>1</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E153">
         <f>VLOOKUP(A153,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="F153">
         <v>2</v>
@@ -8488,68 +8496,68 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" s="8" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B154">
-        <v>4048</v>
+        <v>4047</v>
       </c>
       <c r="C154" s="3">
         <v>1</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E154">
         <f>VLOOKUP(A154,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="F154">
         <v>2</v>
       </c>
       <c r="G154">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A155" t="s">
-        <v>298</v>
+      <c r="A155" s="8" t="s">
+        <v>242</v>
       </c>
       <c r="B155">
-        <v>4049</v>
+        <v>4048</v>
       </c>
       <c r="C155" s="3">
         <v>1</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>306</v>
+        <v>264</v>
       </c>
       <c r="E155">
         <f>VLOOKUP(A155,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1800</v>
+        <v>1710</v>
       </c>
       <c r="F155">
         <v>2</v>
       </c>
       <c r="G155">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A156" s="2" t="s">
-        <v>324</v>
+      <c r="A156" t="s">
+        <v>293</v>
       </c>
       <c r="B156">
-        <v>4050</v>
+        <v>4049</v>
       </c>
       <c r="C156" s="3">
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="E156">
         <f>VLOOKUP(A156,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="F156">
         <v>2</v>
@@ -8559,69 +8567,69 @@
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A157" t="s">
-        <v>299</v>
+      <c r="A157" s="2" t="s">
+        <v>319</v>
       </c>
       <c r="B157">
-        <v>4051</v>
+        <v>4050</v>
       </c>
       <c r="C157" s="3">
         <v>1</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="E157">
         <f>VLOOKUP(A157,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="F157">
         <v>2</v>
       </c>
       <c r="G157">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B158">
-        <v>4052</v>
+        <v>4051</v>
       </c>
       <c r="C158" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="E158">
         <f>VLOOKUP(A158,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="F158">
         <v>2</v>
       </c>
       <c r="G158">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B159">
-        <v>4053</v>
+        <v>4052</v>
       </c>
       <c r="C159" s="3">
         <v>0</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="E159">
         <f>VLOOKUP(A159,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="F159">
         <v>2</v>
@@ -8632,44 +8640,44 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B160">
-        <v>4054</v>
+        <v>4053</v>
       </c>
       <c r="C160" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="E160">
         <f>VLOOKUP(A160,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="F160">
         <v>2</v>
       </c>
       <c r="G160">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B161">
-        <v>4055</v>
+        <v>4054</v>
       </c>
       <c r="C161" s="3">
         <v>1</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E161">
         <f>VLOOKUP(A161,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="F161">
         <v>2</v>
@@ -8680,20 +8688,20 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B162">
-        <v>4056</v>
+        <v>4055</v>
       </c>
       <c r="C162" s="3">
         <v>1</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="E162">
         <f>VLOOKUP(A162,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="F162">
         <v>2</v>
@@ -8704,35 +8712,59 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B163">
-        <v>4057</v>
+        <v>4056</v>
       </c>
       <c r="C163" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="E163">
         <f>VLOOKUP(A163,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
+        <v>1807</v>
+      </c>
+      <c r="F163">
+        <v>2</v>
+      </c>
+      <c r="G163">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>300</v>
+      </c>
+      <c r="B164">
+        <v>4057</v>
+      </c>
+      <c r="C164" s="3">
+        <v>0</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E164">
+        <f>VLOOKUP(A164,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
         <v>1808</v>
       </c>
-      <c r="F163">
-        <v>2</v>
-      </c>
-      <c r="G163">
+      <c r="F164">
+        <v>2</v>
+      </c>
+      <c r="G164">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G163"/>
+  <autoFilter ref="A3:G164"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A122:A123">
+  <conditionalFormatting sqref="A123:A124">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A156">
+  <conditionalFormatting sqref="A157">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/FormulaData.xlsx
+++ b/Datas/FormulaData.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="FormulaData" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FormulaData!$A$3:$G$164</definedName>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="331">
   <si>
     <t>formulaName</t>
   </si>
@@ -375,9 +376,6 @@
     <t>3113,3000</t>
   </si>
   <si>
-    <t>3009,3004</t>
-  </si>
-  <si>
     <t>3011</t>
   </si>
   <si>
@@ -447,12 +445,6 @@
     <t>1017</t>
   </si>
   <si>
-    <t>1028,1005,1008,3004</t>
-  </si>
-  <si>
-    <t>1014,3008,1009,3004</t>
-  </si>
-  <si>
     <t>3006,3125</t>
   </si>
   <si>
@@ -462,12 +454,6 @@
     <t>3000,4021,3113</t>
   </si>
   <si>
-    <t>3010,3006,3004</t>
-  </si>
-  <si>
-    <t>3010,3004</t>
-  </si>
-  <si>
     <t>3123,3001</t>
   </si>
   <si>
@@ -538,18 +524,6 @@
   </si>
   <si>
     <t>4116,3003</t>
-  </si>
-  <si>
-    <t>4007,3004</t>
-  </si>
-  <si>
-    <t>1018,3004,4100,4113</t>
-  </si>
-  <si>
-    <t>3153,3000</t>
-  </si>
-  <si>
-    <t>4000,1014,3004,1017</t>
   </si>
   <si>
     <t>4006,1027</t>
@@ -596,10 +570,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>216</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>皮革</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1067,10 +1037,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3164,3134,1006,4015</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>凉茶</t>
   </si>
   <si>
@@ -1117,6 +1083,56 @@
   </si>
   <si>
     <t>钢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3009,200</t>
+  </si>
+  <si>
+    <t>1028,1005,1008,200</t>
+  </si>
+  <si>
+    <t>1014,3008,1009,200</t>
+  </si>
+  <si>
+    <t>3010,3006,200</t>
+  </si>
+  <si>
+    <t>3010,200</t>
+  </si>
+  <si>
+    <t>4007,200</t>
+  </si>
+  <si>
+    <t>1018,200,4100,4113</t>
+  </si>
+  <si>
+    <t>3158,3000</t>
+  </si>
+  <si>
+    <t>4000,1014,200,1017</t>
+  </si>
+  <si>
+    <t>3164,3134,1006,4015</t>
+  </si>
+  <si>
+    <t>面包</t>
+  </si>
+  <si>
+    <t>煮蟹肉</t>
+  </si>
+  <si>
+    <t>鲮鱼丸</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>296,296,297</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>298,298,297</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1224,7 +1240,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4946,7 +4962,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B6">
         <v>3011</v>
@@ -4954,8 +4970,8 @@
       <c r="C6">
         <v>10</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>175</v>
+      <c r="D6" s="1">
+        <v>216</v>
       </c>
       <c r="E6">
         <f>VLOOKUP(A6,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -4976,7 +4992,7 @@
         <v>3012</v>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>120</v>
@@ -5282,7 +5298,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="B20">
         <v>3025</v>
@@ -5291,7 +5307,7 @@
         <v>13</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>103</v>
+        <v>315</v>
       </c>
       <c r="E20">
         <f>VLOOKUP(A20,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5315,7 +5331,7 @@
         <v>13</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E21">
         <f>VLOOKUP(A21,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5339,7 +5355,7 @@
         <v>13</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E22">
         <f>VLOOKUP(A22,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5363,7 +5379,7 @@
         <v>11</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E23">
         <f>VLOOKUP(A23,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5387,7 +5403,7 @@
         <v>11</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E24">
         <f>VLOOKUP(A24,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5411,7 +5427,7 @@
         <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E25">
         <f>VLOOKUP(A25,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5435,7 +5451,7 @@
         <v>12</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E26">
         <f>VLOOKUP(A26,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5459,7 +5475,7 @@
         <v>13</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E27">
         <f>VLOOKUP(A27,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5483,7 +5499,7 @@
         <v>15</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E28">
         <f>VLOOKUP(A28,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5507,7 +5523,7 @@
         <v>15</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E29">
         <f>VLOOKUP(A29,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5531,7 +5547,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E30">
         <f>VLOOKUP(A30,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5555,7 +5571,7 @@
         <v>15</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E31">
         <f>VLOOKUP(A31,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5579,7 +5595,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E32">
         <f>VLOOKUP(A32,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5603,7 +5619,7 @@
         <v>15</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E33">
         <f>VLOOKUP(A33,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5627,7 +5643,7 @@
         <v>15</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E34">
         <f>VLOOKUP(A34,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5651,7 +5667,7 @@
         <v>15</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E35">
         <f>VLOOKUP(A35,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5675,7 +5691,7 @@
         <v>13</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E36">
         <f>VLOOKUP(A36,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5699,7 +5715,7 @@
         <v>15</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E37">
         <f>VLOOKUP(A37,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5723,7 +5739,7 @@
         <v>14</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E38">
         <f>VLOOKUP(A38,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5747,7 +5763,7 @@
         <v>13</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E39">
         <f>VLOOKUP(A39,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5771,7 +5787,7 @@
         <v>12</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E40">
         <f>VLOOKUP(A40,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5795,7 +5811,7 @@
         <v>12</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E41">
         <f>VLOOKUP(A41,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5819,7 +5835,7 @@
         <v>13</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E42">
         <f>VLOOKUP(A42,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5843,7 +5859,7 @@
         <v>12</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>127</v>
+        <v>316</v>
       </c>
       <c r="E43">
         <f>VLOOKUP(A43,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5867,7 +5883,7 @@
         <v>12</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>128</v>
+        <v>317</v>
       </c>
       <c r="E44">
         <f>VLOOKUP(A44,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5891,7 +5907,7 @@
         <v>15</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E45">
         <f>VLOOKUP(A45,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5915,7 +5931,7 @@
         <v>15</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E46">
         <f>VLOOKUP(A46,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5939,7 +5955,7 @@
         <v>11</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E47">
         <f>VLOOKUP(A47,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5963,7 +5979,7 @@
         <v>15</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>132</v>
+        <v>318</v>
       </c>
       <c r="E48">
         <f>VLOOKUP(A48,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -5987,7 +6003,7 @@
         <v>15</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>133</v>
+        <v>319</v>
       </c>
       <c r="E49">
         <f>VLOOKUP(A49,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6011,7 +6027,7 @@
         <v>14</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E50">
         <f>VLOOKUP(A50,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6035,7 +6051,7 @@
         <v>14</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E51">
         <f>VLOOKUP(A51,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6059,7 +6075,7 @@
         <v>14</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E52">
         <f>VLOOKUP(A52,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6083,7 +6099,7 @@
         <v>14</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E53">
         <f>VLOOKUP(A53,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6107,7 +6123,7 @@
         <v>14</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E54">
         <f>VLOOKUP(A54,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6131,7 +6147,7 @@
         <v>14</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E55">
         <f>VLOOKUP(A55,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6155,7 +6171,7 @@
         <v>14</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E56">
         <f>VLOOKUP(A56,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6179,7 +6195,7 @@
         <v>14</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E57">
         <f>VLOOKUP(A57,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6203,7 +6219,7 @@
         <v>13</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E58">
         <f>VLOOKUP(A58,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6227,7 +6243,7 @@
         <v>13</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E59">
         <f>VLOOKUP(A59,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6251,7 +6267,7 @@
         <v>13</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E60">
         <f>VLOOKUP(A60,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6275,7 +6291,7 @@
         <v>13</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E61">
         <f>VLOOKUP(A61,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6299,7 +6315,7 @@
         <v>13</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E62">
         <f>VLOOKUP(A62,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6323,7 +6339,7 @@
         <v>13</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E63">
         <f>VLOOKUP(A63,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6347,7 +6363,7 @@
         <v>13</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E64">
         <f>VLOOKUP(A64,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6371,7 +6387,7 @@
         <v>13</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E65">
         <f>VLOOKUP(A65,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6395,7 +6411,7 @@
         <v>13</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E66">
         <f>VLOOKUP(A66,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6419,7 +6435,7 @@
         <v>13</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E67">
         <f>VLOOKUP(A67,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6443,7 +6459,7 @@
         <v>13</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E68">
         <f>VLOOKUP(A68,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6467,7 +6483,7 @@
         <v>13</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E69">
         <f>VLOOKUP(A69,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6491,7 +6507,7 @@
         <v>13</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E70">
         <f>VLOOKUP(A70,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6515,7 +6531,7 @@
         <v>13</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E71">
         <f>VLOOKUP(A71,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6539,7 +6555,7 @@
         <v>13</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E72">
         <f>VLOOKUP(A72,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6563,7 +6579,7 @@
         <v>13</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E73">
         <f>VLOOKUP(A73,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6578,7 +6594,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="B74">
         <v>3079</v>
@@ -6587,7 +6603,7 @@
         <v>12</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>158</v>
+        <v>320</v>
       </c>
       <c r="E74">
         <f>VLOOKUP(A74,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6611,7 +6627,7 @@
         <v>12</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>159</v>
+        <v>321</v>
       </c>
       <c r="E75">
         <f>VLOOKUP(A75,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6635,7 +6651,7 @@
         <v>11</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>160</v>
+        <v>322</v>
       </c>
       <c r="E76">
         <f>VLOOKUP(A76,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6659,7 +6675,7 @@
         <v>12</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>161</v>
+        <v>323</v>
       </c>
       <c r="E77">
         <f>VLOOKUP(A77,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6674,7 +6690,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="B78">
         <v>3083</v>
@@ -6683,7 +6699,7 @@
         <v>12</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="E78">
         <f>VLOOKUP(A78,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6707,7 +6723,7 @@
         <v>11</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E79">
         <f>VLOOKUP(A79,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6731,7 +6747,7 @@
         <v>12</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="E80">
         <f>VLOOKUP(A80,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6755,7 +6771,7 @@
         <v>12</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="E81">
         <f>VLOOKUP(A81,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6779,7 +6795,7 @@
         <v>11</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="E82">
         <f>VLOOKUP(A82,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6803,7 +6819,7 @@
         <v>11</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="E83">
         <f>VLOOKUP(A83,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6827,7 +6843,7 @@
         <v>12</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="E84">
         <f>VLOOKUP(A84,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6851,7 +6867,7 @@
         <v>11</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="E85">
         <f>VLOOKUP(A85,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6875,7 +6891,7 @@
         <v>11</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="E86">
         <f>VLOOKUP(A86,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6890,7 +6906,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="B87">
         <v>3092</v>
@@ -6899,7 +6915,7 @@
         <v>15</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="E87">
         <f>VLOOKUP(A87,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6914,7 +6930,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="B88">
         <v>2000</v>
@@ -6922,7 +6938,7 @@
       <c r="C88">
         <v>3</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="1">
         <v>102</v>
       </c>
       <c r="E88">
@@ -6938,7 +6954,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B89">
         <v>2001</v>
@@ -6947,7 +6963,7 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="E89">
         <f>VLOOKUP(A89,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6962,7 +6978,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B90">
         <v>2003</v>
@@ -6971,7 +6987,7 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="E90">
         <f>VLOOKUP(A90,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -6986,7 +7002,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="B91">
         <v>2011</v>
@@ -6994,7 +7010,7 @@
       <c r="C91">
         <v>5</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D91" s="9">
         <v>283</v>
       </c>
       <c r="E91">
@@ -7010,7 +7026,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B92">
         <v>2012</v>
@@ -7018,7 +7034,7 @@
       <c r="C92">
         <v>5</v>
       </c>
-      <c r="D92" s="2">
+      <c r="D92" s="9">
         <v>203</v>
       </c>
       <c r="E92">
@@ -7034,7 +7050,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="B93">
         <v>2020</v>
@@ -7042,8 +7058,8 @@
       <c r="C93">
         <v>0</v>
       </c>
-      <c r="D93" s="9">
-        <v>296296297</v>
+      <c r="D93" s="9" t="s">
+        <v>329</v>
       </c>
       <c r="E93">
         <v>298</v>
@@ -7057,7 +7073,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="B94">
         <v>2021</v>
@@ -7065,8 +7081,8 @@
       <c r="C94">
         <v>0</v>
       </c>
-      <c r="D94" s="9">
-        <v>298298297</v>
+      <c r="D94" s="9" t="s">
+        <v>330</v>
       </c>
       <c r="E94">
         <v>299</v>
@@ -7080,7 +7096,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B95">
         <v>2100</v>
@@ -7089,7 +7105,7 @@
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E95">
         <f>VLOOKUP(A95,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7104,7 +7120,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B96">
         <v>2101</v>
@@ -7113,7 +7129,7 @@
         <v>2</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="E96">
         <f>VLOOKUP(A96,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7128,7 +7144,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B97">
         <v>2102</v>
@@ -7137,7 +7153,7 @@
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="E97">
         <f>VLOOKUP(A97,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7152,7 +7168,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B98">
         <v>2103</v>
@@ -7161,7 +7177,7 @@
         <v>2</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="E98">
         <f>VLOOKUP(A98,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7176,7 +7192,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B99">
         <v>2104</v>
@@ -7185,7 +7201,7 @@
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="E99">
         <f>VLOOKUP(A99,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7200,7 +7216,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B100">
         <v>2105</v>
@@ -7209,7 +7225,7 @@
         <v>2</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E100">
         <f>VLOOKUP(A100,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7224,7 +7240,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B101">
         <v>2106</v>
@@ -7233,7 +7249,7 @@
         <v>2</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E101">
         <f>VLOOKUP(A101,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7248,7 +7264,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B102">
         <v>2107</v>
@@ -7257,7 +7273,7 @@
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E102">
         <f>VLOOKUP(A102,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7272,7 +7288,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="B103">
         <v>2108</v>
@@ -7281,7 +7297,7 @@
         <v>2</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="E103">
         <f>VLOOKUP(A103,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7296,7 +7312,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B104">
         <v>2109</v>
@@ -7305,7 +7321,7 @@
         <v>2</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="E104">
         <f>VLOOKUP(A104,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7320,7 +7336,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="B105">
         <v>2110</v>
@@ -7329,7 +7345,7 @@
         <v>2</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E105">
         <f>VLOOKUP(A105,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7344,7 +7360,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="B106">
         <v>2111</v>
@@ -7353,7 +7369,7 @@
         <v>2</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="E106">
         <f>VLOOKUP(A106,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7368,7 +7384,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B107">
         <v>4000</v>
@@ -7377,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="E107">
         <f>VLOOKUP(A107,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7392,7 +7408,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B108">
         <v>4001</v>
@@ -7401,7 +7417,7 @@
         <v>0</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E108">
         <f>VLOOKUP(A108,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7416,7 +7432,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="6" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="B109">
         <v>4002</v>
@@ -7425,7 +7441,7 @@
         <v>0</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="E109">
         <f>VLOOKUP(A109,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7440,7 +7456,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B110">
         <v>4003</v>
@@ -7449,7 +7465,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="E110">
         <f>VLOOKUP(A110,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7464,7 +7480,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="B111">
         <v>4004</v>
@@ -7473,7 +7489,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E111">
         <f>VLOOKUP(A111,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7488,7 +7504,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B112">
         <v>4005</v>
@@ -7497,7 +7513,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="E112">
         <f>VLOOKUP(A112,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7512,7 +7528,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="B113">
         <v>4006</v>
@@ -7521,7 +7537,7 @@
         <v>0</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="E113">
         <f>VLOOKUP(A113,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7536,7 +7552,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="B114">
         <v>4007</v>
@@ -7545,7 +7561,7 @@
         <v>0</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="E114">
         <f>VLOOKUP(A114,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7560,7 +7576,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B115">
         <v>4008</v>
@@ -7569,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="E115">
         <f>VLOOKUP(A115,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7584,7 +7600,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="7" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B116">
         <v>4009</v>
@@ -7593,7 +7609,7 @@
         <v>0</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="E116">
         <f>VLOOKUP(A116,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7608,7 +7624,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="7" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="B117">
         <v>4010</v>
@@ -7617,7 +7633,7 @@
         <v>0</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="E117">
         <f>VLOOKUP(A117,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7632,7 +7648,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="B118">
         <v>4011</v>
@@ -7641,7 +7657,7 @@
         <v>0</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="E118">
         <f>VLOOKUP(A118,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7656,7 +7672,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B119">
         <v>4012</v>
@@ -7665,7 +7681,7 @@
         <v>0</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="E119">
         <f>VLOOKUP(A119,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7680,7 +7696,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="B120">
         <v>4013</v>
@@ -7689,7 +7705,7 @@
         <v>0</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="E120">
         <f>VLOOKUP(A120,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7704,7 +7720,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B121">
         <v>4014</v>
@@ -7713,7 +7729,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="E121">
         <f>VLOOKUP(A121,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7728,7 +7744,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B122">
         <v>4015</v>
@@ -7737,7 +7753,7 @@
         <v>1</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="E122">
         <f>VLOOKUP(A122,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7752,7 +7768,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="B123">
         <v>4016</v>
@@ -7761,7 +7777,7 @@
         <v>1</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="E123">
         <f>VLOOKUP(A123,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7776,7 +7792,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="B124">
         <v>4017</v>
@@ -7785,7 +7801,7 @@
         <v>1</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="E124">
         <f>VLOOKUP(A124,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7800,7 +7816,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="B125">
         <v>4018</v>
@@ -7809,7 +7825,7 @@
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="E125">
         <f>VLOOKUP(A125,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7824,7 +7840,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="7" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="B126">
         <v>4019</v>
@@ -7833,7 +7849,7 @@
         <v>0</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="E126">
         <f>VLOOKUP(A126,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7848,7 +7864,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="7" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B127">
         <v>4020</v>
@@ -7857,7 +7873,7 @@
         <v>0</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="E127">
         <f>VLOOKUP(A127,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7872,7 +7888,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="B128">
         <v>4021</v>
@@ -7881,7 +7897,7 @@
         <v>1</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="E128">
         <f>VLOOKUP(A128,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7896,7 +7912,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="6" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="B129">
         <v>4022</v>
@@ -7905,7 +7921,7 @@
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="E129">
         <f>VLOOKUP(A129,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7920,7 +7936,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="6" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="B130">
         <v>4023</v>
@@ -7929,7 +7945,7 @@
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="E130">
         <f>VLOOKUP(A130,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7944,7 +7960,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="6" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B131">
         <v>4024</v>
@@ -7953,7 +7969,7 @@
         <v>1</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="E131">
         <f>VLOOKUP(A131,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7968,7 +7984,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="6" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="B132">
         <v>4025</v>
@@ -7977,7 +7993,7 @@
         <v>0</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="E132">
         <f>VLOOKUP(A132,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -7992,7 +8008,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="6" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="B133">
         <v>4026</v>
@@ -8001,7 +8017,7 @@
         <v>0</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="E133">
         <f>VLOOKUP(A133,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8016,7 +8032,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="6" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="B134">
         <v>4027</v>
@@ -8025,7 +8041,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="E134">
         <f>VLOOKUP(A134,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8040,7 +8056,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="6" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="B135">
         <v>4028</v>
@@ -8049,7 +8065,7 @@
         <v>1</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="E135">
         <f>VLOOKUP(A135,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8064,7 +8080,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="6" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="B136">
         <v>4029</v>
@@ -8073,7 +8089,7 @@
         <v>1</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="E136">
         <f>VLOOKUP(A136,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8088,7 +8104,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="6" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="B137">
         <v>4030</v>
@@ -8097,7 +8113,7 @@
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="E137">
         <f>VLOOKUP(A137,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8112,7 +8128,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="6" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="B138">
         <v>4031</v>
@@ -8121,7 +8137,7 @@
         <v>1</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="E138">
         <f>VLOOKUP(A138,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8136,7 +8152,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="6" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="B139">
         <v>4032</v>
@@ -8145,7 +8161,7 @@
         <v>1</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="E139">
         <f>VLOOKUP(A139,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8160,7 +8176,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="6" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B140">
         <v>4033</v>
@@ -8169,7 +8185,7 @@
         <v>0</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="E140">
         <f>VLOOKUP(A140,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8184,7 +8200,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="6" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="B141">
         <v>4034</v>
@@ -8193,7 +8209,7 @@
         <v>1</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="E141">
         <f>VLOOKUP(A141,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8208,7 +8224,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="6" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B142">
         <v>4035</v>
@@ -8217,7 +8233,7 @@
         <v>1</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="E142">
         <f>VLOOKUP(A142,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8232,7 +8248,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="6" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B143">
         <v>4036</v>
@@ -8241,7 +8257,7 @@
         <v>1</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="E143">
         <f>VLOOKUP(A143,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8256,7 +8272,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="B144">
         <v>4037</v>
@@ -8265,7 +8281,7 @@
         <v>1</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="E144">
         <f>VLOOKUP(A144,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8280,7 +8296,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="B145">
         <v>4038</v>
@@ -8289,7 +8305,7 @@
         <v>1</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="E145">
         <f>VLOOKUP(A145,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8304,7 +8320,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="B146">
         <v>4039</v>
@@ -8313,7 +8329,7 @@
         <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="E146">
         <f>VLOOKUP(A146,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8328,7 +8344,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="B147">
         <v>4040</v>
@@ -8337,7 +8353,7 @@
         <v>0</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="E147">
         <f>VLOOKUP(A147,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8352,7 +8368,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="B148">
         <v>4041</v>
@@ -8361,7 +8377,7 @@
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="E148">
         <f>VLOOKUP(A148,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8376,7 +8392,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="B149">
         <v>4042</v>
@@ -8385,7 +8401,7 @@
         <v>1</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="E149">
         <f>VLOOKUP(A149,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8400,7 +8416,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="B150">
         <v>4043</v>
@@ -8409,7 +8425,7 @@
         <v>1</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="E150">
         <f>VLOOKUP(A150,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8424,7 +8440,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="B151">
         <v>4044</v>
@@ -8433,7 +8449,7 @@
         <v>1</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E151">
         <f>VLOOKUP(A151,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8448,7 +8464,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="B152">
         <v>4045</v>
@@ -8457,7 +8473,7 @@
         <v>0</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="E152">
         <f>VLOOKUP(A152,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8472,7 +8488,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B153">
         <v>4046</v>
@@ -8481,7 +8497,7 @@
         <v>1</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="E153">
         <f>VLOOKUP(A153,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8496,7 +8512,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" s="8" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B154">
         <v>4047</v>
@@ -8505,7 +8521,7 @@
         <v>1</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="E154">
         <f>VLOOKUP(A154,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8520,7 +8536,7 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" s="8" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="B155">
         <v>4048</v>
@@ -8529,7 +8545,7 @@
         <v>1</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="E155">
         <f>VLOOKUP(A155,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8544,7 +8560,7 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="B156">
         <v>4049</v>
@@ -8553,7 +8569,7 @@
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="E156">
         <f>VLOOKUP(A156,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8568,7 +8584,7 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="B157">
         <v>4050</v>
@@ -8577,7 +8593,7 @@
         <v>1</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="E157">
         <f>VLOOKUP(A157,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8592,7 +8608,7 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="B158">
         <v>4051</v>
@@ -8601,7 +8617,7 @@
         <v>1</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="E158">
         <f>VLOOKUP(A158,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8616,7 +8632,7 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="B159">
         <v>4052</v>
@@ -8625,7 +8641,7 @@
         <v>0</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E159">
         <f>VLOOKUP(A159,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8640,7 +8656,7 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="B160">
         <v>4053</v>
@@ -8649,7 +8665,7 @@
         <v>0</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E160">
         <f>VLOOKUP(A160,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8664,7 +8680,7 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="B161">
         <v>4054</v>
@@ -8673,7 +8689,7 @@
         <v>1</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="E161">
         <f>VLOOKUP(A161,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8688,7 +8704,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="B162">
         <v>4055</v>
@@ -8697,7 +8713,7 @@
         <v>1</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E162">
         <f>VLOOKUP(A162,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8712,7 +8728,7 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="B163">
         <v>4056</v>
@@ -8721,7 +8737,7 @@
         <v>1</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E163">
         <f>VLOOKUP(A163,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8736,7 +8752,7 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="B164">
         <v>4057</v>
@@ -8745,7 +8761,7 @@
         <v>0</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E164">
         <f>VLOOKUP(A164,[1]ItemData!$A$4:$B$413,2,FALSE)</f>
@@ -8769,14 +8785,691 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="D13:D73" numberStoredAsText="1"/>
-  </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="F2:G85"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="G4" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="5" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F17" t="s">
+        <v>325</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="18" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F19" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F22" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F23" t="s">
+        <v>30</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F24" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F26" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F27" t="s">
+        <v>34</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F28" t="s">
+        <v>35</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F29" t="s">
+        <v>36</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F30" t="s">
+        <v>37</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="31" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F31" t="s">
+        <v>38</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F32" t="s">
+        <v>39</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F33" t="s">
+        <v>40</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F34" t="s">
+        <v>41</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F35" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="36" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F36" t="s">
+        <v>42</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="37" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F37" t="s">
+        <v>43</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="38" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F38" t="s">
+        <v>44</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F39" t="s">
+        <v>45</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F40" t="s">
+        <v>46</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="41" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F41" t="s">
+        <v>47</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="42" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F42" t="s">
+        <v>48</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="43" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="44" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F44" t="s">
+        <v>50</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F45" t="s">
+        <v>51</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="46" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F46" t="s">
+        <v>52</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="47" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F47" t="s">
+        <v>53</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="48" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F48" t="s">
+        <v>54</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="49" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F49" t="s">
+        <v>55</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="50" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F50" t="s">
+        <v>56</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="51" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F51" t="s">
+        <v>57</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F52" t="s">
+        <v>58</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="53" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F53" t="s">
+        <v>59</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="54" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F54" t="s">
+        <v>60</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="55" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F55" t="s">
+        <v>61</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="56" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F56" t="s">
+        <v>62</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="57" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F57" t="s">
+        <v>63</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="58" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F58" t="s">
+        <v>64</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="59" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F59" t="s">
+        <v>65</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="60" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F60" t="s">
+        <v>66</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="61" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F61" t="s">
+        <v>67</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="62" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F62" t="s">
+        <v>68</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="63" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F63" t="s">
+        <v>69</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="64" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F64" t="s">
+        <v>70</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="65" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F65" t="s">
+        <v>71</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="66" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F66" t="s">
+        <v>72</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="67" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="68" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F68" t="s">
+        <v>74</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="69" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F69" t="s">
+        <v>75</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="70" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F70" t="s">
+        <v>76</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="71" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F71" t="s">
+        <v>77</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="72" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F72" t="s">
+        <v>326</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="73" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F73" t="s">
+        <v>78</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="74" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F74" t="s">
+        <v>79</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="75" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F75" t="s">
+        <v>80</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="76" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F76" t="s">
+        <v>327</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="77" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F77" t="s">
+        <v>81</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="78" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F78" t="s">
+        <v>82</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="79" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F79" t="s">
+        <v>83</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="80" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F80" t="s">
+        <v>84</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="81" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F81" t="s">
+        <v>85</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="82" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F82" t="s">
+        <v>86</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="83" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F83" t="s">
+        <v>87</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="84" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F84" t="s">
+        <v>88</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="85" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F85" t="s">
+        <v>302</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A4:C64"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
